--- a/2025.xlsx
+++ b/2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="Questa_cartella_di_lavoro" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.0.10\Assofrutti\MAGAZZINO\RACCOLTO 2025 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3928C86D-9FD4-452F-A7E9-16EF36C02113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0454CDFB-C6A4-462F-819E-788772F7B20E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="471" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -82,7 +82,7 @@
     <author>Giuseppe</author>
   </authors>
   <commentList>
-    <comment ref="G38" authorId="0" shapeId="0" xr:uid="{4F2EEA19-78A7-4BD7-95AB-49158DADB34F}">
+    <comment ref="G49" authorId="0" shapeId="0" xr:uid="{4F2EEA19-78A7-4BD7-95AB-49158DADB34F}">
       <text>
         <r>
           <rPr>
@@ -111,7 +111,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G40" authorId="0" shapeId="0" xr:uid="{6283F16D-1964-4260-A917-DE3147F07F57}">
+    <comment ref="G51" authorId="0" shapeId="0" xr:uid="{6283F16D-1964-4260-A917-DE3147F07F57}">
       <text>
         <r>
           <rPr>
@@ -137,7 +137,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G72" authorId="0" shapeId="0" xr:uid="{60483EB1-A147-463E-934C-1F6A8FC7ACD4}">
+    <comment ref="G94" authorId="0" shapeId="0" xr:uid="{60483EB1-A147-463E-934C-1F6A8FC7ACD4}">
       <text>
         <r>
           <rPr>
@@ -165,7 +165,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G73" authorId="0" shapeId="0" xr:uid="{CDAF20F0-C4B4-4B96-8D6F-45EFFA7FFA71}">
+    <comment ref="G95" authorId="0" shapeId="0" xr:uid="{CDAF20F0-C4B4-4B96-8D6F-45EFFA7FFA71}">
       <text>
         <r>
           <rPr>
@@ -295,7 +295,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3121" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3239" uniqueCount="307">
   <si>
     <t>DATA</t>
   </si>
@@ -1205,6 +1205,18 @@
   <si>
     <t>FA072026</t>
   </si>
+  <si>
+    <t>damiano RESO</t>
+  </si>
+  <si>
+    <t>36/2026</t>
+  </si>
+  <si>
+    <t>BIG02/2026</t>
+  </si>
+  <si>
+    <t>RIPASSATE</t>
+  </si>
 </sst>
 </file>
 
@@ -2079,28 +2091,6 @@
     <xf numFmtId="17" fontId="9" fillId="2" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2122,32 +2112,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2167,11 +2137,53 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2537,20 +2549,20 @@
       <c r="B1" s="189"/>
       <c r="C1" s="189"/>
       <c r="D1" s="1">
-        <v>46231</v>
+        <v>46273</v>
       </c>
       <c r="E1" s="190"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="197" t="s">
+      <c r="G1" s="217" t="s">
         <v>130</v>
       </c>
-      <c r="H1" s="198"/>
-      <c r="I1" s="198"/>
-      <c r="J1" s="199"/>
-      <c r="K1" s="200" t="s">
+      <c r="H1" s="218"/>
+      <c r="I1" s="218"/>
+      <c r="J1" s="227"/>
+      <c r="K1" s="226" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="201"/>
+      <c r="L1" s="219"/>
     </row>
     <row r="2" spans="1:21" ht="39" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
@@ -2853,9 +2865,7 @@
       <c r="E11" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="70">
-        <v>1000</v>
-      </c>
+      <c r="F11" s="70"/>
       <c r="G11" s="70"/>
       <c r="H11" s="76" t="s">
         <v>260</v>
@@ -2865,16 +2875,14 @@
       </c>
       <c r="J11" s="70">
         <f t="shared" ref="J11:J13" si="1">F11-G11</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="K11" s="154" t="s">
         <v>68</v>
       </c>
       <c r="L11" s="63"/>
       <c r="M11" s="139"/>
-      <c r="N11" s="156">
-        <v>1000</v>
-      </c>
+      <c r="N11" s="156"/>
       <c r="O11" s="95"/>
       <c r="P11" s="18">
         <v>1E-3</v>
@@ -2909,9 +2917,7 @@
       <c r="E12" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="70">
-        <v>1000</v>
-      </c>
+      <c r="F12" s="70"/>
       <c r="G12" s="70"/>
       <c r="H12" s="76" t="s">
         <v>260</v>
@@ -2921,16 +2927,14 @@
       </c>
       <c r="J12" s="70">
         <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="K12" s="154" t="s">
         <v>69</v>
       </c>
       <c r="L12" s="63"/>
       <c r="M12" s="139"/>
-      <c r="N12" s="156">
-        <v>1000</v>
-      </c>
+      <c r="N12" s="156"/>
       <c r="O12" s="95"/>
       <c r="P12" s="18">
         <v>2E-3</v>
@@ -3065,9 +3069,7 @@
       <c r="E15" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="70">
-        <v>400</v>
-      </c>
+      <c r="F15" s="70"/>
       <c r="G15" s="70"/>
       <c r="H15" s="76" t="s">
         <v>260</v>
@@ -3077,16 +3079,14 @@
       </c>
       <c r="J15" s="70">
         <f>F15-G15</f>
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="K15" s="154" t="s">
         <v>73</v>
       </c>
       <c r="L15" s="63"/>
       <c r="M15" s="139"/>
-      <c r="N15" s="103">
-        <v>400</v>
-      </c>
+      <c r="N15" s="103"/>
       <c r="O15" s="95"/>
       <c r="P15" s="18">
         <v>3.0000000000000001E-3</v>
@@ -3290,9 +3290,7 @@
       </c>
       <c r="E21" s="32"/>
       <c r="F21" s="104"/>
-      <c r="G21" s="104">
-        <v>2000</v>
-      </c>
+      <c r="G21" s="104"/>
       <c r="H21" s="104" t="s">
         <v>297</v>
       </c>
@@ -3393,17 +3391,17 @@
       </c>
       <c r="F25" s="23">
         <f>SUM(F11:F18)</f>
-        <v>3473</v>
+        <v>1073</v>
       </c>
       <c r="G25" s="155">
         <f>SUM(G11:G24)</f>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="H25" s="23"/>
       <c r="I25" s="23"/>
       <c r="J25" s="23">
         <f>F25-G25</f>
-        <v>1473</v>
+        <v>1073</v>
       </c>
       <c r="K25" s="24" t="s">
         <v>16</v>
@@ -3418,7 +3416,7 @@
       </c>
       <c r="N25" s="25">
         <f>SUM(N11:N18)</f>
-        <v>3473</v>
+        <v>1073</v>
       </c>
       <c r="O25" s="25">
         <f>SUM(O11:O24)</f>
@@ -3499,24 +3497,20 @@
       <c r="E27" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="F27" s="163">
-        <v>300</v>
-      </c>
+      <c r="F27" s="163"/>
       <c r="G27" s="70"/>
       <c r="H27" s="70"/>
       <c r="I27" s="70"/>
       <c r="J27" s="70">
         <f t="shared" si="3"/>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="K27" s="68" t="s">
         <v>67</v>
       </c>
       <c r="L27" s="63"/>
       <c r="M27" s="65"/>
-      <c r="N27" s="158">
-        <v>300</v>
-      </c>
+      <c r="N27" s="158"/>
       <c r="O27" s="95"/>
       <c r="P27" s="18">
         <v>0</v>
@@ -3708,14 +3702,14 @@
         <v>19</v>
       </c>
       <c r="F31" s="163">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="G31" s="70"/>
       <c r="H31" s="70"/>
       <c r="I31" s="70"/>
       <c r="J31" s="70">
         <f t="shared" si="3"/>
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="K31" s="68" t="s">
         <v>73</v>
@@ -3723,7 +3717,7 @@
       <c r="L31" s="63"/>
       <c r="M31" s="65"/>
       <c r="N31" s="158">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="O31" s="95"/>
       <c r="P31" s="18">
@@ -3968,14 +3962,14 @@
         <v>19</v>
       </c>
       <c r="F36" s="163">
-        <v>670</v>
+        <v>572</v>
       </c>
       <c r="G36" s="70"/>
       <c r="H36" s="70"/>
       <c r="I36" s="70"/>
       <c r="J36" s="70">
         <f t="shared" si="3"/>
-        <v>670</v>
+        <v>572</v>
       </c>
       <c r="K36" s="68" t="s">
         <v>64</v>
@@ -3983,7 +3977,7 @@
       <c r="L36" s="63"/>
       <c r="M36" s="65"/>
       <c r="N36" s="158">
-        <v>670</v>
+        <v>572</v>
       </c>
       <c r="O36" s="95"/>
       <c r="P36" s="18">
@@ -4234,7 +4228,7 @@
       </c>
       <c r="F46" s="23">
         <f>SUM(F26:F38)</f>
-        <v>9970</v>
+        <v>9272</v>
       </c>
       <c r="G46" s="23">
         <f>SUM(G26:G45)</f>
@@ -4244,7 +4238,7 @@
       <c r="I46" s="23"/>
       <c r="J46" s="23">
         <f>F46-G46</f>
-        <v>9970</v>
+        <v>9272</v>
       </c>
       <c r="K46" s="24" t="s">
         <v>16</v>
@@ -4259,7 +4253,7 @@
       </c>
       <c r="N46" s="25">
         <f>SUM(N26:N45)</f>
-        <v>9970</v>
+        <v>9272</v>
       </c>
       <c r="O46" s="25">
         <f>SUM(O26:O45)</f>
@@ -4682,23 +4676,23 @@
       <c r="A59" s="70"/>
       <c r="B59" s="131"/>
       <c r="C59" s="70"/>
-      <c r="D59" s="202" t="s">
+      <c r="D59" s="204" t="s">
         <v>24</v>
       </c>
-      <c r="E59" s="203"/>
+      <c r="E59" s="205"/>
       <c r="F59" s="39">
         <f>SUM(F10,F25,F46,F50,F56)</f>
-        <v>14418</v>
+        <v>11320</v>
       </c>
       <c r="G59" s="39">
         <f>SUM(G10,G25,G46,G50,G56)</f>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="H59" s="39"/>
       <c r="I59" s="39"/>
       <c r="J59" s="39">
         <f>SUM(F59-G59)</f>
-        <v>12418</v>
+        <v>11320</v>
       </c>
       <c r="K59" s="40" t="s">
         <v>16</v>
@@ -4713,7 +4707,7 @@
       </c>
       <c r="N59" s="39">
         <f>SUM(N10,N25,N46,N50,N56)</f>
-        <v>14418</v>
+        <v>11320</v>
       </c>
       <c r="O59" s="39">
         <f>SUM(O10,O25,O46,O50,O56)</f>
@@ -4919,18 +4913,18 @@
       <c r="A68" s="111"/>
       <c r="B68" s="111"/>
       <c r="C68" s="111"/>
-      <c r="D68" s="220" t="s">
+      <c r="D68" s="206" t="s">
         <v>46</v>
       </c>
-      <c r="E68" s="221"/>
-      <c r="F68" s="221"/>
-      <c r="G68" s="221"/>
-      <c r="H68" s="221"/>
-      <c r="I68" s="221"/>
-      <c r="J68" s="221"/>
-      <c r="K68" s="221"/>
-      <c r="L68" s="221"/>
-      <c r="M68" s="222"/>
+      <c r="E68" s="207"/>
+      <c r="F68" s="207"/>
+      <c r="G68" s="207"/>
+      <c r="H68" s="207"/>
+      <c r="I68" s="207"/>
+      <c r="J68" s="207"/>
+      <c r="K68" s="207"/>
+      <c r="L68" s="207"/>
+      <c r="M68" s="208"/>
       <c r="N68" s="111"/>
       <c r="O68" s="111"/>
       <c r="P68" s="111"/>
@@ -4987,11 +4981,11 @@
       <c r="U70" s="111"/>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A71" s="223" t="s">
+      <c r="A71" s="209" t="s">
         <v>25</v>
       </c>
-      <c r="B71" s="224"/>
-      <c r="C71" s="225"/>
+      <c r="B71" s="210"/>
+      <c r="C71" s="211"/>
       <c r="D71" s="44" t="s">
         <v>26</v>
       </c>
@@ -5001,14 +4995,14 @@
       <c r="F71" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="G71" s="223" t="s">
+      <c r="G71" s="209" t="s">
         <v>27</v>
       </c>
-      <c r="H71" s="225"/>
-      <c r="I71" s="223" t="s">
+      <c r="H71" s="211"/>
+      <c r="I71" s="209" t="s">
         <v>28</v>
       </c>
-      <c r="J71" s="225"/>
+      <c r="J71" s="211"/>
       <c r="K71" s="111"/>
       <c r="L71" s="111"/>
       <c r="M71" s="111"/>
@@ -5033,18 +5027,18 @@
       <c r="I72" s="111"/>
       <c r="J72" s="111"/>
       <c r="K72" s="111"/>
-      <c r="L72" s="218" t="s">
+      <c r="L72" s="224" t="s">
         <v>44</v>
       </c>
-      <c r="M72" s="219"/>
-      <c r="N72" s="219"/>
-      <c r="O72" s="219"/>
-      <c r="P72" s="219"/>
-      <c r="Q72" s="219"/>
-      <c r="R72" s="219"/>
-      <c r="S72" s="219"/>
-      <c r="T72" s="219"/>
-      <c r="U72" s="219"/>
+      <c r="M72" s="225"/>
+      <c r="N72" s="225"/>
+      <c r="O72" s="225"/>
+      <c r="P72" s="225"/>
+      <c r="Q72" s="225"/>
+      <c r="R72" s="225"/>
+      <c r="S72" s="225"/>
+      <c r="T72" s="225"/>
+      <c r="U72" s="225"/>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="111"/>
@@ -5072,11 +5066,11 @@
       <c r="U73" s="130"/>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A74" s="204" t="s">
+      <c r="A74" s="196" t="s">
         <v>54</v>
       </c>
-      <c r="B74" s="205"/>
-      <c r="C74" s="206"/>
+      <c r="B74" s="197"/>
+      <c r="C74" s="198"/>
       <c r="D74" s="84"/>
       <c r="E74" s="84">
         <v>51420</v>
@@ -5084,15 +5078,15 @@
       <c r="F74" s="153">
         <v>0.42799999999999999</v>
       </c>
-      <c r="G74" s="207">
+      <c r="G74" s="199">
         <f>E74*0.428</f>
         <v>22007.759999999998</v>
       </c>
-      <c r="H74" s="208"/>
-      <c r="I74" s="209">
+      <c r="H74" s="200"/>
+      <c r="I74" s="201">
         <v>22</v>
       </c>
-      <c r="J74" s="210"/>
+      <c r="J74" s="202"/>
       <c r="K74" s="111"/>
       <c r="L74" s="70">
         <v>9390</v>
@@ -5108,11 +5102,11 @@
       <c r="U74" s="70"/>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A75" s="204" t="s">
+      <c r="A75" s="196" t="s">
         <v>55</v>
       </c>
-      <c r="B75" s="205"/>
-      <c r="C75" s="206"/>
+      <c r="B75" s="197"/>
+      <c r="C75" s="198"/>
       <c r="D75" s="84"/>
       <c r="E75" s="84">
         <v>38070</v>
@@ -5120,15 +5114,15 @@
       <c r="F75" s="153">
         <v>0.33100000000000002</v>
       </c>
-      <c r="G75" s="207">
+      <c r="G75" s="199">
         <f>E75*0.331</f>
         <v>12601.17</v>
       </c>
-      <c r="H75" s="208"/>
-      <c r="I75" s="209">
+      <c r="H75" s="200"/>
+      <c r="I75" s="201">
         <v>12</v>
       </c>
-      <c r="J75" s="210"/>
+      <c r="J75" s="202"/>
       <c r="K75" s="111"/>
       <c r="L75" s="70">
         <v>12480</v>
@@ -5144,11 +5138,11 @@
       <c r="U75" s="70"/>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A76" s="204" t="s">
+      <c r="A76" s="196" t="s">
         <v>56</v>
       </c>
-      <c r="B76" s="205"/>
-      <c r="C76" s="206"/>
+      <c r="B76" s="197"/>
+      <c r="C76" s="198"/>
       <c r="D76" s="84"/>
       <c r="E76" s="84">
         <v>42100</v>
@@ -5156,15 +5150,15 @@
       <c r="F76" s="153">
         <v>0.36899999999999999</v>
       </c>
-      <c r="G76" s="207">
+      <c r="G76" s="199">
         <f>E76*0.369</f>
         <v>15534.9</v>
       </c>
-      <c r="H76" s="208"/>
-      <c r="I76" s="209">
+      <c r="H76" s="200"/>
+      <c r="I76" s="201">
         <v>15</v>
       </c>
-      <c r="J76" s="210"/>
+      <c r="J76" s="202"/>
       <c r="K76" s="111"/>
       <c r="L76" s="70">
         <v>13240</v>
@@ -5180,11 +5174,11 @@
       <c r="U76" s="70"/>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A77" s="204" t="s">
+      <c r="A77" s="196" t="s">
         <v>61</v>
       </c>
-      <c r="B77" s="205"/>
-      <c r="C77" s="206"/>
+      <c r="B77" s="197"/>
+      <c r="C77" s="198"/>
       <c r="D77" s="84"/>
       <c r="E77" s="84">
         <v>64570</v>
@@ -5192,15 +5186,15 @@
       <c r="F77" s="153">
         <v>0.48</v>
       </c>
-      <c r="G77" s="207">
+      <c r="G77" s="199">
         <f>E77*0.48</f>
         <v>30993.599999999999</v>
       </c>
-      <c r="H77" s="208"/>
-      <c r="I77" s="211">
+      <c r="H77" s="200"/>
+      <c r="I77" s="222">
         <v>31</v>
       </c>
-      <c r="J77" s="212"/>
+      <c r="J77" s="223"/>
       <c r="K77" s="111"/>
       <c r="L77" s="70"/>
       <c r="M77" s="70"/>
@@ -5226,15 +5220,15 @@
       <c r="F78" s="153">
         <v>0.43</v>
       </c>
-      <c r="G78" s="207">
+      <c r="G78" s="199">
         <f>E78*0.43</f>
         <v>34903.1</v>
       </c>
-      <c r="H78" s="208"/>
-      <c r="I78" s="211">
+      <c r="H78" s="200"/>
+      <c r="I78" s="222">
         <v>35</v>
       </c>
-      <c r="J78" s="212"/>
+      <c r="J78" s="223"/>
       <c r="K78" s="111"/>
       <c r="L78" s="70"/>
       <c r="M78" s="70"/>
@@ -5248,11 +5242,11 @@
       <c r="U78" s="70"/>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A79" s="213" t="s">
+      <c r="A79" s="212" t="s">
         <v>29</v>
       </c>
-      <c r="B79" s="214"/>
-      <c r="C79" s="215"/>
+      <c r="B79" s="213"/>
+      <c r="C79" s="214"/>
       <c r="D79" s="50">
         <f>SUM(D74:D78)</f>
         <v>0</v>
@@ -5262,16 +5256,16 @@
         <v>277330</v>
       </c>
       <c r="F79" s="60"/>
-      <c r="G79" s="216">
+      <c r="G79" s="215">
         <f>SUM(G74:G78)</f>
         <v>116040.53</v>
       </c>
-      <c r="H79" s="217"/>
-      <c r="I79" s="213">
+      <c r="H79" s="216"/>
+      <c r="I79" s="212">
         <f>SUM(I74:I78)</f>
         <v>115</v>
       </c>
-      <c r="J79" s="215"/>
+      <c r="J79" s="214"/>
       <c r="L79">
         <f>SUM(L74:L78)</f>
         <v>35110</v>
@@ -5321,7 +5315,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2485C30B-60FE-4803-A34A-FC87DD6C3347}">
   <sheetPr codeName="Foglio4"/>
-  <dimension ref="A1:U119"/>
+  <dimension ref="A1:U141"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
@@ -5342,26 +5336,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="196" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="196"/>
-      <c r="C1" s="196"/>
+      <c r="A1" s="203" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="203"/>
+      <c r="C1" s="203"/>
       <c r="D1" s="1">
-        <v>46231</v>
+        <v>46280</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="197" t="s">
+      <c r="G1" s="217" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="198"/>
-      <c r="I1" s="198"/>
-      <c r="J1" s="198"/>
-      <c r="K1" s="198"/>
-      <c r="L1" s="198"/>
-      <c r="M1" s="198"/>
-      <c r="N1" s="201"/>
+      <c r="H1" s="218"/>
+      <c r="I1" s="218"/>
+      <c r="J1" s="218"/>
+      <c r="K1" s="218"/>
+      <c r="L1" s="218"/>
+      <c r="M1" s="218"/>
+      <c r="N1" s="219"/>
     </row>
     <row r="2" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
@@ -5923,7 +5917,7 @@
       </c>
       <c r="I17" s="70"/>
       <c r="J17" s="76">
-        <f t="shared" ref="J17:J35" si="1">F17-G17</f>
+        <f t="shared" ref="J17:J46" si="1">F17-G17</f>
         <v>0</v>
       </c>
       <c r="K17" s="195" t="s">
@@ -5931,9 +5925,7 @@
       </c>
       <c r="L17" s="63"/>
       <c r="M17" s="140"/>
-      <c r="N17" s="165">
-        <v>1000</v>
-      </c>
+      <c r="N17" s="165"/>
       <c r="O17" s="95"/>
       <c r="P17" s="18">
         <v>2E-3</v>
@@ -5983,9 +5975,7 @@
       </c>
       <c r="L18" s="63"/>
       <c r="M18" s="140"/>
-      <c r="N18" s="165">
-        <v>1000</v>
-      </c>
+      <c r="N18" s="165"/>
       <c r="O18" s="95"/>
       <c r="P18" s="18">
         <v>1E-3</v>
@@ -6085,9 +6075,7 @@
       </c>
       <c r="L20" s="63"/>
       <c r="M20" s="140"/>
-      <c r="N20" s="165">
-        <v>1000</v>
-      </c>
+      <c r="N20" s="165"/>
       <c r="O20" s="95"/>
       <c r="P20" s="18">
         <v>0</v>
@@ -6137,9 +6125,7 @@
       </c>
       <c r="L21" s="63"/>
       <c r="M21" s="140"/>
-      <c r="N21" s="165">
-        <v>1000</v>
-      </c>
+      <c r="N21" s="165"/>
       <c r="O21" s="95"/>
       <c r="P21" s="18">
         <v>2E-3</v>
@@ -6239,9 +6225,7 @@
       </c>
       <c r="L23" s="63"/>
       <c r="M23" s="140"/>
-      <c r="N23" s="165">
-        <v>1000</v>
-      </c>
+      <c r="N23" s="165"/>
       <c r="O23" s="95"/>
       <c r="P23" s="18">
         <v>2E-3</v>
@@ -6341,9 +6325,7 @@
       </c>
       <c r="L25" s="63"/>
       <c r="M25" s="140"/>
-      <c r="N25" s="165">
-        <v>1000</v>
-      </c>
+      <c r="N25" s="165"/>
       <c r="O25" s="95"/>
       <c r="P25" s="18">
         <v>2E-3</v>
@@ -6593,9 +6575,7 @@
       </c>
       <c r="L30" s="63"/>
       <c r="M30" s="140"/>
-      <c r="N30" s="165">
-        <v>1000</v>
-      </c>
+      <c r="N30" s="165"/>
       <c r="O30" s="95"/>
       <c r="P30" s="18">
         <v>2E-3</v>
@@ -6645,9 +6625,7 @@
       </c>
       <c r="L31" s="63"/>
       <c r="M31" s="140"/>
-      <c r="N31" s="165">
-        <v>1000</v>
-      </c>
+      <c r="N31" s="165"/>
       <c r="O31" s="95"/>
       <c r="P31" s="18">
         <v>0</v>
@@ -6697,9 +6675,7 @@
       </c>
       <c r="L32" s="63"/>
       <c r="M32" s="140"/>
-      <c r="N32" s="165">
-        <v>1000</v>
-      </c>
+      <c r="N32" s="165"/>
       <c r="O32" s="95"/>
       <c r="P32" s="18">
         <v>1E-3</v>
@@ -6749,9 +6725,7 @@
       </c>
       <c r="L33" s="63"/>
       <c r="M33" s="140"/>
-      <c r="N33" s="165">
-        <v>1000</v>
-      </c>
+      <c r="N33" s="165"/>
       <c r="O33" s="95"/>
       <c r="P33" s="18">
         <v>1E-3</v>
@@ -6822,11 +6796,8 @@
       <c r="G35" s="70"/>
       <c r="H35" s="70"/>
       <c r="I35" s="70"/>
-      <c r="J35" s="76">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K35" s="72"/>
+      <c r="J35" s="76"/>
+      <c r="K35" s="195"/>
       <c r="L35" s="63"/>
       <c r="M35" s="140"/>
       <c r="N35" s="165"/>
@@ -6839,793 +6810,722 @@
       <c r="U35" s="119"/>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A36" s="114"/>
-      <c r="B36" s="78"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36" s="32"/>
-      <c r="F36" s="104"/>
-      <c r="G36" s="104"/>
-      <c r="H36" s="104"/>
-      <c r="I36" s="104"/>
-      <c r="J36" s="104"/>
-      <c r="K36" s="33"/>
-      <c r="L36" s="27"/>
+      <c r="A36" s="108" t="s">
+        <v>304</v>
+      </c>
+      <c r="B36" s="79" t="s">
+        <v>305</v>
+      </c>
+      <c r="C36" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E36" s="72" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" s="167">
+        <v>1000</v>
+      </c>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70" t="s">
+        <v>306</v>
+      </c>
+      <c r="I36" s="70"/>
+      <c r="J36" s="76">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="K36" s="195" t="s">
+        <v>63</v>
+      </c>
+      <c r="L36" s="63"/>
       <c r="M36" s="140"/>
-      <c r="N36" s="103"/>
+      <c r="N36" s="165">
+        <v>1000</v>
+      </c>
       <c r="O36" s="95"/>
-      <c r="P36" s="18"/>
-      <c r="Q36" s="18"/>
-      <c r="R36" s="18"/>
-      <c r="S36" s="18"/>
-      <c r="T36" s="26"/>
+      <c r="P36" s="18">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="Q36" s="18">
+        <v>4.6600000000000003E-2</v>
+      </c>
+      <c r="R36" s="18">
+        <v>9.3299999999999994E-2</v>
+      </c>
+      <c r="S36" s="18">
+        <v>0</v>
+      </c>
+      <c r="T36" s="26">
+        <v>0</v>
+      </c>
       <c r="U36" s="119"/>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" s="114"/>
-      <c r="B37" s="78"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="104"/>
-      <c r="G37" s="104"/>
-      <c r="H37" s="104"/>
-      <c r="I37" s="104"/>
-      <c r="J37" s="104"/>
-      <c r="K37" s="33"/>
-      <c r="L37" s="27"/>
+      <c r="A37" s="108" t="s">
+        <v>304</v>
+      </c>
+      <c r="B37" s="79" t="s">
+        <v>305</v>
+      </c>
+      <c r="C37" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E37" s="72" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="167">
+        <v>1000</v>
+      </c>
+      <c r="G37" s="70"/>
+      <c r="H37" s="70" t="s">
+        <v>306</v>
+      </c>
+      <c r="I37" s="70"/>
+      <c r="J37" s="76">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="K37" s="195" t="s">
+        <v>64</v>
+      </c>
+      <c r="L37" s="63"/>
       <c r="M37" s="140"/>
-      <c r="N37" s="103"/>
+      <c r="N37" s="165">
+        <v>1000</v>
+      </c>
       <c r="O37" s="95"/>
-      <c r="P37" s="18"/>
-      <c r="Q37" s="18"/>
-      <c r="R37" s="18"/>
-      <c r="S37" s="18"/>
-      <c r="T37" s="26"/>
+      <c r="P37" s="18">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="Q37" s="18">
+        <v>4.6600000000000003E-2</v>
+      </c>
+      <c r="R37" s="18">
+        <v>9.3299999999999994E-2</v>
+      </c>
+      <c r="S37" s="18">
+        <v>0</v>
+      </c>
+      <c r="T37" s="26">
+        <v>0</v>
+      </c>
       <c r="U37" s="119"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A38" s="114"/>
-      <c r="B38" s="78"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="E38" s="32"/>
-      <c r="F38" s="104"/>
-      <c r="G38" s="104">
-        <v>0</v>
-      </c>
-      <c r="H38" s="104"/>
-      <c r="I38" s="104" t="s">
-        <v>100</v>
-      </c>
-      <c r="J38" s="104"/>
-      <c r="K38" s="33"/>
-      <c r="L38" s="27"/>
+      <c r="A38" s="108" t="s">
+        <v>304</v>
+      </c>
+      <c r="B38" s="79" t="s">
+        <v>305</v>
+      </c>
+      <c r="C38" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="D38" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E38" s="72" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38" s="167">
+        <v>877</v>
+      </c>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70" t="s">
+        <v>306</v>
+      </c>
+      <c r="I38" s="70"/>
+      <c r="J38" s="76">
+        <f t="shared" si="1"/>
+        <v>877</v>
+      </c>
+      <c r="K38" s="195" t="s">
+        <v>68</v>
+      </c>
+      <c r="L38" s="63"/>
       <c r="M38" s="140"/>
-      <c r="N38" s="103"/>
+      <c r="N38" s="165">
+        <v>877</v>
+      </c>
       <c r="O38" s="95"/>
-      <c r="P38" s="18"/>
-      <c r="Q38" s="18"/>
-      <c r="R38" s="18"/>
-      <c r="S38" s="18"/>
-      <c r="T38" s="26"/>
+      <c r="P38" s="18">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="Q38" s="18">
+        <v>4.6600000000000003E-2</v>
+      </c>
+      <c r="R38" s="18">
+        <v>9.3299999999999994E-2</v>
+      </c>
+      <c r="S38" s="18">
+        <v>0</v>
+      </c>
+      <c r="T38" s="26">
+        <v>0</v>
+      </c>
       <c r="U38" s="119"/>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A39" s="114"/>
-      <c r="B39" s="78"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="E39" s="32"/>
-      <c r="F39" s="104"/>
-      <c r="G39" s="104">
-        <v>0</v>
-      </c>
-      <c r="H39" s="104"/>
-      <c r="I39" s="104" t="s">
-        <v>100</v>
-      </c>
-      <c r="J39" s="104"/>
-      <c r="K39" s="33"/>
-      <c r="L39" s="27"/>
+      <c r="A39" s="108" t="s">
+        <v>304</v>
+      </c>
+      <c r="B39" s="79" t="s">
+        <v>305</v>
+      </c>
+      <c r="C39" s="79" t="s">
+        <v>53</v>
+      </c>
+      <c r="D39" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E39" s="72" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" s="167">
+        <v>1000</v>
+      </c>
+      <c r="G39" s="70"/>
+      <c r="H39" s="70" t="s">
+        <v>306</v>
+      </c>
+      <c r="I39" s="70"/>
+      <c r="J39" s="76">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="K39" s="195" t="s">
+        <v>63</v>
+      </c>
+      <c r="L39" s="63"/>
       <c r="M39" s="140"/>
-      <c r="N39" s="103"/>
+      <c r="N39" s="165">
+        <v>1000</v>
+      </c>
       <c r="O39" s="95"/>
-      <c r="P39" s="18"/>
-      <c r="Q39" s="18"/>
-      <c r="R39" s="18"/>
-      <c r="S39" s="18"/>
-      <c r="T39" s="26"/>
+      <c r="P39" s="18">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="Q39" s="18">
+        <v>4.6600000000000003E-2</v>
+      </c>
+      <c r="R39" s="18">
+        <v>9.3299999999999994E-2</v>
+      </c>
+      <c r="S39" s="18">
+        <v>0</v>
+      </c>
+      <c r="T39" s="26">
+        <v>0</v>
+      </c>
       <c r="U39" s="119"/>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A40" s="114"/>
-      <c r="B40" s="78"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="31" t="s">
-        <v>157</v>
-      </c>
-      <c r="E40" s="32"/>
-      <c r="F40" s="104"/>
-      <c r="G40" s="104">
-        <v>0</v>
-      </c>
-      <c r="H40" s="104"/>
-      <c r="I40" s="104" t="s">
-        <v>100</v>
-      </c>
-      <c r="J40" s="104"/>
-      <c r="K40" s="33"/>
-      <c r="L40" s="27"/>
+      <c r="A40" s="108" t="s">
+        <v>304</v>
+      </c>
+      <c r="B40" s="79" t="s">
+        <v>305</v>
+      </c>
+      <c r="C40" s="79" t="s">
+        <v>53</v>
+      </c>
+      <c r="D40" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E40" s="72" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" s="167">
+        <v>1000</v>
+      </c>
+      <c r="G40" s="70"/>
+      <c r="H40" s="70" t="s">
+        <v>306</v>
+      </c>
+      <c r="I40" s="70"/>
+      <c r="J40" s="76">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="K40" s="195" t="s">
+        <v>64</v>
+      </c>
+      <c r="L40" s="63"/>
       <c r="M40" s="140"/>
-      <c r="N40" s="103"/>
+      <c r="N40" s="165">
+        <v>1000</v>
+      </c>
       <c r="O40" s="95"/>
-      <c r="P40" s="18"/>
-      <c r="Q40" s="18"/>
-      <c r="R40" s="18"/>
-      <c r="S40" s="18"/>
-      <c r="T40" s="26"/>
+      <c r="P40" s="18">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="Q40" s="18">
+        <v>4.6600000000000003E-2</v>
+      </c>
+      <c r="R40" s="18">
+        <v>9.3299999999999994E-2</v>
+      </c>
+      <c r="S40" s="18">
+        <v>0</v>
+      </c>
+      <c r="T40" s="26">
+        <v>0</v>
+      </c>
       <c r="U40" s="119"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A41" s="114"/>
-      <c r="B41" s="78"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="31" t="s">
-        <v>180</v>
-      </c>
-      <c r="E41" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="F41" s="104"/>
-      <c r="G41" s="104"/>
-      <c r="H41" s="104"/>
-      <c r="I41" s="104"/>
-      <c r="J41" s="104"/>
-      <c r="K41" s="33"/>
-      <c r="L41" s="27"/>
+      <c r="A41" s="108" t="s">
+        <v>304</v>
+      </c>
+      <c r="B41" s="79" t="s">
+        <v>305</v>
+      </c>
+      <c r="C41" s="79" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E41" s="72" t="s">
+        <v>17</v>
+      </c>
+      <c r="F41" s="167">
+        <v>1000</v>
+      </c>
+      <c r="G41" s="70"/>
+      <c r="H41" s="70" t="s">
+        <v>306</v>
+      </c>
+      <c r="I41" s="70"/>
+      <c r="J41" s="76">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="K41" s="195" t="s">
+        <v>68</v>
+      </c>
+      <c r="L41" s="63"/>
       <c r="M41" s="140"/>
-      <c r="N41" s="103"/>
+      <c r="N41" s="165">
+        <v>1000</v>
+      </c>
       <c r="O41" s="95"/>
-      <c r="P41" s="18"/>
-      <c r="Q41" s="18"/>
-      <c r="R41" s="18"/>
-      <c r="S41" s="18"/>
-      <c r="T41" s="26"/>
+      <c r="P41" s="18">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="Q41" s="18">
+        <v>4.6600000000000003E-2</v>
+      </c>
+      <c r="R41" s="18">
+        <v>9.3299999999999994E-2</v>
+      </c>
+      <c r="S41" s="18">
+        <v>0</v>
+      </c>
+      <c r="T41" s="26">
+        <v>0</v>
+      </c>
       <c r="U41" s="119"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" s="114"/>
-      <c r="B42" s="78"/>
-      <c r="C42" s="78"/>
-      <c r="D42" s="121"/>
-      <c r="E42" s="83"/>
-      <c r="F42" s="104"/>
-      <c r="G42" s="104"/>
-      <c r="H42" s="110"/>
-      <c r="I42" s="105"/>
-      <c r="J42" s="104"/>
-      <c r="K42" s="33"/>
-      <c r="L42" s="27"/>
+      <c r="A42" s="108" t="s">
+        <v>304</v>
+      </c>
+      <c r="B42" s="79" t="s">
+        <v>305</v>
+      </c>
+      <c r="C42" s="79" t="s">
+        <v>53</v>
+      </c>
+      <c r="D42" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E42" s="72" t="s">
+        <v>17</v>
+      </c>
+      <c r="F42" s="167">
+        <v>859</v>
+      </c>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70" t="s">
+        <v>306</v>
+      </c>
+      <c r="I42" s="70"/>
+      <c r="J42" s="76">
+        <f t="shared" si="1"/>
+        <v>859</v>
+      </c>
+      <c r="K42" s="195" t="s">
+        <v>69</v>
+      </c>
+      <c r="L42" s="63"/>
       <c r="M42" s="140"/>
-      <c r="N42" s="103"/>
+      <c r="N42" s="165">
+        <v>859</v>
+      </c>
       <c r="O42" s="95"/>
-      <c r="P42" s="18"/>
-      <c r="Q42" s="18"/>
-      <c r="R42" s="18"/>
-      <c r="S42" s="18"/>
-      <c r="T42" s="26"/>
+      <c r="P42" s="18">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="Q42" s="18">
+        <v>4.6600000000000003E-2</v>
+      </c>
+      <c r="R42" s="18">
+        <v>9.3299999999999994E-2</v>
+      </c>
+      <c r="S42" s="18">
+        <v>0</v>
+      </c>
+      <c r="T42" s="26">
+        <v>0</v>
+      </c>
       <c r="U42" s="119"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="70"/>
+      <c r="A43" s="108"/>
       <c r="B43" s="79"/>
       <c r="C43" s="79"/>
-      <c r="D43" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E43" s="51" t="s">
-        <v>17</v>
-      </c>
-      <c r="F43" s="23">
-        <f>SUM(F17:F36)</f>
-        <v>962</v>
-      </c>
-      <c r="G43" s="23">
-        <f>SUM(G17:G42)</f>
-        <v>0</v>
-      </c>
-      <c r="H43" s="23"/>
-      <c r="I43" s="23"/>
-      <c r="J43" s="23">
-        <f>F43-G43</f>
-        <v>962</v>
-      </c>
-      <c r="K43" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="L43" s="25">
-        <f>SUM(L17:L35)</f>
-        <v>0</v>
-      </c>
-      <c r="M43" s="25">
-        <f>SUM(M17:M35)</f>
-        <v>0</v>
-      </c>
-      <c r="N43" s="25">
-        <f>SUM(N17:N36)</f>
-        <v>10962</v>
-      </c>
-      <c r="O43" s="25">
-        <f>SUM(O17:O35)</f>
-        <v>0</v>
-      </c>
-      <c r="P43" s="26"/>
-      <c r="Q43" s="26"/>
-      <c r="R43" s="26"/>
-      <c r="S43" s="26"/>
+      <c r="D43" s="72"/>
+      <c r="E43" s="72"/>
+      <c r="F43" s="167"/>
+      <c r="G43" s="70"/>
+      <c r="H43" s="70"/>
+      <c r="I43" s="70"/>
+      <c r="J43" s="76"/>
+      <c r="K43" s="195"/>
+      <c r="L43" s="63"/>
+      <c r="M43" s="140"/>
+      <c r="N43" s="165"/>
+      <c r="O43" s="95"/>
+      <c r="P43" s="18"/>
+      <c r="Q43" s="18"/>
+      <c r="R43" s="18"/>
+      <c r="S43" s="18"/>
       <c r="T43" s="26"/>
       <c r="U43" s="119"/>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A44" s="108" t="s">
-        <v>159</v>
-      </c>
-      <c r="B44" s="79" t="s">
-        <v>97</v>
-      </c>
-      <c r="C44" s="79" t="s">
-        <v>52</v>
-      </c>
-      <c r="D44" s="72" t="s">
-        <v>98</v>
-      </c>
-      <c r="E44" s="93" t="s">
-        <v>19</v>
-      </c>
-      <c r="F44" s="58"/>
+      <c r="A44" s="108"/>
+      <c r="B44" s="79"/>
+      <c r="C44" s="79"/>
+      <c r="D44" s="72"/>
+      <c r="E44" s="72"/>
+      <c r="F44" s="167"/>
       <c r="G44" s="70"/>
       <c r="H44" s="70"/>
       <c r="I44" s="70"/>
-      <c r="J44" s="70">
-        <f t="shared" ref="J44:J69" si="2">F44-G44</f>
-        <v>0</v>
-      </c>
-      <c r="K44" s="72" t="s">
-        <v>120</v>
-      </c>
+      <c r="J44" s="76"/>
+      <c r="K44" s="195"/>
       <c r="L44" s="63"/>
-      <c r="M44" s="65"/>
-      <c r="N44" s="66"/>
+      <c r="M44" s="140"/>
+      <c r="N44" s="165"/>
       <c r="O44" s="95"/>
-      <c r="P44" s="18">
-        <v>2E-3</v>
-      </c>
-      <c r="Q44" s="18">
-        <v>0.04</v>
-      </c>
-      <c r="R44" s="18">
-        <v>0.12330000000000001</v>
-      </c>
-      <c r="S44" s="18">
-        <v>0</v>
-      </c>
-      <c r="T44" s="26">
-        <v>0</v>
-      </c>
+      <c r="P44" s="18"/>
+      <c r="Q44" s="18"/>
+      <c r="R44" s="18"/>
+      <c r="S44" s="18"/>
+      <c r="T44" s="26"/>
       <c r="U44" s="119"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A45" s="108" t="s">
-        <v>159</v>
-      </c>
-      <c r="B45" s="79" t="s">
-        <v>97</v>
-      </c>
-      <c r="C45" s="79" t="s">
-        <v>52</v>
-      </c>
-      <c r="D45" s="72" t="s">
-        <v>98</v>
-      </c>
-      <c r="E45" s="93" t="s">
-        <v>19</v>
-      </c>
-      <c r="F45" s="58"/>
+      <c r="A45" s="108"/>
+      <c r="B45" s="79"/>
+      <c r="C45" s="79"/>
+      <c r="D45" s="72"/>
+      <c r="E45" s="72"/>
+      <c r="F45" s="167"/>
       <c r="G45" s="70"/>
       <c r="H45" s="70"/>
       <c r="I45" s="70"/>
-      <c r="J45" s="70">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K45" s="72" t="s">
-        <v>124</v>
-      </c>
+      <c r="J45" s="76"/>
+      <c r="K45" s="195"/>
       <c r="L45" s="63"/>
-      <c r="M45" s="65"/>
-      <c r="N45" s="66"/>
+      <c r="M45" s="140"/>
+      <c r="N45" s="165"/>
       <c r="O45" s="95"/>
-      <c r="P45" s="18">
-        <v>1E-3</v>
-      </c>
-      <c r="Q45" s="18">
-        <v>0.04</v>
-      </c>
-      <c r="R45" s="18">
-        <v>0.1633</v>
-      </c>
-      <c r="S45" s="18">
-        <v>0</v>
-      </c>
-      <c r="T45" s="26">
-        <v>0</v>
-      </c>
+      <c r="P45" s="18"/>
+      <c r="Q45" s="18"/>
+      <c r="R45" s="18"/>
+      <c r="S45" s="18"/>
+      <c r="T45" s="26"/>
       <c r="U45" s="119"/>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A46" s="108" t="s">
-        <v>164</v>
-      </c>
-      <c r="B46" s="79" t="s">
-        <v>97</v>
-      </c>
-      <c r="C46" s="79" t="s">
-        <v>53</v>
-      </c>
-      <c r="D46" s="72" t="s">
-        <v>98</v>
-      </c>
-      <c r="E46" s="93" t="s">
-        <v>19</v>
-      </c>
-      <c r="F46" s="58"/>
+      <c r="A46" s="108"/>
+      <c r="B46" s="79"/>
+      <c r="C46" s="79"/>
+      <c r="D46" s="72"/>
+      <c r="E46" s="72"/>
+      <c r="F46" s="167"/>
       <c r="G46" s="70"/>
-      <c r="H46" s="70" t="s">
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="76">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="72"/>
+      <c r="L46" s="63"/>
+      <c r="M46" s="140"/>
+      <c r="N46" s="165"/>
+      <c r="O46" s="95"/>
+      <c r="P46" s="18"/>
+      <c r="Q46" s="18"/>
+      <c r="R46" s="18"/>
+      <c r="S46" s="18"/>
+      <c r="T46" s="26"/>
+      <c r="U46" s="119"/>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A47" s="114"/>
+      <c r="B47" s="78"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47" s="32"/>
+      <c r="F47" s="104"/>
+      <c r="G47" s="104"/>
+      <c r="H47" s="104"/>
+      <c r="I47" s="104"/>
+      <c r="J47" s="104"/>
+      <c r="K47" s="33"/>
+      <c r="L47" s="27"/>
+      <c r="M47" s="140"/>
+      <c r="N47" s="103"/>
+      <c r="O47" s="95"/>
+      <c r="P47" s="18"/>
+      <c r="Q47" s="18"/>
+      <c r="R47" s="18"/>
+      <c r="S47" s="18"/>
+      <c r="T47" s="26"/>
+      <c r="U47" s="119"/>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A48" s="114"/>
+      <c r="B48" s="78"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="104"/>
+      <c r="G48" s="104"/>
+      <c r="H48" s="104"/>
+      <c r="I48" s="104"/>
+      <c r="J48" s="104"/>
+      <c r="K48" s="33"/>
+      <c r="L48" s="27"/>
+      <c r="M48" s="140"/>
+      <c r="N48" s="103"/>
+      <c r="O48" s="95"/>
+      <c r="P48" s="18"/>
+      <c r="Q48" s="18"/>
+      <c r="R48" s="18"/>
+      <c r="S48" s="18"/>
+      <c r="T48" s="26"/>
+      <c r="U48" s="119"/>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A49" s="114"/>
+      <c r="B49" s="78"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="E49" s="32"/>
+      <c r="F49" s="104"/>
+      <c r="G49" s="104">
+        <v>0</v>
+      </c>
+      <c r="H49" s="104"/>
+      <c r="I49" s="104" t="s">
+        <v>100</v>
+      </c>
+      <c r="J49" s="104"/>
+      <c r="K49" s="33"/>
+      <c r="L49" s="27"/>
+      <c r="M49" s="140"/>
+      <c r="N49" s="103"/>
+      <c r="O49" s="95"/>
+      <c r="P49" s="18"/>
+      <c r="Q49" s="18"/>
+      <c r="R49" s="18"/>
+      <c r="S49" s="18"/>
+      <c r="T49" s="26"/>
+      <c r="U49" s="119"/>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A50" s="114"/>
+      <c r="B50" s="78"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="E50" s="32"/>
+      <c r="F50" s="104"/>
+      <c r="G50" s="104">
+        <v>0</v>
+      </c>
+      <c r="H50" s="104"/>
+      <c r="I50" s="104" t="s">
+        <v>100</v>
+      </c>
+      <c r="J50" s="104"/>
+      <c r="K50" s="33"/>
+      <c r="L50" s="27"/>
+      <c r="M50" s="140"/>
+      <c r="N50" s="103"/>
+      <c r="O50" s="95"/>
+      <c r="P50" s="18"/>
+      <c r="Q50" s="18"/>
+      <c r="R50" s="18"/>
+      <c r="S50" s="18"/>
+      <c r="T50" s="26"/>
+      <c r="U50" s="119"/>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A51" s="114"/>
+      <c r="B51" s="78"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="E51" s="32"/>
+      <c r="F51" s="104"/>
+      <c r="G51" s="104">
+        <v>0</v>
+      </c>
+      <c r="H51" s="104"/>
+      <c r="I51" s="104" t="s">
+        <v>100</v>
+      </c>
+      <c r="J51" s="104"/>
+      <c r="K51" s="33"/>
+      <c r="L51" s="27"/>
+      <c r="M51" s="140"/>
+      <c r="N51" s="103"/>
+      <c r="O51" s="95"/>
+      <c r="P51" s="18"/>
+      <c r="Q51" s="18"/>
+      <c r="R51" s="18"/>
+      <c r="S51" s="18"/>
+      <c r="T51" s="26"/>
+      <c r="U51" s="119"/>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A52" s="114"/>
+      <c r="B52" s="78"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="I46" s="70"/>
-      <c r="J46" s="70">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K46" s="195" t="s">
-        <v>63</v>
-      </c>
-      <c r="L46" s="63"/>
-      <c r="M46" s="65"/>
-      <c r="N46" s="66">
-        <v>1000</v>
-      </c>
-      <c r="O46" s="95"/>
-      <c r="P46" s="18">
-        <v>2E-3</v>
-      </c>
-      <c r="Q46" s="18">
-        <v>0.03</v>
-      </c>
-      <c r="R46" s="18">
-        <v>0.12659999999999999</v>
-      </c>
-      <c r="S46" s="18">
-        <v>0</v>
-      </c>
-      <c r="T46" s="26">
-        <v>0</v>
-      </c>
-      <c r="U46" s="119"/>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="108" t="s">
-        <v>164</v>
-      </c>
-      <c r="B47" s="79" t="s">
-        <v>97</v>
-      </c>
-      <c r="C47" s="79" t="s">
-        <v>53</v>
-      </c>
-      <c r="D47" s="72" t="s">
-        <v>98</v>
-      </c>
-      <c r="E47" s="93" t="s">
-        <v>19</v>
-      </c>
-      <c r="F47" s="58"/>
-      <c r="G47" s="70"/>
-      <c r="H47" s="70"/>
-      <c r="I47" s="70"/>
-      <c r="J47" s="70">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K47" s="72" t="s">
-        <v>64</v>
-      </c>
-      <c r="L47" s="63"/>
-      <c r="M47" s="65"/>
-      <c r="N47" s="66"/>
-      <c r="O47" s="95"/>
-      <c r="P47" s="18">
-        <v>1E-3</v>
-      </c>
-      <c r="Q47" s="18">
-        <v>2.6599999999999999E-2</v>
-      </c>
-      <c r="R47" s="18">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="S47" s="18">
-        <v>0</v>
-      </c>
-      <c r="T47" s="26">
-        <v>0</v>
-      </c>
-      <c r="U47" s="119"/>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A48" s="108" t="s">
-        <v>164</v>
-      </c>
-      <c r="B48" s="79" t="s">
-        <v>97</v>
-      </c>
-      <c r="C48" s="79" t="s">
-        <v>53</v>
-      </c>
-      <c r="D48" s="72" t="s">
-        <v>98</v>
-      </c>
-      <c r="E48" s="93" t="s">
-        <v>19</v>
-      </c>
-      <c r="F48" s="58"/>
-      <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
-      <c r="I48" s="70"/>
-      <c r="J48" s="70">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K48" s="72" t="s">
-        <v>68</v>
-      </c>
-      <c r="L48" s="63"/>
-      <c r="M48" s="65"/>
-      <c r="N48" s="66"/>
-      <c r="O48" s="95"/>
-      <c r="P48" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="18">
-        <v>0.05</v>
-      </c>
-      <c r="R48" s="18">
-        <v>0.1166</v>
-      </c>
-      <c r="S48" s="18">
-        <v>0</v>
-      </c>
-      <c r="T48" s="26">
-        <v>0</v>
-      </c>
-      <c r="U48" s="119"/>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A49" s="108" t="s">
-        <v>164</v>
-      </c>
-      <c r="B49" s="79" t="s">
-        <v>97</v>
-      </c>
-      <c r="C49" s="79" t="s">
-        <v>53</v>
-      </c>
-      <c r="D49" s="72" t="s">
-        <v>98</v>
-      </c>
-      <c r="E49" s="93" t="s">
-        <v>19</v>
-      </c>
-      <c r="F49" s="58"/>
-      <c r="G49" s="70"/>
-      <c r="H49" s="70" t="s">
-        <v>180</v>
-      </c>
-      <c r="I49" s="70"/>
-      <c r="J49" s="70">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K49" s="195" t="s">
-        <v>69</v>
-      </c>
-      <c r="L49" s="63"/>
-      <c r="M49" s="65"/>
-      <c r="N49" s="66">
-        <v>1000</v>
-      </c>
-      <c r="O49" s="95"/>
-      <c r="P49" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="18">
-        <v>0.03</v>
-      </c>
-      <c r="R49" s="18">
-        <v>0.1166</v>
-      </c>
-      <c r="S49" s="18">
-        <v>0</v>
-      </c>
-      <c r="T49" s="26">
-        <v>0</v>
-      </c>
-      <c r="U49" s="119"/>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A50" s="108" t="s">
-        <v>164</v>
-      </c>
-      <c r="B50" s="79" t="s">
-        <v>97</v>
-      </c>
-      <c r="C50" s="79" t="s">
-        <v>53</v>
-      </c>
-      <c r="D50" s="72" t="s">
-        <v>98</v>
-      </c>
-      <c r="E50" s="93" t="s">
-        <v>19</v>
-      </c>
-      <c r="F50" s="58"/>
-      <c r="G50" s="70"/>
-      <c r="H50" s="70"/>
-      <c r="I50" s="70"/>
-      <c r="J50" s="70">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K50" s="72" t="s">
-        <v>70</v>
-      </c>
-      <c r="L50" s="63"/>
-      <c r="M50" s="65"/>
-      <c r="N50" s="66"/>
-      <c r="O50" s="95"/>
-      <c r="P50" s="18">
-        <v>1E-3</v>
-      </c>
-      <c r="Q50" s="18">
-        <v>4.3299999999999998E-2</v>
-      </c>
-      <c r="R50" s="18">
-        <v>0.11</v>
-      </c>
-      <c r="S50" s="18">
-        <v>0</v>
-      </c>
-      <c r="T50" s="26">
-        <v>0</v>
-      </c>
-      <c r="U50" s="119"/>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A51" s="108" t="s">
-        <v>164</v>
-      </c>
-      <c r="B51" s="79" t="s">
-        <v>97</v>
-      </c>
-      <c r="C51" s="79" t="s">
-        <v>53</v>
-      </c>
-      <c r="D51" s="72" t="s">
-        <v>98</v>
-      </c>
-      <c r="E51" s="93" t="s">
-        <v>19</v>
-      </c>
-      <c r="F51" s="58"/>
-      <c r="G51" s="70"/>
-      <c r="H51" s="70" t="s">
-        <v>180</v>
-      </c>
-      <c r="I51" s="70"/>
-      <c r="J51" s="70">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K51" s="72" t="s">
-        <v>71</v>
-      </c>
-      <c r="L51" s="63"/>
-      <c r="M51" s="65"/>
-      <c r="N51" s="66"/>
-      <c r="O51" s="95"/>
-      <c r="P51" s="18">
-        <v>1E-3</v>
-      </c>
-      <c r="Q51" s="18">
-        <v>3.6600000000000001E-2</v>
-      </c>
-      <c r="R51" s="18">
-        <v>9.6600000000000005E-2</v>
-      </c>
-      <c r="S51" s="18">
-        <v>0</v>
-      </c>
-      <c r="T51" s="26">
-        <v>0</v>
-      </c>
-      <c r="U51" s="119"/>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A52" s="108" t="s">
-        <v>164</v>
-      </c>
-      <c r="B52" s="79" t="s">
-        <v>97</v>
-      </c>
-      <c r="C52" s="79" t="s">
-        <v>53</v>
-      </c>
-      <c r="D52" s="72" t="s">
-        <v>98</v>
-      </c>
-      <c r="E52" s="93" t="s">
-        <v>19</v>
-      </c>
-      <c r="F52" s="58"/>
-      <c r="G52" s="70"/>
-      <c r="H52" s="70" t="s">
-        <v>180</v>
-      </c>
-      <c r="I52" s="70"/>
-      <c r="J52" s="70">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K52" s="195" t="s">
-        <v>72</v>
-      </c>
-      <c r="L52" s="63"/>
-      <c r="M52" s="65"/>
-      <c r="N52" s="66">
-        <v>1000</v>
-      </c>
+      <c r="E52" s="32" t="s">
+        <v>227</v>
+      </c>
+      <c r="F52" s="104"/>
+      <c r="G52" s="104"/>
+      <c r="H52" s="104"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="104"/>
+      <c r="K52" s="33"/>
+      <c r="L52" s="27"/>
+      <c r="M52" s="140"/>
+      <c r="N52" s="103"/>
       <c r="O52" s="95"/>
-      <c r="P52" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="18">
-        <v>0.02</v>
-      </c>
-      <c r="R52" s="18">
-        <v>0.1033</v>
-      </c>
-      <c r="S52" s="18">
-        <v>0</v>
-      </c>
-      <c r="T52" s="26">
-        <v>0</v>
-      </c>
+      <c r="P52" s="18"/>
+      <c r="Q52" s="18"/>
+      <c r="R52" s="18"/>
+      <c r="S52" s="18"/>
+      <c r="T52" s="26"/>
       <c r="U52" s="119"/>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A53" s="108" t="s">
-        <v>164</v>
-      </c>
-      <c r="B53" s="79" t="s">
-        <v>97</v>
-      </c>
-      <c r="C53" s="79" t="s">
-        <v>53</v>
-      </c>
-      <c r="D53" s="72" t="s">
-        <v>98</v>
-      </c>
-      <c r="E53" s="93" t="s">
-        <v>19</v>
-      </c>
-      <c r="F53" s="58"/>
-      <c r="G53" s="70"/>
-      <c r="H53" s="70"/>
-      <c r="I53" s="70"/>
-      <c r="J53" s="70">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K53" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="L53" s="63"/>
-      <c r="M53" s="65"/>
-      <c r="N53" s="66"/>
+      <c r="A53" s="114"/>
+      <c r="B53" s="78"/>
+      <c r="C53" s="78"/>
+      <c r="D53" s="121"/>
+      <c r="E53" s="83"/>
+      <c r="F53" s="104"/>
+      <c r="G53" s="104"/>
+      <c r="H53" s="110"/>
+      <c r="I53" s="105"/>
+      <c r="J53" s="104"/>
+      <c r="K53" s="33"/>
+      <c r="L53" s="27"/>
+      <c r="M53" s="140"/>
+      <c r="N53" s="103"/>
       <c r="O53" s="95"/>
-      <c r="P53" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="18">
-        <v>0.04</v>
-      </c>
-      <c r="R53" s="18">
-        <v>0.09</v>
-      </c>
-      <c r="S53" s="18">
-        <v>0</v>
-      </c>
-      <c r="T53" s="26">
-        <v>0</v>
-      </c>
+      <c r="P53" s="18"/>
+      <c r="Q53" s="18"/>
+      <c r="R53" s="18"/>
+      <c r="S53" s="18"/>
+      <c r="T53" s="26"/>
       <c r="U53" s="119"/>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A54" s="108" t="s">
-        <v>164</v>
-      </c>
-      <c r="B54" s="79" t="s">
-        <v>97</v>
-      </c>
-      <c r="C54" s="79" t="s">
-        <v>53</v>
-      </c>
-      <c r="D54" s="72" t="s">
-        <v>98</v>
-      </c>
-      <c r="E54" s="93" t="s">
-        <v>19</v>
-      </c>
-      <c r="F54" s="58"/>
-      <c r="G54" s="70"/>
-      <c r="H54" s="70" t="s">
-        <v>278</v>
-      </c>
-      <c r="I54" s="70"/>
-      <c r="J54" s="70">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K54" s="72" t="s">
-        <v>92</v>
-      </c>
-      <c r="L54" s="63"/>
-      <c r="M54" s="65"/>
-      <c r="N54" s="66"/>
-      <c r="O54" s="95"/>
-      <c r="P54" s="18">
-        <v>2E-3</v>
-      </c>
-      <c r="Q54" s="18">
-        <v>4.6600000000000003E-2</v>
-      </c>
-      <c r="R54" s="18">
-        <v>6.6600000000000006E-2</v>
-      </c>
-      <c r="S54" s="18">
-        <v>0</v>
-      </c>
-      <c r="T54" s="26">
-        <v>0</v>
-      </c>
+      <c r="A54" s="70"/>
+      <c r="B54" s="79"/>
+      <c r="C54" s="79"/>
+      <c r="D54" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="F54" s="23">
+        <f>SUM(F17:F47)</f>
+        <v>7698</v>
+      </c>
+      <c r="G54" s="23">
+        <f>SUM(G17:G53)</f>
+        <v>0</v>
+      </c>
+      <c r="H54" s="23"/>
+      <c r="I54" s="23"/>
+      <c r="J54" s="23">
+        <f>F54-G54</f>
+        <v>7698</v>
+      </c>
+      <c r="K54" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="L54" s="25">
+        <f>SUM(L17:L46)</f>
+        <v>0</v>
+      </c>
+      <c r="M54" s="25">
+        <f>SUM(M17:M46)</f>
+        <v>0</v>
+      </c>
+      <c r="N54" s="25">
+        <f>SUM(N17:N47)</f>
+        <v>7698</v>
+      </c>
+      <c r="O54" s="25">
+        <f>SUM(O17:O46)</f>
+        <v>0</v>
+      </c>
+      <c r="P54" s="26"/>
+      <c r="Q54" s="26"/>
+      <c r="R54" s="26"/>
+      <c r="S54" s="26"/>
+      <c r="T54" s="26"/>
       <c r="U54" s="119"/>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="108" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B55" s="79" t="s">
         <v>97</v>
       </c>
       <c r="C55" s="79" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D55" s="72" t="s">
         <v>98</v>
@@ -7635,16 +7535,14 @@
       </c>
       <c r="F55" s="58"/>
       <c r="G55" s="70"/>
-      <c r="H55" s="70" t="s">
-        <v>278</v>
-      </c>
+      <c r="H55" s="70"/>
       <c r="I55" s="70"/>
       <c r="J55" s="70">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="J55:J91" si="2">F55-G55</f>
         <v>0</v>
       </c>
       <c r="K55" s="72" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="L55" s="63"/>
       <c r="M55" s="65"/>
@@ -7657,7 +7555,7 @@
         <v>0.04</v>
       </c>
       <c r="R55" s="18">
-        <v>9.6600000000000005E-2</v>
+        <v>0.12330000000000001</v>
       </c>
       <c r="S55" s="18">
         <v>0</v>
@@ -7669,13 +7567,13 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="108" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B56" s="79" t="s">
         <v>97</v>
       </c>
       <c r="C56" s="79" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D56" s="72" t="s">
         <v>98</v>
@@ -7685,29 +7583,27 @@
       </c>
       <c r="F56" s="58"/>
       <c r="G56" s="70"/>
-      <c r="H56" s="70" t="s">
-        <v>278</v>
-      </c>
+      <c r="H56" s="70"/>
       <c r="I56" s="70"/>
       <c r="J56" s="70">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K56" s="72" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="L56" s="63"/>
       <c r="M56" s="65"/>
       <c r="N56" s="66"/>
       <c r="O56" s="95"/>
       <c r="P56" s="18">
-        <v>2E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="Q56" s="18">
-        <v>4.3299999999999998E-2</v>
+        <v>0.04</v>
       </c>
       <c r="R56" s="18">
-        <v>9.3299999999999994E-2</v>
+        <v>0.1633</v>
       </c>
       <c r="S56" s="18">
         <v>0</v>
@@ -7733,31 +7629,35 @@
       <c r="E57" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="F57" s="58"/>
+      <c r="F57" s="58">
+        <v>1000</v>
+      </c>
       <c r="G57" s="70"/>
       <c r="H57" s="70" t="s">
-        <v>278</v>
+        <v>303</v>
       </c>
       <c r="I57" s="70"/>
       <c r="J57" s="70">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K57" s="72" t="s">
-        <v>95</v>
+        <v>1000</v>
+      </c>
+      <c r="K57" s="195" t="s">
+        <v>63</v>
       </c>
       <c r="L57" s="63"/>
       <c r="M57" s="65"/>
-      <c r="N57" s="66"/>
+      <c r="N57" s="66">
+        <v>1000</v>
+      </c>
       <c r="O57" s="95"/>
       <c r="P57" s="18">
         <v>2E-3</v>
       </c>
       <c r="Q57" s="18">
-        <v>5.33E-2</v>
+        <v>0.03</v>
       </c>
       <c r="R57" s="18">
-        <v>0.1066</v>
+        <v>0.12659999999999999</v>
       </c>
       <c r="S57" s="18">
         <v>0</v>
@@ -7785,29 +7685,27 @@
       </c>
       <c r="F58" s="58"/>
       <c r="G58" s="70"/>
-      <c r="H58" s="70" t="s">
-        <v>278</v>
-      </c>
+      <c r="H58" s="70"/>
       <c r="I58" s="70"/>
       <c r="J58" s="70">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K58" s="72" t="s">
-        <v>118</v>
+        <v>64</v>
       </c>
       <c r="L58" s="63"/>
       <c r="M58" s="65"/>
       <c r="N58" s="66"/>
       <c r="O58" s="95"/>
       <c r="P58" s="18">
-        <v>0</v>
+        <v>1E-3</v>
       </c>
       <c r="Q58" s="18">
-        <v>4.3299999999999998E-2</v>
+        <v>2.6599999999999999E-2</v>
       </c>
       <c r="R58" s="18">
-        <v>0.14000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="S58" s="18">
         <v>0</v>
@@ -7835,29 +7733,27 @@
       </c>
       <c r="F59" s="58"/>
       <c r="G59" s="70"/>
-      <c r="H59" s="70" t="s">
-        <v>278</v>
-      </c>
+      <c r="H59" s="70"/>
       <c r="I59" s="70"/>
       <c r="J59" s="70">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K59" s="72" t="s">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="L59" s="63"/>
       <c r="M59" s="65"/>
       <c r="N59" s="66"/>
       <c r="O59" s="95"/>
       <c r="P59" s="18">
-        <v>1E-3</v>
+        <v>0</v>
       </c>
       <c r="Q59" s="18">
         <v>0.05</v>
       </c>
       <c r="R59" s="18">
-        <v>0.12659999999999999</v>
+        <v>0.1166</v>
       </c>
       <c r="S59" s="18">
         <v>0</v>
@@ -7885,27 +7781,29 @@
       </c>
       <c r="F60" s="58"/>
       <c r="G60" s="70"/>
-      <c r="H60" s="70"/>
+      <c r="H60" s="70" t="s">
+        <v>180</v>
+      </c>
       <c r="I60" s="70"/>
       <c r="J60" s="70">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K60" s="72" t="s">
-        <v>120</v>
+      <c r="K60" s="195" t="s">
+        <v>69</v>
       </c>
       <c r="L60" s="63"/>
       <c r="M60" s="65"/>
       <c r="N60" s="66"/>
       <c r="O60" s="95"/>
       <c r="P60" s="18">
-        <v>1E-3</v>
+        <v>0</v>
       </c>
       <c r="Q60" s="18">
-        <v>4.6600000000000003E-2</v>
+        <v>0.03</v>
       </c>
       <c r="R60" s="18">
-        <v>0.1333</v>
+        <v>0.1166</v>
       </c>
       <c r="S60" s="18">
         <v>0</v>
@@ -7933,29 +7831,27 @@
       </c>
       <c r="F61" s="58"/>
       <c r="G61" s="70"/>
-      <c r="H61" s="70" t="s">
-        <v>278</v>
-      </c>
+      <c r="H61" s="70"/>
       <c r="I61" s="70"/>
       <c r="J61" s="70">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K61" s="195" t="s">
-        <v>124</v>
+      <c r="K61" s="72" t="s">
+        <v>70</v>
       </c>
       <c r="L61" s="63"/>
       <c r="M61" s="65"/>
       <c r="N61" s="66"/>
       <c r="O61" s="95"/>
       <c r="P61" s="18">
-        <v>2E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="Q61" s="18">
-        <v>3.6600000000000001E-2</v>
+        <v>4.3299999999999998E-2</v>
       </c>
       <c r="R61" s="18">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="S61" s="18">
         <v>0</v>
@@ -7967,13 +7863,13 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="108" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B62" s="79" t="s">
         <v>97</v>
       </c>
       <c r="C62" s="79" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="D62" s="72" t="s">
         <v>98</v>
@@ -7991,14 +7887,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K62" s="195" t="s">
-        <v>63</v>
+      <c r="K62" s="72" t="s">
+        <v>71</v>
       </c>
       <c r="L62" s="63"/>
       <c r="M62" s="65"/>
-      <c r="N62" s="66">
-        <v>1000</v>
-      </c>
+      <c r="N62" s="66"/>
       <c r="O62" s="95"/>
       <c r="P62" s="18">
         <v>1E-3</v>
@@ -8007,7 +7901,7 @@
         <v>3.6600000000000001E-2</v>
       </c>
       <c r="R62" s="18">
-        <v>0.12330000000000001</v>
+        <v>9.6600000000000005E-2</v>
       </c>
       <c r="S62" s="18">
         <v>0</v>
@@ -8019,13 +7913,13 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="108" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B63" s="79" t="s">
         <v>97</v>
       </c>
       <c r="C63" s="79" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="D63" s="72" t="s">
         <v>98</v>
@@ -8044,22 +7938,20 @@
         <v>0</v>
       </c>
       <c r="K63" s="195" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="L63" s="63"/>
       <c r="M63" s="65"/>
-      <c r="N63" s="66">
-        <v>1000</v>
-      </c>
+      <c r="N63" s="66"/>
       <c r="O63" s="95"/>
       <c r="P63" s="18">
-        <v>3.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="Q63" s="18">
-        <v>2.3300000000000001E-2</v>
+        <v>0.02</v>
       </c>
       <c r="R63" s="18">
-        <v>0.1366</v>
+        <v>0.1033</v>
       </c>
       <c r="S63" s="18">
         <v>0</v>
@@ -8071,13 +7963,13 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="108" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B64" s="79" t="s">
         <v>97</v>
       </c>
       <c r="C64" s="79" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="D64" s="72" t="s">
         <v>98</v>
@@ -8087,31 +7979,27 @@
       </c>
       <c r="F64" s="58"/>
       <c r="G64" s="70"/>
-      <c r="H64" s="70" t="s">
-        <v>180</v>
-      </c>
+      <c r="H64" s="70"/>
       <c r="I64" s="70"/>
       <c r="J64" s="70">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K64" s="195" t="s">
-        <v>68</v>
+      <c r="K64" s="72" t="s">
+        <v>73</v>
       </c>
       <c r="L64" s="63"/>
       <c r="M64" s="65"/>
-      <c r="N64" s="66">
-        <v>1000</v>
-      </c>
+      <c r="N64" s="66"/>
       <c r="O64" s="95"/>
       <c r="P64" s="18">
-        <v>2E-3</v>
+        <v>0</v>
       </c>
       <c r="Q64" s="18">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="R64" s="18">
-        <v>9.3299999999999994E-2</v>
+        <v>0.09</v>
       </c>
       <c r="S64" s="18">
         <v>0</v>
@@ -8123,13 +8011,13 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="108" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B65" s="79" t="s">
         <v>97</v>
       </c>
       <c r="C65" s="79" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="D65" s="72" t="s">
         <v>98</v>
@@ -8140,30 +8028,28 @@
       <c r="F65" s="58"/>
       <c r="G65" s="70"/>
       <c r="H65" s="70" t="s">
-        <v>180</v>
+        <v>278</v>
       </c>
       <c r="I65" s="70"/>
       <c r="J65" s="70">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K65" s="195" t="s">
-        <v>69</v>
+      <c r="K65" s="72" t="s">
+        <v>92</v>
       </c>
       <c r="L65" s="63"/>
       <c r="M65" s="65"/>
-      <c r="N65" s="66">
-        <v>1000</v>
-      </c>
+      <c r="N65" s="66"/>
       <c r="O65" s="95"/>
       <c r="P65" s="18">
         <v>2E-3</v>
       </c>
       <c r="Q65" s="18">
-        <v>2.3300000000000001E-2</v>
+        <v>4.6600000000000003E-2</v>
       </c>
       <c r="R65" s="18">
-        <v>8.3299999999999999E-2</v>
+        <v>6.6600000000000006E-2</v>
       </c>
       <c r="S65" s="18">
         <v>0</v>
@@ -8175,13 +8061,13 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="108" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B66" s="79" t="s">
-        <v>168</v>
+        <v>97</v>
       </c>
       <c r="C66" s="79" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="D66" s="72" t="s">
         <v>98</v>
@@ -8192,30 +8078,28 @@
       <c r="F66" s="58"/>
       <c r="G66" s="70"/>
       <c r="H66" s="70" t="s">
-        <v>180</v>
+        <v>278</v>
       </c>
       <c r="I66" s="70"/>
       <c r="J66" s="70">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K66" s="195" t="s">
-        <v>70</v>
+      <c r="K66" s="72" t="s">
+        <v>93</v>
       </c>
       <c r="L66" s="63"/>
       <c r="M66" s="65"/>
-      <c r="N66" s="66">
-        <v>1000</v>
-      </c>
+      <c r="N66" s="66"/>
       <c r="O66" s="95"/>
       <c r="P66" s="18">
-        <v>1E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="Q66" s="18">
-        <v>1.66E-2</v>
+        <v>0.04</v>
       </c>
       <c r="R66" s="18">
-        <v>7.3300000000000004E-2</v>
+        <v>9.6600000000000005E-2</v>
       </c>
       <c r="S66" s="18">
         <v>0</v>
@@ -8227,13 +8111,13 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="108" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B67" s="79" t="s">
-        <v>168</v>
+        <v>97</v>
       </c>
       <c r="C67" s="79" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="D67" s="72" t="s">
         <v>98</v>
@@ -8244,30 +8128,28 @@
       <c r="F67" s="58"/>
       <c r="G67" s="70"/>
       <c r="H67" s="70" t="s">
-        <v>180</v>
+        <v>278</v>
       </c>
       <c r="I67" s="70"/>
       <c r="J67" s="70">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K67" s="195" t="s">
-        <v>71</v>
+      <c r="K67" s="72" t="s">
+        <v>94</v>
       </c>
       <c r="L67" s="63"/>
       <c r="M67" s="65"/>
-      <c r="N67" s="66">
-        <v>1000</v>
-      </c>
+      <c r="N67" s="66"/>
       <c r="O67" s="95"/>
       <c r="P67" s="18">
-        <v>1E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="Q67" s="18">
-        <v>0.02</v>
+        <v>4.3299999999999998E-2</v>
       </c>
       <c r="R67" s="18">
-        <v>6.6600000000000006E-2</v>
+        <v>9.3299999999999994E-2</v>
       </c>
       <c r="S67" s="18">
         <v>0</v>
@@ -8279,13 +8161,13 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="108" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B68" s="79" t="s">
-        <v>168</v>
+        <v>97</v>
       </c>
       <c r="C68" s="79" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="D68" s="72" t="s">
         <v>98</v>
@@ -8296,30 +8178,28 @@
       <c r="F68" s="58"/>
       <c r="G68" s="70"/>
       <c r="H68" s="70" t="s">
-        <v>180</v>
+        <v>278</v>
       </c>
       <c r="I68" s="70"/>
       <c r="J68" s="70">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K68" s="195" t="s">
-        <v>72</v>
+      <c r="K68" s="72" t="s">
+        <v>95</v>
       </c>
       <c r="L68" s="63"/>
       <c r="M68" s="65"/>
-      <c r="N68" s="66">
-        <v>1100</v>
-      </c>
+      <c r="N68" s="66"/>
       <c r="O68" s="95"/>
       <c r="P68" s="18">
         <v>2E-3</v>
       </c>
       <c r="Q68" s="18">
-        <v>2.3300000000000001E-2</v>
+        <v>5.33E-2</v>
       </c>
       <c r="R68" s="18">
-        <v>7.0000000000000007E-2</v>
+        <v>0.1066</v>
       </c>
       <c r="S68" s="18">
         <v>0</v>
@@ -8330,1737 +8210,2830 @@
       <c r="U68" s="119"/>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A69" s="108"/>
-      <c r="B69" s="79"/>
-      <c r="C69" s="79"/>
-      <c r="D69" s="72"/>
-      <c r="E69" s="93"/>
-      <c r="F69" s="162"/>
+      <c r="A69" s="108" t="s">
+        <v>164</v>
+      </c>
+      <c r="B69" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="C69" s="79" t="s">
+        <v>53</v>
+      </c>
+      <c r="D69" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E69" s="93" t="s">
+        <v>19</v>
+      </c>
+      <c r="F69" s="58"/>
       <c r="G69" s="70"/>
-      <c r="H69" s="70"/>
+      <c r="H69" s="70" t="s">
+        <v>278</v>
+      </c>
       <c r="I69" s="70"/>
       <c r="J69" s="70">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K69" s="72"/>
+      <c r="K69" s="72" t="s">
+        <v>118</v>
+      </c>
       <c r="L69" s="63"/>
       <c r="M69" s="65"/>
       <c r="N69" s="66"/>
       <c r="O69" s="95"/>
-      <c r="P69" s="18"/>
-      <c r="Q69" s="18"/>
-      <c r="R69" s="18"/>
-      <c r="S69" s="18"/>
-      <c r="T69" s="26"/>
+      <c r="P69" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="18">
+        <v>4.3299999999999998E-2</v>
+      </c>
+      <c r="R69" s="18">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="S69" s="18">
+        <v>0</v>
+      </c>
+      <c r="T69" s="26">
+        <v>0</v>
+      </c>
       <c r="U69" s="119"/>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A70" s="34"/>
-      <c r="B70" s="35"/>
-      <c r="C70" s="35"/>
-      <c r="D70" s="36" t="s">
-        <v>101</v>
-      </c>
-      <c r="E70" s="37"/>
-      <c r="F70" s="147"/>
-      <c r="G70" s="147"/>
-      <c r="H70" s="147"/>
-      <c r="I70" s="147"/>
-      <c r="J70" s="106"/>
-      <c r="K70" s="38"/>
+      <c r="A70" s="108" t="s">
+        <v>164</v>
+      </c>
+      <c r="B70" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="C70" s="79" t="s">
+        <v>53</v>
+      </c>
+      <c r="D70" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E70" s="93" t="s">
+        <v>19</v>
+      </c>
+      <c r="F70" s="58"/>
+      <c r="G70" s="70"/>
+      <c r="H70" s="70" t="s">
+        <v>278</v>
+      </c>
+      <c r="I70" s="70"/>
+      <c r="J70" s="70">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K70" s="72" t="s">
+        <v>119</v>
+      </c>
       <c r="L70" s="63"/>
       <c r="M70" s="65"/>
       <c r="N70" s="66"/>
       <c r="O70" s="95"/>
-      <c r="P70" s="18"/>
-      <c r="Q70" s="18"/>
-      <c r="R70" s="18"/>
-      <c r="S70" s="18"/>
-      <c r="T70" s="26"/>
+      <c r="P70" s="18">
+        <v>1E-3</v>
+      </c>
+      <c r="Q70" s="18">
+        <v>0.05</v>
+      </c>
+      <c r="R70" s="18">
+        <v>0.12659999999999999</v>
+      </c>
+      <c r="S70" s="18">
+        <v>0</v>
+      </c>
+      <c r="T70" s="26">
+        <v>0</v>
+      </c>
       <c r="U70" s="119"/>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A71" s="34"/>
-      <c r="B71" s="35"/>
-      <c r="C71" s="35"/>
-      <c r="D71" s="36"/>
-      <c r="E71" s="37"/>
-      <c r="F71" s="147"/>
-      <c r="G71" s="147"/>
-      <c r="H71" s="147"/>
-      <c r="I71" s="147"/>
-      <c r="J71" s="106"/>
-      <c r="K71" s="38"/>
+      <c r="A71" s="108" t="s">
+        <v>164</v>
+      </c>
+      <c r="B71" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="C71" s="79" t="s">
+        <v>53</v>
+      </c>
+      <c r="D71" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E71" s="93" t="s">
+        <v>19</v>
+      </c>
+      <c r="F71" s="58"/>
+      <c r="G71" s="70"/>
+      <c r="H71" s="70"/>
+      <c r="I71" s="70"/>
+      <c r="J71" s="70">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K71" s="72" t="s">
+        <v>120</v>
+      </c>
       <c r="L71" s="63"/>
       <c r="M71" s="65"/>
       <c r="N71" s="66"/>
       <c r="O71" s="95"/>
-      <c r="P71" s="18"/>
-      <c r="Q71" s="18"/>
-      <c r="R71" s="18"/>
-      <c r="S71" s="18"/>
-      <c r="T71" s="26"/>
+      <c r="P71" s="18">
+        <v>1E-3</v>
+      </c>
+      <c r="Q71" s="18">
+        <v>4.6600000000000003E-2</v>
+      </c>
+      <c r="R71" s="18">
+        <v>0.1333</v>
+      </c>
+      <c r="S71" s="18">
+        <v>0</v>
+      </c>
+      <c r="T71" s="26">
+        <v>0</v>
+      </c>
       <c r="U71" s="119"/>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A72" s="34"/>
-      <c r="B72" s="35"/>
-      <c r="C72" s="35"/>
-      <c r="D72" s="36" t="s">
-        <v>123</v>
-      </c>
-      <c r="E72" s="37"/>
-      <c r="F72" s="147"/>
-      <c r="G72" s="147">
-        <v>0</v>
-      </c>
-      <c r="H72" s="147"/>
-      <c r="I72" s="185">
-        <v>46296</v>
-      </c>
-      <c r="J72" s="106"/>
-      <c r="K72" s="38"/>
-      <c r="L72" s="27"/>
-      <c r="M72" s="28"/>
-      <c r="N72" s="103"/>
+      <c r="A72" s="108" t="s">
+        <v>164</v>
+      </c>
+      <c r="B72" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="C72" s="79" t="s">
+        <v>53</v>
+      </c>
+      <c r="D72" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E72" s="93" t="s">
+        <v>19</v>
+      </c>
+      <c r="F72" s="58"/>
+      <c r="G72" s="70"/>
+      <c r="H72" s="70" t="s">
+        <v>278</v>
+      </c>
+      <c r="I72" s="70"/>
+      <c r="J72" s="70">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K72" s="195" t="s">
+        <v>124</v>
+      </c>
+      <c r="L72" s="63"/>
+      <c r="M72" s="65"/>
+      <c r="N72" s="66"/>
       <c r="O72" s="95"/>
-      <c r="P72" s="18"/>
-      <c r="Q72" s="29"/>
-      <c r="R72" s="29"/>
-      <c r="S72" s="29"/>
-      <c r="T72" s="26"/>
+      <c r="P72" s="18">
+        <v>2E-3</v>
+      </c>
+      <c r="Q72" s="18">
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="R72" s="18">
+        <v>0.16</v>
+      </c>
+      <c r="S72" s="18">
+        <v>0</v>
+      </c>
+      <c r="T72" s="26">
+        <v>0</v>
+      </c>
       <c r="U72" s="119"/>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A73" s="34"/>
-      <c r="B73" s="35"/>
-      <c r="C73" s="80"/>
-      <c r="D73" s="36" t="s">
-        <v>157</v>
-      </c>
-      <c r="E73" s="37"/>
-      <c r="F73" s="147"/>
-      <c r="G73" s="147">
-        <v>0</v>
-      </c>
-      <c r="H73" s="147"/>
-      <c r="I73" s="185">
-        <v>46296</v>
-      </c>
-      <c r="J73" s="106"/>
-      <c r="K73" s="38"/>
-      <c r="L73" s="101"/>
-      <c r="M73" s="102"/>
-      <c r="N73" s="103"/>
+      <c r="A73" s="108" t="s">
+        <v>167</v>
+      </c>
+      <c r="B73" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="C73" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="D73" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E73" s="93" t="s">
+        <v>19</v>
+      </c>
+      <c r="F73" s="58"/>
+      <c r="G73" s="70"/>
+      <c r="H73" s="70" t="s">
+        <v>180</v>
+      </c>
+      <c r="I73" s="70"/>
+      <c r="J73" s="70">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K73" s="195" t="s">
+        <v>63</v>
+      </c>
+      <c r="L73" s="63"/>
+      <c r="M73" s="65"/>
+      <c r="N73" s="66"/>
       <c r="O73" s="95"/>
-      <c r="P73" s="26"/>
-      <c r="Q73" s="26"/>
-      <c r="R73" s="26"/>
-      <c r="S73" s="26"/>
-      <c r="T73" s="26"/>
+      <c r="P73" s="18">
+        <v>1E-3</v>
+      </c>
+      <c r="Q73" s="18">
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="R73" s="18">
+        <v>0.12330000000000001</v>
+      </c>
+      <c r="S73" s="18">
+        <v>0</v>
+      </c>
+      <c r="T73" s="26">
+        <v>0</v>
+      </c>
       <c r="U73" s="119"/>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A74" s="34"/>
-      <c r="B74" s="35"/>
-      <c r="C74" s="80"/>
-      <c r="D74" s="36" t="s">
+      <c r="A74" s="108" t="s">
+        <v>167</v>
+      </c>
+      <c r="B74" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="C74" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="D74" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E74" s="93" t="s">
+        <v>19</v>
+      </c>
+      <c r="F74" s="58"/>
+      <c r="G74" s="70"/>
+      <c r="H74" s="70" t="s">
         <v>180</v>
       </c>
-      <c r="E74" s="37" t="s">
-        <v>228</v>
-      </c>
-      <c r="F74" s="147"/>
-      <c r="G74" s="147"/>
-      <c r="H74" s="147"/>
-      <c r="I74" s="185"/>
-      <c r="J74" s="106"/>
-      <c r="K74" s="38"/>
-      <c r="L74" s="101"/>
-      <c r="M74" s="102"/>
-      <c r="N74" s="103"/>
+      <c r="I74" s="70"/>
+      <c r="J74" s="70">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K74" s="195" t="s">
+        <v>64</v>
+      </c>
+      <c r="L74" s="63"/>
+      <c r="M74" s="65"/>
+      <c r="N74" s="66"/>
       <c r="O74" s="95"/>
-      <c r="P74" s="26"/>
-      <c r="Q74" s="26"/>
-      <c r="R74" s="26"/>
-      <c r="S74" s="26"/>
-      <c r="T74" s="26"/>
+      <c r="P74" s="18">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="Q74" s="18">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="R74" s="18">
+        <v>0.1366</v>
+      </c>
+      <c r="S74" s="18">
+        <v>0</v>
+      </c>
+      <c r="T74" s="26">
+        <v>0</v>
+      </c>
       <c r="U74" s="119"/>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A75" s="34"/>
-      <c r="B75" s="35"/>
-      <c r="C75" s="80"/>
-      <c r="D75" s="36"/>
-      <c r="E75" s="37"/>
-      <c r="F75" s="147"/>
-      <c r="G75" s="147"/>
-      <c r="H75" s="147"/>
-      <c r="I75" s="185"/>
-      <c r="J75" s="106"/>
-      <c r="K75" s="38"/>
-      <c r="L75" s="101"/>
-      <c r="M75" s="102"/>
-      <c r="N75" s="103"/>
+      <c r="A75" s="108" t="s">
+        <v>167</v>
+      </c>
+      <c r="B75" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="C75" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="D75" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E75" s="93" t="s">
+        <v>19</v>
+      </c>
+      <c r="F75" s="58"/>
+      <c r="G75" s="70"/>
+      <c r="H75" s="70" t="s">
+        <v>180</v>
+      </c>
+      <c r="I75" s="70"/>
+      <c r="J75" s="70">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K75" s="195" t="s">
+        <v>68</v>
+      </c>
+      <c r="L75" s="63"/>
+      <c r="M75" s="65"/>
+      <c r="N75" s="66"/>
       <c r="O75" s="95"/>
-      <c r="P75" s="26"/>
-      <c r="Q75" s="26"/>
-      <c r="R75" s="26"/>
-      <c r="S75" s="26"/>
-      <c r="T75" s="26"/>
+      <c r="P75" s="18">
+        <v>2E-3</v>
+      </c>
+      <c r="Q75" s="18">
+        <v>0.02</v>
+      </c>
+      <c r="R75" s="18">
+        <v>9.3299999999999994E-2</v>
+      </c>
+      <c r="S75" s="18">
+        <v>0</v>
+      </c>
+      <c r="T75" s="26">
+        <v>0</v>
+      </c>
       <c r="U75" s="119"/>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A76" s="70"/>
-      <c r="B76" s="131"/>
-      <c r="C76" s="70"/>
-      <c r="D76" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E76" s="24" t="s">
+      <c r="A76" s="108" t="s">
+        <v>167</v>
+      </c>
+      <c r="B76" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="C76" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="D76" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E76" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="F76" s="23">
-        <f>SUM(F44:F69)</f>
-        <v>0</v>
-      </c>
-      <c r="G76" s="23">
-        <f>SUM(G44:G74)</f>
-        <v>0</v>
-      </c>
-      <c r="H76" s="23"/>
-      <c r="I76" s="23"/>
-      <c r="J76" s="23">
-        <f>F76-G76</f>
-        <v>0</v>
-      </c>
-      <c r="K76" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="L76" s="25">
-        <f>SUM(L44:L69)</f>
-        <v>0</v>
-      </c>
-      <c r="M76" s="25">
-        <f>SUM(M44:M73)</f>
-        <v>0</v>
-      </c>
-      <c r="N76" s="25">
-        <f>SUM(N44:N73)</f>
-        <v>10100</v>
-      </c>
-      <c r="O76" s="25">
-        <f>SUM(O38:O43)</f>
-        <v>0</v>
-      </c>
-      <c r="P76" s="26"/>
-      <c r="Q76" s="26"/>
-      <c r="R76" s="26"/>
-      <c r="S76" s="26"/>
-      <c r="T76" s="26"/>
+      <c r="F76" s="58"/>
+      <c r="G76" s="70"/>
+      <c r="H76" s="70" t="s">
+        <v>180</v>
+      </c>
+      <c r="I76" s="70"/>
+      <c r="J76" s="70">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K76" s="195" t="s">
+        <v>69</v>
+      </c>
+      <c r="L76" s="63"/>
+      <c r="M76" s="65"/>
+      <c r="N76" s="66"/>
+      <c r="O76" s="95"/>
+      <c r="P76" s="18">
+        <v>2E-3</v>
+      </c>
+      <c r="Q76" s="18">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="R76" s="18">
+        <v>8.3299999999999999E-2</v>
+      </c>
+      <c r="S76" s="18">
+        <v>0</v>
+      </c>
+      <c r="T76" s="26">
+        <v>0</v>
+      </c>
       <c r="U76" s="119"/>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A77" s="108"/>
-      <c r="B77" s="79"/>
-      <c r="C77" s="79"/>
-      <c r="D77" s="157"/>
-      <c r="E77" s="75"/>
+      <c r="A77" s="108" t="s">
+        <v>167</v>
+      </c>
+      <c r="B77" s="79" t="s">
+        <v>168</v>
+      </c>
+      <c r="C77" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="D77" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E77" s="93" t="s">
+        <v>19</v>
+      </c>
       <c r="F77" s="58"/>
-      <c r="G77" s="47"/>
-      <c r="H77" s="47"/>
-      <c r="I77" s="47"/>
+      <c r="G77" s="70"/>
+      <c r="H77" s="70" t="s">
+        <v>180</v>
+      </c>
+      <c r="I77" s="70"/>
       <c r="J77" s="70">
-        <f t="shared" ref="J77:J88" si="3">F77-G77</f>
-        <v>0</v>
-      </c>
-      <c r="K77" s="68"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K77" s="195" t="s">
+        <v>70</v>
+      </c>
       <c r="L77" s="63"/>
       <c r="M77" s="65"/>
       <c r="N77" s="66"/>
-      <c r="O77" s="115"/>
-      <c r="P77" s="18"/>
-      <c r="Q77" s="18"/>
-      <c r="R77" s="18"/>
-      <c r="S77" s="18"/>
-      <c r="T77" s="94"/>
-      <c r="U77" s="123"/>
+      <c r="O77" s="95"/>
+      <c r="P77" s="18">
+        <v>1E-3</v>
+      </c>
+      <c r="Q77" s="18">
+        <v>1.66E-2</v>
+      </c>
+      <c r="R77" s="18">
+        <v>7.3300000000000004E-2</v>
+      </c>
+      <c r="S77" s="18">
+        <v>0</v>
+      </c>
+      <c r="T77" s="26">
+        <v>0</v>
+      </c>
+      <c r="U77" s="119"/>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A78" s="108"/>
-      <c r="B78" s="79"/>
-      <c r="C78" s="79"/>
-      <c r="D78" s="157"/>
-      <c r="E78" s="75"/>
+      <c r="A78" s="108" t="s">
+        <v>167</v>
+      </c>
+      <c r="B78" s="79" t="s">
+        <v>168</v>
+      </c>
+      <c r="C78" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="D78" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E78" s="93" t="s">
+        <v>19</v>
+      </c>
       <c r="F78" s="58"/>
-      <c r="G78" s="47"/>
-      <c r="H78" s="47"/>
-      <c r="I78" s="47"/>
+      <c r="G78" s="70"/>
+      <c r="H78" s="70" t="s">
+        <v>180</v>
+      </c>
+      <c r="I78" s="70"/>
       <c r="J78" s="70">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K78" s="68"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K78" s="195" t="s">
+        <v>71</v>
+      </c>
       <c r="L78" s="63"/>
       <c r="M78" s="65"/>
       <c r="N78" s="66"/>
-      <c r="O78" s="115"/>
-      <c r="P78" s="18"/>
-      <c r="Q78" s="18"/>
-      <c r="R78" s="18"/>
-      <c r="S78" s="18"/>
-      <c r="T78" s="94"/>
-      <c r="U78" s="123"/>
+      <c r="O78" s="95"/>
+      <c r="P78" s="18">
+        <v>1E-3</v>
+      </c>
+      <c r="Q78" s="18">
+        <v>0.02</v>
+      </c>
+      <c r="R78" s="18">
+        <v>6.6600000000000006E-2</v>
+      </c>
+      <c r="S78" s="18">
+        <v>0</v>
+      </c>
+      <c r="T78" s="26">
+        <v>0</v>
+      </c>
+      <c r="U78" s="119"/>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="108" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B79" s="79" t="s">
-        <v>97</v>
+        <v>168</v>
       </c>
       <c r="C79" s="79" t="s">
-        <v>160</v>
-      </c>
-      <c r="D79" s="157" t="s">
-        <v>76</v>
-      </c>
-      <c r="E79" s="75" t="s">
-        <v>22</v>
-      </c>
-      <c r="F79" s="58">
-        <v>990</v>
-      </c>
-      <c r="G79" s="47"/>
-      <c r="H79" s="47"/>
-      <c r="I79" s="47"/>
+        <v>77</v>
+      </c>
+      <c r="D79" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E79" s="93" t="s">
+        <v>19</v>
+      </c>
+      <c r="F79" s="58"/>
+      <c r="G79" s="70"/>
+      <c r="H79" s="70" t="s">
+        <v>180</v>
+      </c>
+      <c r="I79" s="70"/>
       <c r="J79" s="70">
-        <f t="shared" si="3"/>
-        <v>990</v>
-      </c>
-      <c r="K79" s="68" t="s">
-        <v>78</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K79" s="195" t="s">
+        <v>72</v>
       </c>
       <c r="L79" s="63"/>
       <c r="M79" s="65"/>
-      <c r="N79" s="66">
-        <v>990</v>
-      </c>
-      <c r="O79" s="115"/>
+      <c r="N79" s="66"/>
+      <c r="O79" s="95"/>
       <c r="P79" s="18">
-        <v>0.36499999999999999</v>
+        <v>2E-3</v>
       </c>
       <c r="Q79" s="18">
-        <v>0</v>
+        <v>2.3300000000000001E-2</v>
       </c>
       <c r="R79" s="18">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="S79" s="18">
         <v>0</v>
       </c>
-      <c r="T79" s="94">
-        <v>0.13900000000000001</v>
-      </c>
-      <c r="U79" s="123"/>
+      <c r="T79" s="26">
+        <v>0</v>
+      </c>
+      <c r="U79" s="119"/>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="108" t="s">
-        <v>159</v>
+        <v>304</v>
       </c>
       <c r="B80" s="79" t="s">
-        <v>97</v>
+        <v>305</v>
       </c>
       <c r="C80" s="79" t="s">
-        <v>160</v>
-      </c>
-      <c r="D80" s="157" t="s">
-        <v>76</v>
-      </c>
-      <c r="E80" s="75" t="s">
-        <v>22</v>
-      </c>
-      <c r="F80" s="58">
-        <v>872</v>
-      </c>
-      <c r="G80" s="47"/>
-      <c r="H80" s="47"/>
-      <c r="I80" s="47"/>
+        <v>77</v>
+      </c>
+      <c r="D80" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E80" s="93" t="s">
+        <v>19</v>
+      </c>
+      <c r="F80" s="58"/>
+      <c r="G80" s="70"/>
+      <c r="H80" s="70"/>
+      <c r="I80" s="70"/>
       <c r="J80" s="70">
-        <f t="shared" si="3"/>
-        <v>872</v>
-      </c>
-      <c r="K80" s="68" t="s">
-        <v>78</v>
-      </c>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K80" s="195"/>
       <c r="L80" s="63"/>
       <c r="M80" s="65"/>
-      <c r="N80" s="66">
-        <v>872</v>
-      </c>
-      <c r="O80" s="115"/>
-      <c r="P80" s="18">
-        <v>0.39200000000000002</v>
-      </c>
-      <c r="Q80" s="18">
-        <v>0</v>
-      </c>
-      <c r="R80" s="18">
-        <v>0</v>
-      </c>
-      <c r="S80" s="18">
-        <v>0</v>
-      </c>
-      <c r="T80" s="94">
-        <v>0.16400000000000001</v>
-      </c>
-      <c r="U80" s="123"/>
+      <c r="N80" s="66"/>
+      <c r="O80" s="95"/>
+      <c r="P80" s="18"/>
+      <c r="Q80" s="18"/>
+      <c r="R80" s="18"/>
+      <c r="S80" s="18"/>
+      <c r="T80" s="26"/>
+      <c r="U80" s="119"/>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="108" t="s">
-        <v>164</v>
+        <v>304</v>
       </c>
       <c r="B81" s="79" t="s">
-        <v>97</v>
+        <v>305</v>
       </c>
       <c r="C81" s="79" t="s">
-        <v>165</v>
-      </c>
-      <c r="D81" s="157" t="s">
-        <v>76</v>
-      </c>
-      <c r="E81" s="75" t="s">
-        <v>22</v>
+        <v>77</v>
+      </c>
+      <c r="D81" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E81" s="93" t="s">
+        <v>19</v>
       </c>
       <c r="F81" s="58">
-        <v>931</v>
-      </c>
-      <c r="G81" s="47"/>
-      <c r="H81" s="47"/>
-      <c r="I81" s="47"/>
+        <v>1000</v>
+      </c>
+      <c r="G81" s="70"/>
+      <c r="H81" s="70" t="s">
+        <v>306</v>
+      </c>
+      <c r="I81" s="70"/>
       <c r="J81" s="70">
-        <f t="shared" si="3"/>
-        <v>931</v>
-      </c>
-      <c r="K81" s="68" t="s">
-        <v>78</v>
+        <f t="shared" si="2"/>
+        <v>1000</v>
+      </c>
+      <c r="K81" s="195" t="s">
+        <v>63</v>
       </c>
       <c r="L81" s="63"/>
       <c r="M81" s="65"/>
       <c r="N81" s="66">
-        <v>931</v>
-      </c>
-      <c r="O81" s="115"/>
+        <v>1000</v>
+      </c>
+      <c r="O81" s="95"/>
       <c r="P81" s="18">
-        <v>0.35599999999999998</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="Q81" s="18">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="R81" s="18">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="S81" s="18">
         <v>0</v>
       </c>
-      <c r="T81" s="94">
-        <v>0.23599999999999999</v>
-      </c>
-      <c r="U81" s="123"/>
+      <c r="T81" s="26">
+        <v>0</v>
+      </c>
+      <c r="U81" s="119"/>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="108" t="s">
-        <v>164</v>
+        <v>304</v>
       </c>
       <c r="B82" s="79" t="s">
-        <v>97</v>
+        <v>305</v>
       </c>
       <c r="C82" s="79" t="s">
-        <v>165</v>
-      </c>
-      <c r="D82" s="157" t="s">
-        <v>76</v>
-      </c>
-      <c r="E82" s="75" t="s">
-        <v>22</v>
+        <v>77</v>
+      </c>
+      <c r="D82" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E82" s="93" t="s">
+        <v>19</v>
       </c>
       <c r="F82" s="58">
-        <v>949</v>
-      </c>
-      <c r="G82" s="47"/>
-      <c r="H82" s="47"/>
-      <c r="I82" s="47"/>
+        <v>1000</v>
+      </c>
+      <c r="G82" s="70"/>
+      <c r="H82" s="70" t="s">
+        <v>306</v>
+      </c>
+      <c r="I82" s="70"/>
       <c r="J82" s="70">
-        <f t="shared" si="3"/>
-        <v>949</v>
-      </c>
-      <c r="K82" s="68" t="s">
-        <v>78</v>
+        <f t="shared" si="2"/>
+        <v>1000</v>
+      </c>
+      <c r="K82" s="195" t="s">
+        <v>64</v>
       </c>
       <c r="L82" s="63"/>
       <c r="M82" s="65"/>
       <c r="N82" s="66">
-        <v>949</v>
-      </c>
-      <c r="O82" s="115"/>
+        <v>1000</v>
+      </c>
+      <c r="O82" s="95"/>
       <c r="P82" s="18">
-        <v>0.41299999999999998</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="Q82" s="18">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="R82" s="18">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="S82" s="18">
         <v>0</v>
       </c>
-      <c r="T82" s="94">
-        <v>0.19700000000000001</v>
-      </c>
-      <c r="U82" s="123"/>
+      <c r="T82" s="26">
+        <v>0</v>
+      </c>
+      <c r="U82" s="119"/>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="108" t="s">
-        <v>164</v>
+        <v>304</v>
       </c>
       <c r="B83" s="79" t="s">
-        <v>97</v>
+        <v>305</v>
       </c>
       <c r="C83" s="79" t="s">
-        <v>165</v>
-      </c>
-      <c r="D83" s="157" t="s">
-        <v>76</v>
-      </c>
-      <c r="E83" s="75" t="s">
-        <v>22</v>
+        <v>77</v>
+      </c>
+      <c r="D83" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E83" s="93" t="s">
+        <v>19</v>
       </c>
       <c r="F83" s="58">
-        <v>1026</v>
-      </c>
-      <c r="G83" s="47"/>
-      <c r="H83" s="47"/>
-      <c r="I83" s="47"/>
+        <v>1000</v>
+      </c>
+      <c r="G83" s="70"/>
+      <c r="H83" s="70" t="s">
+        <v>306</v>
+      </c>
+      <c r="I83" s="70"/>
       <c r="J83" s="70">
-        <f t="shared" si="3"/>
-        <v>1026</v>
-      </c>
-      <c r="K83" s="68" t="s">
-        <v>78</v>
+        <f t="shared" si="2"/>
+        <v>1000</v>
+      </c>
+      <c r="K83" s="195" t="s">
+        <v>68</v>
       </c>
       <c r="L83" s="63"/>
       <c r="M83" s="65"/>
       <c r="N83" s="66">
-        <v>1026</v>
-      </c>
-      <c r="O83" s="115"/>
+        <v>1000</v>
+      </c>
+      <c r="O83" s="95"/>
       <c r="P83" s="18">
-        <v>8.9999999999999993E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="Q83" s="18">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="R83" s="18">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="S83" s="18">
         <v>0</v>
       </c>
-      <c r="T83" s="94">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="U83" s="123"/>
+      <c r="T83" s="26">
+        <v>0</v>
+      </c>
+      <c r="U83" s="119"/>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="108" t="s">
-        <v>164</v>
+        <v>304</v>
       </c>
       <c r="B84" s="79" t="s">
-        <v>97</v>
+        <v>305</v>
       </c>
       <c r="C84" s="79" t="s">
-        <v>165</v>
-      </c>
-      <c r="D84" s="157" t="s">
-        <v>76</v>
-      </c>
-      <c r="E84" s="75" t="s">
-        <v>22</v>
+        <v>77</v>
+      </c>
+      <c r="D84" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E84" s="93" t="s">
+        <v>19</v>
       </c>
       <c r="F84" s="58">
-        <v>926</v>
-      </c>
-      <c r="G84" s="47"/>
-      <c r="H84" s="47"/>
-      <c r="I84" s="47"/>
+        <v>1000</v>
+      </c>
+      <c r="G84" s="70"/>
+      <c r="H84" s="70" t="s">
+        <v>306</v>
+      </c>
+      <c r="I84" s="70"/>
       <c r="J84" s="70">
-        <f t="shared" si="3"/>
-        <v>926</v>
-      </c>
-      <c r="K84" s="68" t="s">
-        <v>78</v>
+        <f t="shared" si="2"/>
+        <v>1000</v>
+      </c>
+      <c r="K84" s="195" t="s">
+        <v>69</v>
       </c>
       <c r="L84" s="63"/>
       <c r="M84" s="65"/>
       <c r="N84" s="66">
-        <v>926</v>
-      </c>
-      <c r="O84" s="115"/>
+        <v>1000</v>
+      </c>
+      <c r="O84" s="95"/>
       <c r="P84" s="18">
-        <v>0.307</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="Q84" s="18">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="R84" s="18">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="S84" s="18">
         <v>0</v>
       </c>
-      <c r="T84" s="94">
-        <v>0.158</v>
-      </c>
-      <c r="U84" s="123"/>
+      <c r="T84" s="26">
+        <v>0</v>
+      </c>
+      <c r="U84" s="119"/>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="108" t="s">
-        <v>167</v>
+        <v>304</v>
       </c>
       <c r="B85" s="79" t="s">
-        <v>97</v>
+        <v>305</v>
       </c>
       <c r="C85" s="79" t="s">
         <v>77</v>
       </c>
-      <c r="D85" s="157" t="s">
-        <v>76</v>
-      </c>
-      <c r="E85" s="75" t="s">
-        <v>22</v>
+      <c r="D85" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E85" s="93" t="s">
+        <v>19</v>
       </c>
       <c r="F85" s="58">
-        <v>890</v>
-      </c>
-      <c r="G85" s="47"/>
-      <c r="H85" s="47"/>
-      <c r="I85" s="47"/>
+        <v>1000</v>
+      </c>
+      <c r="G85" s="70"/>
+      <c r="H85" s="70" t="s">
+        <v>306</v>
+      </c>
+      <c r="I85" s="70"/>
       <c r="J85" s="70">
-        <f t="shared" si="3"/>
-        <v>890</v>
-      </c>
-      <c r="K85" s="68" t="s">
-        <v>78</v>
+        <f t="shared" si="2"/>
+        <v>1000</v>
+      </c>
+      <c r="K85" s="195" t="s">
+        <v>70</v>
       </c>
       <c r="L85" s="63"/>
       <c r="M85" s="65"/>
       <c r="N85" s="66">
-        <v>890</v>
-      </c>
-      <c r="O85" s="115"/>
+        <v>1000</v>
+      </c>
+      <c r="O85" s="95"/>
       <c r="P85" s="18">
-        <v>0.27500000000000002</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="Q85" s="18">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="R85" s="18">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="S85" s="18">
         <v>0</v>
       </c>
-      <c r="T85" s="94">
-        <v>0.11600000000000001</v>
-      </c>
-      <c r="U85" s="123"/>
+      <c r="T85" s="26">
+        <v>0</v>
+      </c>
+      <c r="U85" s="119"/>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="108" t="s">
-        <v>167</v>
+        <v>304</v>
       </c>
       <c r="B86" s="79" t="s">
-        <v>97</v>
+        <v>305</v>
       </c>
       <c r="C86" s="79" t="s">
         <v>77</v>
       </c>
-      <c r="D86" s="157" t="s">
-        <v>76</v>
-      </c>
-      <c r="E86" s="75" t="s">
-        <v>22</v>
+      <c r="D86" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E86" s="93" t="s">
+        <v>19</v>
       </c>
       <c r="F86" s="58">
-        <v>940</v>
-      </c>
-      <c r="G86" s="47"/>
-      <c r="H86" s="47"/>
-      <c r="I86" s="47"/>
+        <v>874</v>
+      </c>
+      <c r="G86" s="70"/>
+      <c r="H86" s="70" t="s">
+        <v>306</v>
+      </c>
+      <c r="I86" s="70"/>
       <c r="J86" s="70">
-        <f t="shared" si="3"/>
-        <v>940</v>
-      </c>
-      <c r="K86" s="68" t="s">
-        <v>78</v>
+        <f t="shared" si="2"/>
+        <v>874</v>
+      </c>
+      <c r="K86" s="195" t="s">
+        <v>71</v>
       </c>
       <c r="L86" s="63"/>
       <c r="M86" s="65"/>
       <c r="N86" s="66">
-        <v>940</v>
-      </c>
-      <c r="O86" s="115"/>
+        <v>874</v>
+      </c>
+      <c r="O86" s="95"/>
       <c r="P86" s="18">
-        <v>0.28399999999999997</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="Q86" s="18">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="R86" s="18">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="S86" s="18">
         <v>0</v>
       </c>
-      <c r="T86" s="94">
-        <v>0.158</v>
-      </c>
-      <c r="U86" s="123"/>
+      <c r="T86" s="26">
+        <v>0</v>
+      </c>
+      <c r="U86" s="119"/>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="108" t="s">
-        <v>167</v>
+        <v>304</v>
       </c>
       <c r="B87" s="79" t="s">
-        <v>168</v>
+        <v>305</v>
       </c>
       <c r="C87" s="79" t="s">
         <v>77</v>
       </c>
-      <c r="D87" s="157" t="s">
-        <v>76</v>
-      </c>
-      <c r="E87" s="75" t="s">
-        <v>22</v>
+      <c r="D87" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E87" s="93" t="s">
+        <v>19</v>
       </c>
       <c r="F87" s="58">
-        <v>746</v>
-      </c>
-      <c r="G87" s="47"/>
-      <c r="H87" s="47"/>
-      <c r="I87" s="47"/>
+        <v>950</v>
+      </c>
+      <c r="G87" s="70"/>
+      <c r="H87" s="70" t="s">
+        <v>306</v>
+      </c>
+      <c r="I87" s="70"/>
       <c r="J87" s="70">
-        <f t="shared" si="3"/>
-        <v>746</v>
-      </c>
-      <c r="K87" s="68" t="s">
-        <v>78</v>
+        <f t="shared" si="2"/>
+        <v>950</v>
+      </c>
+      <c r="K87" s="195" t="s">
+        <v>72</v>
       </c>
       <c r="L87" s="63"/>
       <c r="M87" s="65"/>
       <c r="N87" s="66">
-        <v>746</v>
-      </c>
-      <c r="O87" s="115"/>
+        <v>950</v>
+      </c>
+      <c r="O87" s="95"/>
       <c r="P87" s="18">
-        <v>1.2E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="Q87" s="18">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="R87" s="18">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="S87" s="18">
         <v>0</v>
       </c>
-      <c r="T87" s="94">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="U87" s="123"/>
+      <c r="T87" s="26">
+        <v>0</v>
+      </c>
+      <c r="U87" s="119"/>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A88" s="81"/>
-      <c r="B88" s="132"/>
-      <c r="C88" s="82"/>
-      <c r="D88" s="70"/>
-      <c r="E88" s="57"/>
-      <c r="F88" s="58"/>
-      <c r="G88" s="47"/>
-      <c r="H88" s="47"/>
-      <c r="I88" s="47"/>
+      <c r="A88" s="108" t="s">
+        <v>304</v>
+      </c>
+      <c r="B88" s="79" t="s">
+        <v>305</v>
+      </c>
+      <c r="C88" s="79" t="s">
+        <v>53</v>
+      </c>
+      <c r="D88" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E88" s="93" t="s">
+        <v>19</v>
+      </c>
+      <c r="F88" s="58">
+        <v>1000</v>
+      </c>
+      <c r="G88" s="70"/>
+      <c r="H88" s="70" t="s">
+        <v>306</v>
+      </c>
+      <c r="I88" s="70"/>
       <c r="J88" s="70">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K88" s="55"/>
+        <f t="shared" si="2"/>
+        <v>1000</v>
+      </c>
+      <c r="K88" s="195" t="s">
+        <v>63</v>
+      </c>
       <c r="L88" s="63"/>
       <c r="M88" s="65"/>
-      <c r="N88" s="107"/>
-      <c r="O88" s="115"/>
-      <c r="P88" s="18"/>
-      <c r="Q88" s="18"/>
-      <c r="R88" s="18"/>
-      <c r="S88" s="29"/>
-      <c r="T88" s="29"/>
-      <c r="U88" s="123"/>
+      <c r="N88" s="66">
+        <v>1000</v>
+      </c>
+      <c r="O88" s="95"/>
+      <c r="P88" s="18">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="Q88" s="18">
+        <v>0.05</v>
+      </c>
+      <c r="R88" s="18">
+        <v>0.08</v>
+      </c>
+      <c r="S88" s="18">
+        <v>0</v>
+      </c>
+      <c r="T88" s="26">
+        <v>0</v>
+      </c>
+      <c r="U88" s="119"/>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A89" s="124"/>
-      <c r="B89" s="133"/>
-      <c r="C89" s="125"/>
-      <c r="D89" s="126"/>
-      <c r="E89" s="87"/>
-      <c r="F89" s="88"/>
-      <c r="G89" s="89"/>
-      <c r="H89" s="89"/>
-      <c r="I89" s="89"/>
-      <c r="J89" s="127"/>
-      <c r="K89" s="90"/>
+      <c r="A89" s="108" t="s">
+        <v>304</v>
+      </c>
+      <c r="B89" s="79" t="s">
+        <v>305</v>
+      </c>
+      <c r="C89" s="79" t="s">
+        <v>53</v>
+      </c>
+      <c r="D89" s="72" t="s">
+        <v>98</v>
+      </c>
+      <c r="E89" s="93" t="s">
+        <v>19</v>
+      </c>
+      <c r="F89" s="58">
+        <v>987</v>
+      </c>
+      <c r="G89" s="70"/>
+      <c r="H89" s="70" t="s">
+        <v>306</v>
+      </c>
+      <c r="I89" s="70"/>
+      <c r="J89" s="70">
+        <f t="shared" si="2"/>
+        <v>987</v>
+      </c>
+      <c r="K89" s="195" t="s">
+        <v>64</v>
+      </c>
       <c r="L89" s="63"/>
-      <c r="M89" s="64"/>
-      <c r="N89" s="107"/>
-      <c r="O89" s="115"/>
-      <c r="P89" s="18"/>
-      <c r="Q89" s="18"/>
-      <c r="R89" s="18"/>
-      <c r="S89" s="18"/>
-      <c r="T89" s="18"/>
-      <c r="U89" s="122"/>
+      <c r="M89" s="65"/>
+      <c r="N89" s="66">
+        <v>987</v>
+      </c>
+      <c r="O89" s="95"/>
+      <c r="P89" s="18">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="Q89" s="18">
+        <v>0.05</v>
+      </c>
+      <c r="R89" s="18">
+        <v>0.08</v>
+      </c>
+      <c r="S89" s="18">
+        <v>0</v>
+      </c>
+      <c r="T89" s="26">
+        <v>0</v>
+      </c>
+      <c r="U89" s="119"/>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A90" s="124"/>
-      <c r="B90" s="133"/>
-      <c r="C90" s="125"/>
-      <c r="D90" s="127"/>
-      <c r="E90" s="87"/>
-      <c r="F90" s="88"/>
-      <c r="G90" s="91"/>
-      <c r="H90" s="91"/>
-      <c r="I90" s="91"/>
-      <c r="J90" s="127"/>
-      <c r="K90" s="144"/>
+      <c r="A90" s="108"/>
+      <c r="B90" s="79"/>
+      <c r="C90" s="79"/>
+      <c r="D90" s="72"/>
+      <c r="E90" s="93"/>
+      <c r="F90" s="58"/>
+      <c r="G90" s="70"/>
+      <c r="H90" s="70"/>
+      <c r="I90" s="70"/>
+      <c r="J90" s="70"/>
+      <c r="K90" s="195"/>
       <c r="L90" s="63"/>
       <c r="M90" s="65"/>
-      <c r="N90" s="107"/>
-      <c r="O90" s="115"/>
+      <c r="N90" s="66"/>
+      <c r="O90" s="95"/>
       <c r="P90" s="18"/>
       <c r="Q90" s="18"/>
       <c r="R90" s="18"/>
       <c r="S90" s="18"/>
-      <c r="T90" s="18"/>
-      <c r="U90" s="122"/>
+      <c r="T90" s="26"/>
+      <c r="U90" s="119"/>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A91" s="127"/>
-      <c r="B91" s="134"/>
-      <c r="C91" s="125"/>
-      <c r="D91" s="127"/>
-      <c r="E91" s="87"/>
-      <c r="F91" s="88"/>
-      <c r="G91" s="91"/>
-      <c r="H91" s="91"/>
-      <c r="I91" s="91"/>
-      <c r="J91" s="127"/>
-      <c r="K91" s="90"/>
-      <c r="L91" s="56"/>
+      <c r="A91" s="108"/>
+      <c r="B91" s="79"/>
+      <c r="C91" s="79"/>
+      <c r="D91" s="72"/>
+      <c r="E91" s="93"/>
+      <c r="F91" s="162"/>
+      <c r="G91" s="70"/>
+      <c r="H91" s="70"/>
+      <c r="I91" s="70"/>
+      <c r="J91" s="70">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K91" s="72"/>
+      <c r="L91" s="63"/>
       <c r="M91" s="65"/>
-      <c r="N91" s="107"/>
-      <c r="O91" s="115"/>
+      <c r="N91" s="66"/>
+      <c r="O91" s="95"/>
       <c r="P91" s="18"/>
       <c r="Q91" s="18"/>
       <c r="R91" s="18"/>
       <c r="S91" s="18"/>
-      <c r="T91" s="18"/>
-      <c r="U91" s="123"/>
+      <c r="T91" s="26"/>
+      <c r="U91" s="119"/>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A92" s="128"/>
-      <c r="B92" s="135"/>
-      <c r="C92" s="129"/>
-      <c r="D92" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E92" s="52" t="s">
-        <v>22</v>
-      </c>
-      <c r="F92" s="23">
-        <f>SUM(F77:F91)</f>
-        <v>8270</v>
-      </c>
-      <c r="G92" s="23">
-        <f>SUM(G77:G91)</f>
-        <v>0</v>
-      </c>
-      <c r="H92" s="23"/>
-      <c r="I92" s="23"/>
-      <c r="J92" s="23">
-        <f>F92-G92</f>
-        <v>8270</v>
-      </c>
-      <c r="K92" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="L92" s="25">
-        <f>SUM(L77:L88)</f>
-        <v>0</v>
-      </c>
-      <c r="M92" s="25">
-        <f>SUM(M77:M88)</f>
-        <v>0</v>
-      </c>
-      <c r="N92" s="25">
-        <f>SUM(N77:N91)</f>
-        <v>8270</v>
-      </c>
-      <c r="O92" s="25">
-        <f>SUM(O77:O91)</f>
-        <v>0</v>
-      </c>
+      <c r="A92" s="34"/>
+      <c r="B92" s="35"/>
+      <c r="C92" s="35"/>
+      <c r="D92" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="E92" s="37"/>
+      <c r="F92" s="147"/>
+      <c r="G92" s="147"/>
+      <c r="H92" s="147"/>
+      <c r="I92" s="147"/>
+      <c r="J92" s="106"/>
+      <c r="K92" s="38"/>
+      <c r="L92" s="63"/>
+      <c r="M92" s="65"/>
+      <c r="N92" s="66"/>
+      <c r="O92" s="95"/>
       <c r="P92" s="18"/>
       <c r="Q92" s="18"/>
       <c r="R92" s="18"/>
       <c r="S92" s="18"/>
-      <c r="T92" s="18"/>
-      <c r="U92" s="123"/>
+      <c r="T92" s="26"/>
+      <c r="U92" s="119"/>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A93" s="128"/>
-      <c r="B93" s="135"/>
-      <c r="C93" s="129"/>
-      <c r="D93" s="23"/>
-      <c r="E93" s="52"/>
-      <c r="F93" s="23"/>
-      <c r="G93" s="23"/>
-      <c r="H93" s="23"/>
-      <c r="I93" s="23"/>
-      <c r="J93" s="23"/>
-      <c r="K93" s="24"/>
-      <c r="L93" s="25"/>
-      <c r="M93" s="25"/>
-      <c r="N93" s="25"/>
-      <c r="O93" s="25"/>
+      <c r="A93" s="34"/>
+      <c r="B93" s="35"/>
+      <c r="C93" s="35"/>
+      <c r="D93" s="36"/>
+      <c r="E93" s="37"/>
+      <c r="F93" s="147"/>
+      <c r="G93" s="147"/>
+      <c r="H93" s="147"/>
+      <c r="I93" s="147"/>
+      <c r="J93" s="106"/>
+      <c r="K93" s="38"/>
+      <c r="L93" s="63"/>
+      <c r="M93" s="65"/>
+      <c r="N93" s="66"/>
+      <c r="O93" s="95"/>
       <c r="P93" s="18"/>
       <c r="Q93" s="18"/>
       <c r="R93" s="18"/>
       <c r="S93" s="18"/>
-      <c r="T93" s="18"/>
-      <c r="U93" s="123"/>
+      <c r="T93" s="26"/>
+      <c r="U93" s="119"/>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A94" s="81" t="s">
-        <v>164</v>
-      </c>
-      <c r="B94" s="79" t="s">
-        <v>97</v>
-      </c>
-      <c r="C94" s="79" t="s">
-        <v>166</v>
-      </c>
-      <c r="D94" s="157" t="s">
-        <v>76</v>
-      </c>
-      <c r="E94" s="75" t="s">
-        <v>135</v>
-      </c>
-      <c r="F94" s="58">
-        <v>665</v>
-      </c>
-      <c r="G94" s="47"/>
-      <c r="H94" s="47"/>
-      <c r="I94" s="47"/>
-      <c r="J94" s="70">
-        <v>665</v>
-      </c>
-      <c r="K94" s="68" t="s">
-        <v>78</v>
-      </c>
-      <c r="L94" s="63"/>
-      <c r="M94" s="64"/>
-      <c r="N94" s="173">
-        <v>665</v>
-      </c>
-      <c r="O94" s="25"/>
-      <c r="P94" s="18">
-        <v>0.36499999999999999</v>
-      </c>
-      <c r="Q94" s="18">
-        <v>0.22</v>
-      </c>
-      <c r="R94" s="18">
-        <v>0.18</v>
-      </c>
-      <c r="S94" s="18">
-        <v>0</v>
-      </c>
-      <c r="T94" s="18">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="U94" s="123"/>
+      <c r="A94" s="34"/>
+      <c r="B94" s="35"/>
+      <c r="C94" s="35"/>
+      <c r="D94" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="E94" s="37"/>
+      <c r="F94" s="147"/>
+      <c r="G94" s="147">
+        <v>0</v>
+      </c>
+      <c r="H94" s="147"/>
+      <c r="I94" s="185">
+        <v>46296</v>
+      </c>
+      <c r="J94" s="106"/>
+      <c r="K94" s="38"/>
+      <c r="L94" s="27"/>
+      <c r="M94" s="28"/>
+      <c r="N94" s="103"/>
+      <c r="O94" s="95"/>
+      <c r="P94" s="18"/>
+      <c r="Q94" s="29"/>
+      <c r="R94" s="29"/>
+      <c r="S94" s="29"/>
+      <c r="T94" s="26"/>
+      <c r="U94" s="119"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A95" s="81" t="s">
-        <v>164</v>
-      </c>
-      <c r="B95" s="79" t="s">
-        <v>97</v>
-      </c>
-      <c r="C95" s="79" t="s">
-        <v>166</v>
-      </c>
-      <c r="D95" s="157" t="s">
-        <v>76</v>
-      </c>
-      <c r="E95" s="75" t="s">
-        <v>134</v>
-      </c>
-      <c r="F95" s="58">
-        <v>653</v>
-      </c>
-      <c r="G95" s="46"/>
-      <c r="H95" s="47"/>
-      <c r="I95" s="46"/>
-      <c r="J95" s="70">
-        <v>653</v>
-      </c>
-      <c r="K95" s="68" t="s">
-        <v>78</v>
-      </c>
-      <c r="L95" s="63"/>
-      <c r="M95" s="65"/>
-      <c r="N95" s="173">
-        <v>653</v>
-      </c>
-      <c r="O95" s="115"/>
-      <c r="P95" s="18">
-        <v>0.32900000000000001</v>
-      </c>
-      <c r="Q95" s="18">
-        <v>0.25</v>
-      </c>
-      <c r="R95" s="18">
-        <v>0.23</v>
-      </c>
-      <c r="S95" s="18">
-        <v>0</v>
-      </c>
-      <c r="T95" s="18">
-        <v>1.9E-2</v>
-      </c>
-      <c r="U95" s="123"/>
+      <c r="A95" s="34"/>
+      <c r="B95" s="35"/>
+      <c r="C95" s="80"/>
+      <c r="D95" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="E95" s="37"/>
+      <c r="F95" s="147"/>
+      <c r="G95" s="147">
+        <v>0</v>
+      </c>
+      <c r="H95" s="147"/>
+      <c r="I95" s="185">
+        <v>46296</v>
+      </c>
+      <c r="J95" s="106"/>
+      <c r="K95" s="38"/>
+      <c r="L95" s="101"/>
+      <c r="M95" s="102"/>
+      <c r="N95" s="103"/>
+      <c r="O95" s="95"/>
+      <c r="P95" s="26"/>
+      <c r="Q95" s="26"/>
+      <c r="R95" s="26"/>
+      <c r="S95" s="26"/>
+      <c r="T95" s="26"/>
+      <c r="U95" s="119"/>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A96" s="70"/>
-      <c r="B96" s="131"/>
-      <c r="C96" s="70"/>
-      <c r="D96" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E96" s="52" t="s">
-        <v>39</v>
-      </c>
-      <c r="F96" s="25">
-        <f>SUM(F94:F95)</f>
-        <v>1318</v>
-      </c>
-      <c r="G96" s="25">
-        <f>SUM(G94:G95)</f>
-        <v>0</v>
-      </c>
-      <c r="H96" s="23"/>
-      <c r="I96" s="23"/>
-      <c r="J96" s="25">
-        <f>F96-G96</f>
-        <v>1318</v>
-      </c>
-      <c r="K96" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="L96" s="25">
-        <f>SUM(L94:L95)</f>
-        <v>0</v>
-      </c>
-      <c r="M96" s="25">
-        <f>SUM(M77:M95)</f>
-        <v>0</v>
-      </c>
-      <c r="N96" s="25">
-        <f>SUM(N94:N95)</f>
-        <v>1318</v>
-      </c>
-      <c r="O96" s="25">
-        <f>SUM(O77:O95)</f>
-        <v>0</v>
-      </c>
+      <c r="A96" s="34"/>
+      <c r="B96" s="35"/>
+      <c r="C96" s="80"/>
+      <c r="D96" s="36" t="s">
+        <v>180</v>
+      </c>
+      <c r="E96" s="37" t="s">
+        <v>228</v>
+      </c>
+      <c r="F96" s="147"/>
+      <c r="G96" s="147"/>
+      <c r="H96" s="147"/>
+      <c r="I96" s="185"/>
+      <c r="J96" s="106"/>
+      <c r="K96" s="38"/>
+      <c r="L96" s="101"/>
+      <c r="M96" s="102"/>
+      <c r="N96" s="103"/>
+      <c r="O96" s="95"/>
       <c r="P96" s="26"/>
       <c r="Q96" s="26"/>
       <c r="R96" s="26"/>
       <c r="S96" s="26"/>
       <c r="T96" s="26"/>
-      <c r="U96" s="111"/>
+      <c r="U96" s="119"/>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A97" s="70"/>
-      <c r="B97" s="131"/>
-      <c r="C97" s="81"/>
-      <c r="D97" s="70"/>
-      <c r="E97" s="108"/>
-      <c r="F97" s="70"/>
-      <c r="G97" s="70"/>
-      <c r="H97" s="70"/>
-      <c r="I97" s="70"/>
-      <c r="J97" s="70"/>
-      <c r="K97" s="70"/>
+      <c r="A97" s="34"/>
+      <c r="B97" s="35"/>
+      <c r="C97" s="80"/>
+      <c r="D97" s="36"/>
+      <c r="E97" s="37"/>
+      <c r="F97" s="147"/>
+      <c r="G97" s="147"/>
+      <c r="H97" s="147"/>
+      <c r="I97" s="185"/>
+      <c r="J97" s="106"/>
+      <c r="K97" s="38"/>
       <c r="L97" s="101"/>
-      <c r="M97" s="109"/>
-      <c r="N97" s="107"/>
-      <c r="O97" s="115"/>
+      <c r="M97" s="102"/>
+      <c r="N97" s="103"/>
+      <c r="O97" s="95"/>
       <c r="P97" s="26"/>
       <c r="Q97" s="26"/>
       <c r="R97" s="26"/>
       <c r="S97" s="26"/>
       <c r="T97" s="26"/>
-      <c r="U97" s="111"/>
+      <c r="U97" s="119"/>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="70"/>
       <c r="B98" s="131"/>
       <c r="C98" s="70"/>
-      <c r="D98" s="70"/>
-      <c r="E98" s="70"/>
-      <c r="F98" s="70"/>
-      <c r="G98" s="70"/>
-      <c r="H98" s="70"/>
-      <c r="I98" s="70"/>
-      <c r="J98" s="70"/>
-      <c r="K98" s="70"/>
-      <c r="L98" s="101"/>
-      <c r="M98" s="109"/>
-      <c r="N98" s="107"/>
-      <c r="O98" s="115"/>
+      <c r="D98" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E98" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F98" s="23">
+        <f>SUM(F55:F91)</f>
+        <v>9811</v>
+      </c>
+      <c r="G98" s="23">
+        <f>SUM(G55:G96)</f>
+        <v>0</v>
+      </c>
+      <c r="H98" s="23"/>
+      <c r="I98" s="23"/>
+      <c r="J98" s="23">
+        <f>F98-G98</f>
+        <v>9811</v>
+      </c>
+      <c r="K98" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="L98" s="25">
+        <f>SUM(L55:L91)</f>
+        <v>0</v>
+      </c>
+      <c r="M98" s="25">
+        <f>SUM(M55:M95)</f>
+        <v>0</v>
+      </c>
+      <c r="N98" s="25">
+        <f>SUM(N55:N95)</f>
+        <v>9811</v>
+      </c>
+      <c r="O98" s="25">
+        <f>SUM(O49:O54)</f>
+        <v>0</v>
+      </c>
       <c r="P98" s="26"/>
       <c r="Q98" s="26"/>
       <c r="R98" s="26"/>
       <c r="S98" s="26"/>
-      <c r="T98" s="70"/>
-      <c r="U98" s="111"/>
+      <c r="T98" s="26"/>
+      <c r="U98" s="119"/>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A99" s="70"/>
-      <c r="B99" s="131"/>
-      <c r="C99" s="70"/>
-      <c r="D99" s="202" t="s">
+      <c r="A99" s="108"/>
+      <c r="B99" s="79"/>
+      <c r="C99" s="79"/>
+      <c r="D99" s="157"/>
+      <c r="E99" s="75"/>
+      <c r="F99" s="58"/>
+      <c r="G99" s="47"/>
+      <c r="H99" s="47"/>
+      <c r="I99" s="47"/>
+      <c r="J99" s="70">
+        <f t="shared" ref="J99:J110" si="3">F99-G99</f>
+        <v>0</v>
+      </c>
+      <c r="K99" s="68"/>
+      <c r="L99" s="63"/>
+      <c r="M99" s="65"/>
+      <c r="N99" s="66"/>
+      <c r="O99" s="115"/>
+      <c r="P99" s="18"/>
+      <c r="Q99" s="18"/>
+      <c r="R99" s="18"/>
+      <c r="S99" s="18"/>
+      <c r="T99" s="94"/>
+      <c r="U99" s="123"/>
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A100" s="108"/>
+      <c r="B100" s="79"/>
+      <c r="C100" s="79"/>
+      <c r="D100" s="157"/>
+      <c r="E100" s="75"/>
+      <c r="F100" s="58"/>
+      <c r="G100" s="47"/>
+      <c r="H100" s="47"/>
+      <c r="I100" s="47"/>
+      <c r="J100" s="70">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K100" s="68"/>
+      <c r="L100" s="63"/>
+      <c r="M100" s="65"/>
+      <c r="N100" s="66"/>
+      <c r="O100" s="115"/>
+      <c r="P100" s="18"/>
+      <c r="Q100" s="18"/>
+      <c r="R100" s="18"/>
+      <c r="S100" s="18"/>
+      <c r="T100" s="94"/>
+      <c r="U100" s="123"/>
+    </row>
+    <row r="101" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A101" s="108" t="s">
+        <v>159</v>
+      </c>
+      <c r="B101" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="C101" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="D101" s="157" t="s">
+        <v>76</v>
+      </c>
+      <c r="E101" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="F101" s="58">
+        <v>990</v>
+      </c>
+      <c r="G101" s="47"/>
+      <c r="H101" s="47"/>
+      <c r="I101" s="47"/>
+      <c r="J101" s="70">
+        <f t="shared" si="3"/>
+        <v>990</v>
+      </c>
+      <c r="K101" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="L101" s="63"/>
+      <c r="M101" s="65"/>
+      <c r="N101" s="66">
+        <v>990</v>
+      </c>
+      <c r="O101" s="115"/>
+      <c r="P101" s="18">
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="Q101" s="18">
+        <v>0</v>
+      </c>
+      <c r="R101" s="18">
+        <v>0</v>
+      </c>
+      <c r="S101" s="18">
+        <v>0</v>
+      </c>
+      <c r="T101" s="94">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="U101" s="123"/>
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A102" s="108" t="s">
+        <v>159</v>
+      </c>
+      <c r="B102" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="C102" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="D102" s="157" t="s">
+        <v>76</v>
+      </c>
+      <c r="E102" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="F102" s="58">
+        <v>872</v>
+      </c>
+      <c r="G102" s="47"/>
+      <c r="H102" s="47"/>
+      <c r="I102" s="47"/>
+      <c r="J102" s="70">
+        <f t="shared" si="3"/>
+        <v>872</v>
+      </c>
+      <c r="K102" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="L102" s="63"/>
+      <c r="M102" s="65"/>
+      <c r="N102" s="66">
+        <v>872</v>
+      </c>
+      <c r="O102" s="115"/>
+      <c r="P102" s="18">
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="Q102" s="18">
+        <v>0</v>
+      </c>
+      <c r="R102" s="18">
+        <v>0</v>
+      </c>
+      <c r="S102" s="18">
+        <v>0</v>
+      </c>
+      <c r="T102" s="94">
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="U102" s="123"/>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A103" s="108" t="s">
+        <v>164</v>
+      </c>
+      <c r="B103" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="C103" s="79" t="s">
+        <v>165</v>
+      </c>
+      <c r="D103" s="157" t="s">
+        <v>76</v>
+      </c>
+      <c r="E103" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="F103" s="58">
+        <v>931</v>
+      </c>
+      <c r="G103" s="47"/>
+      <c r="H103" s="47"/>
+      <c r="I103" s="47"/>
+      <c r="J103" s="70">
+        <f t="shared" si="3"/>
+        <v>931</v>
+      </c>
+      <c r="K103" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="L103" s="63"/>
+      <c r="M103" s="65"/>
+      <c r="N103" s="66">
+        <v>931</v>
+      </c>
+      <c r="O103" s="115"/>
+      <c r="P103" s="18">
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="Q103" s="18">
+        <v>0</v>
+      </c>
+      <c r="R103" s="18">
+        <v>0</v>
+      </c>
+      <c r="S103" s="18">
+        <v>0</v>
+      </c>
+      <c r="T103" s="94">
+        <v>0.23599999999999999</v>
+      </c>
+      <c r="U103" s="123"/>
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A104" s="108" t="s">
+        <v>164</v>
+      </c>
+      <c r="B104" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="C104" s="79" t="s">
+        <v>165</v>
+      </c>
+      <c r="D104" s="157" t="s">
+        <v>76</v>
+      </c>
+      <c r="E104" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="F104" s="58">
+        <v>949</v>
+      </c>
+      <c r="G104" s="47"/>
+      <c r="H104" s="47"/>
+      <c r="I104" s="47"/>
+      <c r="J104" s="70">
+        <f t="shared" si="3"/>
+        <v>949</v>
+      </c>
+      <c r="K104" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="L104" s="63"/>
+      <c r="M104" s="65"/>
+      <c r="N104" s="66">
+        <v>949</v>
+      </c>
+      <c r="O104" s="115"/>
+      <c r="P104" s="18">
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="Q104" s="18">
+        <v>0</v>
+      </c>
+      <c r="R104" s="18">
+        <v>0</v>
+      </c>
+      <c r="S104" s="18">
+        <v>0</v>
+      </c>
+      <c r="T104" s="94">
+        <v>0.19700000000000001</v>
+      </c>
+      <c r="U104" s="123"/>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A105" s="108" t="s">
+        <v>164</v>
+      </c>
+      <c r="B105" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="C105" s="79" t="s">
+        <v>165</v>
+      </c>
+      <c r="D105" s="157" t="s">
+        <v>76</v>
+      </c>
+      <c r="E105" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="F105" s="58">
+        <v>1026</v>
+      </c>
+      <c r="G105" s="47"/>
+      <c r="H105" s="47"/>
+      <c r="I105" s="47"/>
+      <c r="J105" s="70">
+        <f t="shared" si="3"/>
+        <v>1026</v>
+      </c>
+      <c r="K105" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="L105" s="63"/>
+      <c r="M105" s="65"/>
+      <c r="N105" s="66">
+        <v>1026</v>
+      </c>
+      <c r="O105" s="115"/>
+      <c r="P105" s="18">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="Q105" s="18">
+        <v>0</v>
+      </c>
+      <c r="R105" s="18">
+        <v>0</v>
+      </c>
+      <c r="S105" s="18">
+        <v>0</v>
+      </c>
+      <c r="T105" s="94">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="U105" s="123"/>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A106" s="108" t="s">
+        <v>164</v>
+      </c>
+      <c r="B106" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="C106" s="79" t="s">
+        <v>165</v>
+      </c>
+      <c r="D106" s="157" t="s">
+        <v>76</v>
+      </c>
+      <c r="E106" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="F106" s="58">
+        <v>926</v>
+      </c>
+      <c r="G106" s="47"/>
+      <c r="H106" s="47"/>
+      <c r="I106" s="47"/>
+      <c r="J106" s="70">
+        <f t="shared" si="3"/>
+        <v>926</v>
+      </c>
+      <c r="K106" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="L106" s="63"/>
+      <c r="M106" s="65"/>
+      <c r="N106" s="66">
+        <v>926</v>
+      </c>
+      <c r="O106" s="115"/>
+      <c r="P106" s="18">
+        <v>0.307</v>
+      </c>
+      <c r="Q106" s="18">
+        <v>0</v>
+      </c>
+      <c r="R106" s="18">
+        <v>0</v>
+      </c>
+      <c r="S106" s="18">
+        <v>0</v>
+      </c>
+      <c r="T106" s="94">
+        <v>0.158</v>
+      </c>
+      <c r="U106" s="123"/>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A107" s="108" t="s">
+        <v>167</v>
+      </c>
+      <c r="B107" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="C107" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="D107" s="157" t="s">
+        <v>76</v>
+      </c>
+      <c r="E107" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="F107" s="58">
+        <v>890</v>
+      </c>
+      <c r="G107" s="47"/>
+      <c r="H107" s="47"/>
+      <c r="I107" s="47"/>
+      <c r="J107" s="70">
+        <f t="shared" si="3"/>
+        <v>890</v>
+      </c>
+      <c r="K107" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="L107" s="63"/>
+      <c r="M107" s="65"/>
+      <c r="N107" s="66">
+        <v>890</v>
+      </c>
+      <c r="O107" s="115"/>
+      <c r="P107" s="18">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="Q107" s="18">
+        <v>0</v>
+      </c>
+      <c r="R107" s="18">
+        <v>0</v>
+      </c>
+      <c r="S107" s="18">
+        <v>0</v>
+      </c>
+      <c r="T107" s="94">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="U107" s="123"/>
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A108" s="108" t="s">
+        <v>167</v>
+      </c>
+      <c r="B108" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="C108" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="D108" s="157" t="s">
+        <v>76</v>
+      </c>
+      <c r="E108" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="F108" s="58">
+        <v>940</v>
+      </c>
+      <c r="G108" s="47"/>
+      <c r="H108" s="47"/>
+      <c r="I108" s="47"/>
+      <c r="J108" s="70">
+        <f t="shared" si="3"/>
+        <v>940</v>
+      </c>
+      <c r="K108" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="L108" s="63"/>
+      <c r="M108" s="65"/>
+      <c r="N108" s="66">
+        <v>940</v>
+      </c>
+      <c r="O108" s="115"/>
+      <c r="P108" s="18">
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="Q108" s="18">
+        <v>0</v>
+      </c>
+      <c r="R108" s="18">
+        <v>0</v>
+      </c>
+      <c r="S108" s="18">
+        <v>0</v>
+      </c>
+      <c r="T108" s="94">
+        <v>0.158</v>
+      </c>
+      <c r="U108" s="123"/>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A109" s="108" t="s">
+        <v>167</v>
+      </c>
+      <c r="B109" s="79" t="s">
+        <v>168</v>
+      </c>
+      <c r="C109" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="D109" s="157" t="s">
+        <v>76</v>
+      </c>
+      <c r="E109" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="F109" s="58">
+        <v>746</v>
+      </c>
+      <c r="G109" s="47"/>
+      <c r="H109" s="47"/>
+      <c r="I109" s="47"/>
+      <c r="J109" s="70">
+        <f t="shared" si="3"/>
+        <v>746</v>
+      </c>
+      <c r="K109" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="L109" s="63"/>
+      <c r="M109" s="65"/>
+      <c r="N109" s="66">
+        <v>746</v>
+      </c>
+      <c r="O109" s="115"/>
+      <c r="P109" s="18">
+        <v>1.2E-2</v>
+      </c>
+      <c r="Q109" s="18">
+        <v>0</v>
+      </c>
+      <c r="R109" s="18">
+        <v>0</v>
+      </c>
+      <c r="S109" s="18">
+        <v>0</v>
+      </c>
+      <c r="T109" s="94">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="U109" s="123"/>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A110" s="81"/>
+      <c r="B110" s="132"/>
+      <c r="C110" s="82"/>
+      <c r="D110" s="70"/>
+      <c r="E110" s="57"/>
+      <c r="F110" s="58"/>
+      <c r="G110" s="47"/>
+      <c r="H110" s="47"/>
+      <c r="I110" s="47"/>
+      <c r="J110" s="70">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K110" s="55"/>
+      <c r="L110" s="63"/>
+      <c r="M110" s="65"/>
+      <c r="N110" s="107"/>
+      <c r="O110" s="115"/>
+      <c r="P110" s="18"/>
+      <c r="Q110" s="18"/>
+      <c r="R110" s="18"/>
+      <c r="S110" s="29"/>
+      <c r="T110" s="29"/>
+      <c r="U110" s="123"/>
+    </row>
+    <row r="111" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A111" s="124"/>
+      <c r="B111" s="133"/>
+      <c r="C111" s="125"/>
+      <c r="D111" s="126"/>
+      <c r="E111" s="87"/>
+      <c r="F111" s="88"/>
+      <c r="G111" s="89"/>
+      <c r="H111" s="89"/>
+      <c r="I111" s="89"/>
+      <c r="J111" s="127"/>
+      <c r="K111" s="90"/>
+      <c r="L111" s="63"/>
+      <c r="M111" s="64"/>
+      <c r="N111" s="107"/>
+      <c r="O111" s="115"/>
+      <c r="P111" s="18"/>
+      <c r="Q111" s="18"/>
+      <c r="R111" s="18"/>
+      <c r="S111" s="18"/>
+      <c r="T111" s="18"/>
+      <c r="U111" s="122"/>
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A112" s="124"/>
+      <c r="B112" s="133"/>
+      <c r="C112" s="125"/>
+      <c r="D112" s="127"/>
+      <c r="E112" s="87"/>
+      <c r="F112" s="88"/>
+      <c r="G112" s="91"/>
+      <c r="H112" s="91"/>
+      <c r="I112" s="91"/>
+      <c r="J112" s="127"/>
+      <c r="K112" s="144"/>
+      <c r="L112" s="63"/>
+      <c r="M112" s="65"/>
+      <c r="N112" s="107"/>
+      <c r="O112" s="115"/>
+      <c r="P112" s="18"/>
+      <c r="Q112" s="18"/>
+      <c r="R112" s="18"/>
+      <c r="S112" s="18"/>
+      <c r="T112" s="18"/>
+      <c r="U112" s="122"/>
+    </row>
+    <row r="113" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A113" s="127"/>
+      <c r="B113" s="134"/>
+      <c r="C113" s="125"/>
+      <c r="D113" s="127"/>
+      <c r="E113" s="87"/>
+      <c r="F113" s="88"/>
+      <c r="G113" s="91"/>
+      <c r="H113" s="91"/>
+      <c r="I113" s="91"/>
+      <c r="J113" s="127"/>
+      <c r="K113" s="90"/>
+      <c r="L113" s="56"/>
+      <c r="M113" s="65"/>
+      <c r="N113" s="107"/>
+      <c r="O113" s="115"/>
+      <c r="P113" s="18"/>
+      <c r="Q113" s="18"/>
+      <c r="R113" s="18"/>
+      <c r="S113" s="18"/>
+      <c r="T113" s="18"/>
+      <c r="U113" s="123"/>
+    </row>
+    <row r="114" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A114" s="128"/>
+      <c r="B114" s="135"/>
+      <c r="C114" s="129"/>
+      <c r="D114" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E114" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="F114" s="23">
+        <f>SUM(F99:F113)</f>
+        <v>8270</v>
+      </c>
+      <c r="G114" s="23">
+        <f>SUM(G99:G113)</f>
+        <v>0</v>
+      </c>
+      <c r="H114" s="23"/>
+      <c r="I114" s="23"/>
+      <c r="J114" s="23">
+        <f>F114-G114</f>
+        <v>8270</v>
+      </c>
+      <c r="K114" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="L114" s="25">
+        <f>SUM(L99:L110)</f>
+        <v>0</v>
+      </c>
+      <c r="M114" s="25">
+        <f>SUM(M99:M110)</f>
+        <v>0</v>
+      </c>
+      <c r="N114" s="25">
+        <f>SUM(N99:N113)</f>
+        <v>8270</v>
+      </c>
+      <c r="O114" s="25">
+        <f>SUM(O99:O113)</f>
+        <v>0</v>
+      </c>
+      <c r="P114" s="18"/>
+      <c r="Q114" s="18"/>
+      <c r="R114" s="18"/>
+      <c r="S114" s="18"/>
+      <c r="T114" s="18"/>
+      <c r="U114" s="123"/>
+    </row>
+    <row r="115" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A115" s="128"/>
+      <c r="B115" s="135"/>
+      <c r="C115" s="129"/>
+      <c r="D115" s="23"/>
+      <c r="E115" s="52"/>
+      <c r="F115" s="23"/>
+      <c r="G115" s="23"/>
+      <c r="H115" s="23"/>
+      <c r="I115" s="23"/>
+      <c r="J115" s="23"/>
+      <c r="K115" s="24"/>
+      <c r="L115" s="25"/>
+      <c r="M115" s="25"/>
+      <c r="N115" s="25"/>
+      <c r="O115" s="25"/>
+      <c r="P115" s="18"/>
+      <c r="Q115" s="18"/>
+      <c r="R115" s="18"/>
+      <c r="S115" s="18"/>
+      <c r="T115" s="18"/>
+      <c r="U115" s="123"/>
+    </row>
+    <row r="116" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A116" s="81" t="s">
+        <v>164</v>
+      </c>
+      <c r="B116" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="C116" s="79" t="s">
+        <v>166</v>
+      </c>
+      <c r="D116" s="157" t="s">
+        <v>76</v>
+      </c>
+      <c r="E116" s="75" t="s">
+        <v>135</v>
+      </c>
+      <c r="F116" s="58">
+        <v>665</v>
+      </c>
+      <c r="G116" s="47"/>
+      <c r="H116" s="47"/>
+      <c r="I116" s="47"/>
+      <c r="J116" s="70">
+        <v>665</v>
+      </c>
+      <c r="K116" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="L116" s="63"/>
+      <c r="M116" s="64"/>
+      <c r="N116" s="173">
+        <v>665</v>
+      </c>
+      <c r="O116" s="25"/>
+      <c r="P116" s="18">
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="Q116" s="18">
+        <v>0.22</v>
+      </c>
+      <c r="R116" s="18">
+        <v>0.18</v>
+      </c>
+      <c r="S116" s="18">
+        <v>0</v>
+      </c>
+      <c r="T116" s="18">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="U116" s="123"/>
+    </row>
+    <row r="117" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A117" s="81" t="s">
+        <v>164</v>
+      </c>
+      <c r="B117" s="79" t="s">
+        <v>97</v>
+      </c>
+      <c r="C117" s="79" t="s">
+        <v>166</v>
+      </c>
+      <c r="D117" s="157" t="s">
+        <v>76</v>
+      </c>
+      <c r="E117" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="F117" s="58">
+        <v>653</v>
+      </c>
+      <c r="G117" s="46"/>
+      <c r="H117" s="47"/>
+      <c r="I117" s="46"/>
+      <c r="J117" s="70">
+        <v>653</v>
+      </c>
+      <c r="K117" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="L117" s="63"/>
+      <c r="M117" s="65"/>
+      <c r="N117" s="173">
+        <v>653</v>
+      </c>
+      <c r="O117" s="115"/>
+      <c r="P117" s="18">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="Q117" s="18">
+        <v>0.25</v>
+      </c>
+      <c r="R117" s="18">
+        <v>0.23</v>
+      </c>
+      <c r="S117" s="18">
+        <v>0</v>
+      </c>
+      <c r="T117" s="18">
+        <v>1.9E-2</v>
+      </c>
+      <c r="U117" s="123"/>
+    </row>
+    <row r="118" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A118" s="70"/>
+      <c r="B118" s="131"/>
+      <c r="C118" s="70"/>
+      <c r="D118" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E118" s="52" t="s">
+        <v>39</v>
+      </c>
+      <c r="F118" s="25">
+        <f>SUM(F116:F117)</f>
+        <v>1318</v>
+      </c>
+      <c r="G118" s="25">
+        <f>SUM(G116:G117)</f>
+        <v>0</v>
+      </c>
+      <c r="H118" s="23"/>
+      <c r="I118" s="23"/>
+      <c r="J118" s="25">
+        <f>F118-G118</f>
+        <v>1318</v>
+      </c>
+      <c r="K118" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="L118" s="25">
+        <f>SUM(L116:L117)</f>
+        <v>0</v>
+      </c>
+      <c r="M118" s="25">
+        <f>SUM(M99:M117)</f>
+        <v>0</v>
+      </c>
+      <c r="N118" s="25">
+        <f>SUM(N116:N117)</f>
+        <v>1318</v>
+      </c>
+      <c r="O118" s="25">
+        <f>SUM(O99:O117)</f>
+        <v>0</v>
+      </c>
+      <c r="P118" s="26"/>
+      <c r="Q118" s="26"/>
+      <c r="R118" s="26"/>
+      <c r="S118" s="26"/>
+      <c r="T118" s="26"/>
+      <c r="U118" s="111"/>
+    </row>
+    <row r="119" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A119" s="70"/>
+      <c r="B119" s="131"/>
+      <c r="C119" s="81"/>
+      <c r="D119" s="70"/>
+      <c r="E119" s="108"/>
+      <c r="F119" s="70"/>
+      <c r="G119" s="70"/>
+      <c r="H119" s="70"/>
+      <c r="I119" s="70"/>
+      <c r="J119" s="70"/>
+      <c r="K119" s="70"/>
+      <c r="L119" s="101"/>
+      <c r="M119" s="109"/>
+      <c r="N119" s="107"/>
+      <c r="O119" s="115"/>
+      <c r="P119" s="26"/>
+      <c r="Q119" s="26"/>
+      <c r="R119" s="26"/>
+      <c r="S119" s="26"/>
+      <c r="T119" s="26"/>
+      <c r="U119" s="111"/>
+    </row>
+    <row r="120" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A120" s="70"/>
+      <c r="B120" s="131"/>
+      <c r="C120" s="70"/>
+      <c r="D120" s="70"/>
+      <c r="E120" s="70"/>
+      <c r="F120" s="70"/>
+      <c r="G120" s="70"/>
+      <c r="H120" s="70"/>
+      <c r="I120" s="70"/>
+      <c r="J120" s="70"/>
+      <c r="K120" s="70"/>
+      <c r="L120" s="101"/>
+      <c r="M120" s="109"/>
+      <c r="N120" s="107"/>
+      <c r="O120" s="115"/>
+      <c r="P120" s="26"/>
+      <c r="Q120" s="26"/>
+      <c r="R120" s="26"/>
+      <c r="S120" s="26"/>
+      <c r="T120" s="70"/>
+      <c r="U120" s="111"/>
+    </row>
+    <row r="121" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A121" s="70"/>
+      <c r="B121" s="131"/>
+      <c r="C121" s="70"/>
+      <c r="D121" s="204" t="s">
         <v>24</v>
       </c>
-      <c r="E99" s="203"/>
-      <c r="F99" s="39">
-        <f>SUM(F16,F43,F76,F92,F96)</f>
-        <v>10550</v>
-      </c>
-      <c r="G99" s="39">
-        <f>SUM(G16,G43,G76,G92,G96)</f>
-        <v>0</v>
-      </c>
-      <c r="H99" s="39"/>
-      <c r="I99" s="39"/>
-      <c r="J99" s="39">
-        <f>SUM(F99-G99)</f>
-        <v>10550</v>
-      </c>
-      <c r="K99" s="40" t="s">
+      <c r="E121" s="205"/>
+      <c r="F121" s="39">
+        <f>SUM(F16,F54,F98,F114,F118)</f>
+        <v>27097</v>
+      </c>
+      <c r="G121" s="39">
+        <f>SUM(G16,G54,G98,G114,G118)</f>
+        <v>0</v>
+      </c>
+      <c r="H121" s="39"/>
+      <c r="I121" s="39"/>
+      <c r="J121" s="39">
+        <f>SUM(F121-G121)</f>
+        <v>27097</v>
+      </c>
+      <c r="K121" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="L99" s="39">
-        <f>SUM(L16,L43,L76,L92,L96)</f>
-        <v>0</v>
-      </c>
-      <c r="M99" s="39">
-        <f>SUM(M16,M43,M76,M92,M96)</f>
-        <v>0</v>
-      </c>
-      <c r="N99" s="39">
-        <f>SUM(N16,N43,N76,N92,N96)</f>
-        <v>30650</v>
-      </c>
-      <c r="O99" s="39">
-        <f>SUM(O16,O43,O76,O92,O96)</f>
-        <v>0</v>
-      </c>
-      <c r="P99" s="26"/>
-      <c r="Q99" s="26"/>
-      <c r="R99" s="26"/>
-      <c r="S99" s="26"/>
-      <c r="T99" s="70"/>
-      <c r="U99" s="111"/>
-    </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A100" s="111"/>
-      <c r="B100" s="111"/>
-      <c r="C100" s="111"/>
-      <c r="D100" s="111"/>
-      <c r="E100" s="111"/>
-      <c r="F100" s="111"/>
-      <c r="G100" s="111"/>
-      <c r="H100" s="111"/>
-      <c r="I100" s="111"/>
-      <c r="J100" s="111"/>
-      <c r="K100" s="111"/>
-      <c r="L100" s="111"/>
-      <c r="M100" s="111"/>
-      <c r="N100" s="111"/>
-      <c r="O100" s="111"/>
-      <c r="P100" s="116"/>
-      <c r="Q100" s="116"/>
-      <c r="R100" s="116"/>
-      <c r="S100" s="116"/>
-      <c r="T100" s="111"/>
-      <c r="U100" s="111"/>
-    </row>
-    <row r="101" spans="1:21" ht="18" x14ac:dyDescent="0.25">
-      <c r="A101" s="111"/>
-      <c r="B101" s="111"/>
-      <c r="C101" s="111"/>
-      <c r="D101" s="41"/>
-      <c r="E101" s="111"/>
-      <c r="F101" s="111"/>
-      <c r="G101" s="111"/>
-      <c r="H101" s="111"/>
-      <c r="I101" s="111"/>
-      <c r="J101" s="111"/>
-      <c r="K101" s="42" t="s">
+      <c r="L121" s="39">
+        <f>SUM(L16,L54,L98,L114,L118)</f>
+        <v>0</v>
+      </c>
+      <c r="M121" s="39">
+        <f>SUM(M16,M54,M98,M114,M118)</f>
+        <v>0</v>
+      </c>
+      <c r="N121" s="39">
+        <f>SUM(N16,N54,N98,N114,N118)</f>
+        <v>27097</v>
+      </c>
+      <c r="O121" s="39">
+        <f>SUM(O16,O54,O98,O114,O118)</f>
+        <v>0</v>
+      </c>
+      <c r="P121" s="26"/>
+      <c r="Q121" s="26"/>
+      <c r="R121" s="26"/>
+      <c r="S121" s="26"/>
+      <c r="T121" s="70"/>
+      <c r="U121" s="111"/>
+    </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A122" s="111"/>
+      <c r="B122" s="111"/>
+      <c r="C122" s="111"/>
+      <c r="D122" s="111"/>
+      <c r="E122" s="111"/>
+      <c r="F122" s="111"/>
+      <c r="G122" s="111"/>
+      <c r="H122" s="111"/>
+      <c r="I122" s="111"/>
+      <c r="J122" s="111"/>
+      <c r="K122" s="111"/>
+      <c r="L122" s="111"/>
+      <c r="M122" s="111"/>
+      <c r="N122" s="111"/>
+      <c r="O122" s="111"/>
+      <c r="P122" s="116"/>
+      <c r="Q122" s="116"/>
+      <c r="R122" s="116"/>
+      <c r="S122" s="116"/>
+      <c r="T122" s="111"/>
+      <c r="U122" s="111"/>
+    </row>
+    <row r="123" spans="1:21" ht="18" x14ac:dyDescent="0.25">
+      <c r="A123" s="111"/>
+      <c r="B123" s="111"/>
+      <c r="C123" s="111"/>
+      <c r="D123" s="41"/>
+      <c r="E123" s="111"/>
+      <c r="F123" s="111"/>
+      <c r="G123" s="111"/>
+      <c r="H123" s="111"/>
+      <c r="I123" s="111"/>
+      <c r="J123" s="111"/>
+      <c r="K123" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="L101" s="42">
-        <f>F99-L99-M99-N99-O99</f>
-        <v>-20100</v>
-      </c>
-      <c r="M101" s="111"/>
-      <c r="N101" s="111"/>
-      <c r="O101" s="111"/>
-      <c r="P101" s="111"/>
-      <c r="Q101" s="111"/>
-      <c r="R101" s="111"/>
-      <c r="S101" s="111"/>
-      <c r="T101" s="111"/>
-      <c r="U101" s="111"/>
-    </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A102" s="111"/>
-      <c r="B102" s="111"/>
-      <c r="C102" s="111"/>
-      <c r="D102" s="43"/>
-      <c r="E102" s="111"/>
-      <c r="F102" s="111"/>
-      <c r="G102" s="111"/>
-      <c r="H102" s="111"/>
-      <c r="I102" s="111"/>
-      <c r="J102" s="111"/>
-      <c r="K102" s="111"/>
-      <c r="L102" s="111"/>
-      <c r="M102" s="111"/>
-      <c r="N102" s="111"/>
-      <c r="O102" s="111"/>
-      <c r="P102" s="111"/>
-      <c r="Q102" s="111"/>
-      <c r="R102" s="111"/>
-      <c r="S102" s="111"/>
-      <c r="T102" s="111"/>
-      <c r="U102" s="111"/>
-    </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A103" s="111"/>
-      <c r="B103" s="111"/>
-      <c r="C103" s="111"/>
-      <c r="D103" s="43"/>
-      <c r="E103" s="111"/>
-      <c r="F103" s="111"/>
-      <c r="G103" s="48"/>
-      <c r="H103" s="48"/>
-      <c r="I103" s="48"/>
-      <c r="J103" s="48"/>
-      <c r="K103" s="111"/>
-      <c r="L103" s="111"/>
-      <c r="M103" s="111"/>
-      <c r="N103" s="111"/>
-      <c r="O103" s="111"/>
-      <c r="P103" s="111"/>
-      <c r="Q103" s="111"/>
-      <c r="R103" s="111"/>
-      <c r="S103" s="111"/>
-      <c r="T103" s="111"/>
-      <c r="U103" s="111"/>
-    </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A104" s="111"/>
-      <c r="B104" s="111"/>
-      <c r="C104" s="111"/>
-      <c r="D104" s="43"/>
-      <c r="E104" s="111"/>
-      <c r="F104" s="111"/>
-      <c r="G104" s="111"/>
-      <c r="H104" s="111"/>
-      <c r="I104" s="111"/>
-      <c r="J104" s="111"/>
-      <c r="K104" s="111"/>
-      <c r="L104" s="111"/>
-      <c r="M104" s="111"/>
-      <c r="N104" s="111"/>
-      <c r="O104" s="111"/>
-      <c r="P104" s="111"/>
-      <c r="Q104" s="111"/>
-      <c r="R104" s="111"/>
-      <c r="S104" s="111"/>
-      <c r="T104" s="111"/>
-      <c r="U104" s="111"/>
-    </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A105" s="111"/>
-      <c r="B105" s="111"/>
-      <c r="C105" s="111"/>
-      <c r="D105" s="43"/>
-      <c r="E105" s="111"/>
-      <c r="F105" s="111"/>
-      <c r="G105" s="111"/>
-      <c r="H105" s="111"/>
-      <c r="I105" s="111"/>
-      <c r="J105" s="111"/>
-      <c r="K105" s="111"/>
-      <c r="L105" s="111"/>
-      <c r="M105" s="111"/>
-      <c r="N105" s="111"/>
-      <c r="O105" s="111"/>
-      <c r="P105" s="111"/>
-      <c r="Q105" s="111"/>
-      <c r="R105" s="111"/>
-      <c r="S105" s="111"/>
-      <c r="T105" s="111"/>
-      <c r="U105" s="111"/>
-    </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A106" s="111"/>
-      <c r="B106" s="111"/>
-      <c r="C106" s="111"/>
-      <c r="D106" s="111"/>
-      <c r="E106" s="111"/>
-      <c r="F106" s="111"/>
-      <c r="G106" s="111"/>
-      <c r="H106" s="111"/>
-      <c r="I106" s="111"/>
-      <c r="J106" s="111"/>
-      <c r="K106" s="111"/>
-      <c r="L106" s="111"/>
-      <c r="M106" s="111"/>
-      <c r="N106" s="111"/>
-      <c r="O106" s="111"/>
-      <c r="P106" s="111"/>
-      <c r="Q106" s="111"/>
-      <c r="R106" s="111"/>
-      <c r="S106" s="111"/>
-      <c r="T106" s="111"/>
-      <c r="U106" s="111"/>
-    </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A107" s="111"/>
-      <c r="B107" s="111"/>
-      <c r="C107" s="111"/>
-      <c r="D107" s="111"/>
-      <c r="E107" s="111"/>
-      <c r="F107" s="111"/>
-      <c r="G107" s="111"/>
-      <c r="H107" s="111"/>
-      <c r="I107" s="111"/>
-      <c r="J107" s="111"/>
-      <c r="K107" s="111"/>
-      <c r="L107" s="111"/>
-      <c r="M107" s="111"/>
-      <c r="N107" s="111"/>
-      <c r="O107" s="111"/>
-      <c r="P107" s="111"/>
-      <c r="Q107" s="111"/>
-      <c r="R107" s="111"/>
-      <c r="S107" s="111"/>
-      <c r="T107" s="111"/>
-      <c r="U107" s="111"/>
-    </row>
-    <row r="108" spans="1:21" ht="33" x14ac:dyDescent="0.45">
-      <c r="A108" s="111"/>
-      <c r="B108" s="111"/>
-      <c r="C108" s="111"/>
-      <c r="D108" s="220" t="s">
+      <c r="L123" s="42">
+        <f>F121-L121-M121-N121-O121</f>
+        <v>0</v>
+      </c>
+      <c r="M123" s="111"/>
+      <c r="N123" s="111"/>
+      <c r="O123" s="111"/>
+      <c r="P123" s="111"/>
+      <c r="Q123" s="111"/>
+      <c r="R123" s="111"/>
+      <c r="S123" s="111"/>
+      <c r="T123" s="111"/>
+      <c r="U123" s="111"/>
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A124" s="111"/>
+      <c r="B124" s="111"/>
+      <c r="C124" s="111"/>
+      <c r="D124" s="43"/>
+      <c r="E124" s="111"/>
+      <c r="F124" s="111"/>
+      <c r="G124" s="111"/>
+      <c r="H124" s="111"/>
+      <c r="I124" s="111"/>
+      <c r="J124" s="111"/>
+      <c r="K124" s="111"/>
+      <c r="L124" s="111"/>
+      <c r="M124" s="111"/>
+      <c r="N124" s="111"/>
+      <c r="O124" s="111"/>
+      <c r="P124" s="111"/>
+      <c r="Q124" s="111"/>
+      <c r="R124" s="111"/>
+      <c r="S124" s="111"/>
+      <c r="T124" s="111"/>
+      <c r="U124" s="111"/>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A125" s="111"/>
+      <c r="B125" s="111"/>
+      <c r="C125" s="111"/>
+      <c r="D125" s="43"/>
+      <c r="E125" s="111"/>
+      <c r="F125" s="111"/>
+      <c r="G125" s="48"/>
+      <c r="H125" s="48"/>
+      <c r="I125" s="48"/>
+      <c r="J125" s="48"/>
+      <c r="K125" s="111"/>
+      <c r="L125" s="111"/>
+      <c r="M125" s="111"/>
+      <c r="N125" s="111"/>
+      <c r="O125" s="111"/>
+      <c r="P125" s="111"/>
+      <c r="Q125" s="111"/>
+      <c r="R125" s="111"/>
+      <c r="S125" s="111"/>
+      <c r="T125" s="111"/>
+      <c r="U125" s="111"/>
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A126" s="111"/>
+      <c r="B126" s="111"/>
+      <c r="C126" s="111"/>
+      <c r="D126" s="43"/>
+      <c r="E126" s="111"/>
+      <c r="F126" s="111"/>
+      <c r="G126" s="111"/>
+      <c r="H126" s="111"/>
+      <c r="I126" s="111"/>
+      <c r="J126" s="111"/>
+      <c r="K126" s="111"/>
+      <c r="L126" s="111"/>
+      <c r="M126" s="111"/>
+      <c r="N126" s="111"/>
+      <c r="O126" s="111"/>
+      <c r="P126" s="111"/>
+      <c r="Q126" s="111"/>
+      <c r="R126" s="111"/>
+      <c r="S126" s="111"/>
+      <c r="T126" s="111"/>
+      <c r="U126" s="111"/>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A127" s="111"/>
+      <c r="B127" s="111"/>
+      <c r="C127" s="111"/>
+      <c r="D127" s="43"/>
+      <c r="E127" s="111"/>
+      <c r="F127" s="111"/>
+      <c r="G127" s="111"/>
+      <c r="H127" s="111"/>
+      <c r="I127" s="111"/>
+      <c r="J127" s="111"/>
+      <c r="K127" s="111"/>
+      <c r="L127" s="111"/>
+      <c r="M127" s="111"/>
+      <c r="N127" s="111"/>
+      <c r="O127" s="111"/>
+      <c r="P127" s="111"/>
+      <c r="Q127" s="111"/>
+      <c r="R127" s="111"/>
+      <c r="S127" s="111"/>
+      <c r="T127" s="111"/>
+      <c r="U127" s="111"/>
+    </row>
+    <row r="128" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A128" s="111"/>
+      <c r="B128" s="111"/>
+      <c r="C128" s="111"/>
+      <c r="D128" s="111"/>
+      <c r="E128" s="111"/>
+      <c r="F128" s="111"/>
+      <c r="G128" s="111"/>
+      <c r="H128" s="111"/>
+      <c r="I128" s="111"/>
+      <c r="J128" s="111"/>
+      <c r="K128" s="111"/>
+      <c r="L128" s="111"/>
+      <c r="M128" s="111"/>
+      <c r="N128" s="111"/>
+      <c r="O128" s="111"/>
+      <c r="P128" s="111"/>
+      <c r="Q128" s="111"/>
+      <c r="R128" s="111"/>
+      <c r="S128" s="111"/>
+      <c r="T128" s="111"/>
+      <c r="U128" s="111"/>
+    </row>
+    <row r="129" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A129" s="111"/>
+      <c r="B129" s="111"/>
+      <c r="C129" s="111"/>
+      <c r="D129" s="111"/>
+      <c r="E129" s="111"/>
+      <c r="F129" s="111"/>
+      <c r="G129" s="111"/>
+      <c r="H129" s="111"/>
+      <c r="I129" s="111"/>
+      <c r="J129" s="111"/>
+      <c r="K129" s="111"/>
+      <c r="L129" s="111"/>
+      <c r="M129" s="111"/>
+      <c r="N129" s="111"/>
+      <c r="O129" s="111"/>
+      <c r="P129" s="111"/>
+      <c r="Q129" s="111"/>
+      <c r="R129" s="111"/>
+      <c r="S129" s="111"/>
+      <c r="T129" s="111"/>
+      <c r="U129" s="111"/>
+    </row>
+    <row r="130" spans="1:21" ht="33" x14ac:dyDescent="0.45">
+      <c r="A130" s="111"/>
+      <c r="B130" s="111"/>
+      <c r="C130" s="111"/>
+      <c r="D130" s="206" t="s">
         <v>48</v>
       </c>
-      <c r="E108" s="221"/>
-      <c r="F108" s="221"/>
-      <c r="G108" s="221"/>
-      <c r="H108" s="221"/>
-      <c r="I108" s="221"/>
-      <c r="J108" s="221"/>
-      <c r="K108" s="221"/>
-      <c r="L108" s="221"/>
-      <c r="M108" s="222"/>
-      <c r="N108" s="111"/>
-      <c r="O108" s="111"/>
-      <c r="P108" s="111"/>
-      <c r="Q108" s="111"/>
-      <c r="R108" s="111"/>
-      <c r="S108" s="111"/>
-      <c r="T108" s="111"/>
-      <c r="U108" s="111"/>
-    </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A109" s="111"/>
-      <c r="B109" s="111"/>
-      <c r="C109" s="111"/>
-      <c r="D109" s="111"/>
-      <c r="E109" s="111"/>
-      <c r="F109" s="111"/>
-      <c r="G109" s="111"/>
-      <c r="H109" s="111"/>
-      <c r="I109" s="111"/>
-      <c r="J109" s="111"/>
-      <c r="K109" s="111"/>
-      <c r="L109" s="111"/>
-      <c r="M109" s="111"/>
-      <c r="N109" s="111"/>
-      <c r="O109" s="111"/>
-      <c r="P109" s="111"/>
-      <c r="Q109" s="111"/>
-      <c r="R109" s="111"/>
-      <c r="S109" s="111"/>
-      <c r="T109" s="111"/>
-      <c r="U109" s="111"/>
-    </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A110" s="111"/>
-      <c r="B110" s="111"/>
-      <c r="C110" s="111"/>
-      <c r="D110" s="111"/>
-      <c r="E110" s="111"/>
-      <c r="F110" s="111"/>
-      <c r="G110" s="111"/>
-      <c r="H110" s="111"/>
-      <c r="I110" s="111"/>
-      <c r="J110" s="111"/>
-      <c r="K110" s="111"/>
-      <c r="L110" s="111"/>
-      <c r="M110" s="111"/>
-      <c r="N110" s="111"/>
-      <c r="O110" s="111"/>
-      <c r="P110" s="111"/>
-      <c r="Q110" s="111"/>
-      <c r="R110" s="111"/>
-      <c r="S110" s="111"/>
-      <c r="T110" s="111"/>
-      <c r="U110" s="111"/>
-    </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A111" s="223" t="s">
+      <c r="E130" s="207"/>
+      <c r="F130" s="207"/>
+      <c r="G130" s="207"/>
+      <c r="H130" s="207"/>
+      <c r="I130" s="207"/>
+      <c r="J130" s="207"/>
+      <c r="K130" s="207"/>
+      <c r="L130" s="207"/>
+      <c r="M130" s="208"/>
+      <c r="N130" s="111"/>
+      <c r="O130" s="111"/>
+      <c r="P130" s="111"/>
+      <c r="Q130" s="111"/>
+      <c r="R130" s="111"/>
+      <c r="S130" s="111"/>
+      <c r="T130" s="111"/>
+      <c r="U130" s="111"/>
+    </row>
+    <row r="131" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A131" s="111"/>
+      <c r="B131" s="111"/>
+      <c r="C131" s="111"/>
+      <c r="D131" s="111"/>
+      <c r="E131" s="111"/>
+      <c r="F131" s="111"/>
+      <c r="G131" s="111"/>
+      <c r="H131" s="111"/>
+      <c r="I131" s="111"/>
+      <c r="J131" s="111"/>
+      <c r="K131" s="111"/>
+      <c r="L131" s="111"/>
+      <c r="M131" s="111"/>
+      <c r="N131" s="111"/>
+      <c r="O131" s="111"/>
+      <c r="P131" s="111"/>
+      <c r="Q131" s="111"/>
+      <c r="R131" s="111"/>
+      <c r="S131" s="111"/>
+      <c r="T131" s="111"/>
+      <c r="U131" s="111"/>
+    </row>
+    <row r="132" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A132" s="111"/>
+      <c r="B132" s="111"/>
+      <c r="C132" s="111"/>
+      <c r="D132" s="111"/>
+      <c r="E132" s="111"/>
+      <c r="F132" s="111"/>
+      <c r="G132" s="111"/>
+      <c r="H132" s="111"/>
+      <c r="I132" s="111"/>
+      <c r="J132" s="111"/>
+      <c r="K132" s="111"/>
+      <c r="L132" s="111"/>
+      <c r="M132" s="111"/>
+      <c r="N132" s="111"/>
+      <c r="O132" s="111"/>
+      <c r="P132" s="111"/>
+      <c r="Q132" s="111"/>
+      <c r="R132" s="111"/>
+      <c r="S132" s="111"/>
+      <c r="T132" s="111"/>
+      <c r="U132" s="111"/>
+    </row>
+    <row r="133" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A133" s="209" t="s">
         <v>25</v>
       </c>
-      <c r="B111" s="224"/>
-      <c r="C111" s="225"/>
-      <c r="D111" s="44" t="s">
+      <c r="B133" s="210"/>
+      <c r="C133" s="211"/>
+      <c r="D133" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="E111" s="59" t="s">
+      <c r="E133" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="F111" s="61" t="s">
+      <c r="F133" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="G111" s="223" t="s">
+      <c r="G133" s="209" t="s">
         <v>27</v>
       </c>
-      <c r="H111" s="225"/>
-      <c r="I111" s="223" t="s">
+      <c r="H133" s="211"/>
+      <c r="I133" s="209" t="s">
         <v>28</v>
       </c>
-      <c r="J111" s="225"/>
-      <c r="K111" s="111"/>
-      <c r="L111" s="111"/>
-      <c r="M111" s="111"/>
-      <c r="N111" s="111"/>
-      <c r="O111" s="111"/>
-      <c r="P111" s="111"/>
-      <c r="Q111" s="111"/>
-      <c r="R111" s="111"/>
-      <c r="S111" s="111"/>
-      <c r="T111" s="111"/>
-      <c r="U111" s="111"/>
-    </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A112" s="111"/>
-      <c r="B112" s="111"/>
-      <c r="C112" s="111"/>
-      <c r="D112" s="111"/>
-      <c r="E112" s="111"/>
-      <c r="F112" s="111"/>
-      <c r="G112" s="111"/>
-      <c r="H112" s="111"/>
-      <c r="I112" s="111"/>
-      <c r="J112" s="111"/>
-      <c r="K112" s="111"/>
-      <c r="L112" s="218" t="s">
+      <c r="J133" s="211"/>
+      <c r="K133" s="111"/>
+      <c r="L133" s="111"/>
+      <c r="M133" s="111"/>
+      <c r="N133" s="111"/>
+      <c r="O133" s="111"/>
+      <c r="P133" s="111"/>
+      <c r="Q133" s="111"/>
+      <c r="R133" s="111"/>
+      <c r="S133" s="111"/>
+      <c r="T133" s="111"/>
+      <c r="U133" s="111"/>
+    </row>
+    <row r="134" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A134" s="111"/>
+      <c r="B134" s="111"/>
+      <c r="C134" s="111"/>
+      <c r="D134" s="111"/>
+      <c r="E134" s="111"/>
+      <c r="F134" s="111"/>
+      <c r="G134" s="111"/>
+      <c r="H134" s="111"/>
+      <c r="I134" s="111"/>
+      <c r="J134" s="111"/>
+      <c r="K134" s="111"/>
+      <c r="L134" s="224" t="s">
         <v>35</v>
       </c>
-      <c r="M112" s="219"/>
-      <c r="N112" s="219"/>
-      <c r="O112" s="219"/>
-      <c r="P112" s="219"/>
-      <c r="Q112" s="219"/>
-      <c r="R112" s="219"/>
-      <c r="S112" s="219"/>
-      <c r="T112" s="219"/>
-      <c r="U112" s="219"/>
-    </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A113" s="111"/>
-      <c r="B113" s="111"/>
-      <c r="C113" s="111"/>
-      <c r="D113" s="111"/>
-      <c r="E113" s="111"/>
-      <c r="F113" s="111"/>
-      <c r="G113" s="111"/>
-      <c r="H113" s="111"/>
-      <c r="I113" s="111"/>
-      <c r="J113" s="111"/>
-      <c r="K113" s="111"/>
-      <c r="L113" s="130"/>
-      <c r="M113" s="130"/>
-      <c r="N113" s="130"/>
-      <c r="O113" s="130"/>
-      <c r="P113" s="130"/>
-      <c r="Q113" s="130"/>
-      <c r="R113" s="130"/>
-      <c r="S113" s="130"/>
-      <c r="T113" s="130"/>
-      <c r="U113" s="130"/>
-    </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A114" s="204" t="s">
+      <c r="M134" s="225"/>
+      <c r="N134" s="225"/>
+      <c r="O134" s="225"/>
+      <c r="P134" s="225"/>
+      <c r="Q134" s="225"/>
+      <c r="R134" s="225"/>
+      <c r="S134" s="225"/>
+      <c r="T134" s="225"/>
+      <c r="U134" s="225"/>
+    </row>
+    <row r="135" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A135" s="111"/>
+      <c r="B135" s="111"/>
+      <c r="C135" s="111"/>
+      <c r="D135" s="111"/>
+      <c r="E135" s="111"/>
+      <c r="F135" s="111"/>
+      <c r="G135" s="111"/>
+      <c r="H135" s="111"/>
+      <c r="I135" s="111"/>
+      <c r="J135" s="111"/>
+      <c r="K135" s="111"/>
+      <c r="L135" s="130"/>
+      <c r="M135" s="130"/>
+      <c r="N135" s="130"/>
+      <c r="O135" s="130"/>
+      <c r="P135" s="130"/>
+      <c r="Q135" s="130"/>
+      <c r="R135" s="130"/>
+      <c r="S135" s="130"/>
+      <c r="T135" s="130"/>
+      <c r="U135" s="130"/>
+    </row>
+    <row r="136" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A136" s="196" t="s">
         <v>50</v>
       </c>
-      <c r="B114" s="205"/>
-      <c r="C114" s="206"/>
-      <c r="D114" s="49"/>
-      <c r="E114" s="84">
+      <c r="B136" s="197"/>
+      <c r="C136" s="198"/>
+      <c r="D136" s="49"/>
+      <c r="E136" s="84">
         <v>80240</v>
       </c>
-      <c r="F114" s="153">
+      <c r="F136" s="153">
         <v>0.40699999999999997</v>
       </c>
-      <c r="G114" s="207">
-        <f>E114*0.407</f>
+      <c r="G136" s="199">
+        <f>E136*0.407</f>
         <v>32657.679999999997</v>
       </c>
-      <c r="H114" s="208"/>
-      <c r="I114" s="209">
+      <c r="H136" s="200"/>
+      <c r="I136" s="201">
         <v>32</v>
       </c>
-      <c r="J114" s="210"/>
-      <c r="K114" s="111"/>
-      <c r="L114" s="70"/>
-      <c r="M114" s="70"/>
-      <c r="N114" s="70"/>
-      <c r="O114" s="70"/>
-      <c r="P114" s="70"/>
-      <c r="Q114" s="70"/>
-      <c r="R114" s="70"/>
-      <c r="S114" s="70"/>
-      <c r="T114" s="70"/>
-      <c r="U114" s="70"/>
-    </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A115" s="204" t="s">
+      <c r="J136" s="202"/>
+      <c r="K136" s="111"/>
+      <c r="L136" s="70"/>
+      <c r="M136" s="70"/>
+      <c r="N136" s="70"/>
+      <c r="O136" s="70"/>
+      <c r="P136" s="70"/>
+      <c r="Q136" s="70"/>
+      <c r="R136" s="70"/>
+      <c r="S136" s="70"/>
+      <c r="T136" s="70"/>
+      <c r="U136" s="70"/>
+    </row>
+    <row r="137" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A137" s="196" t="s">
         <v>51</v>
       </c>
-      <c r="B115" s="205"/>
-      <c r="C115" s="206"/>
-      <c r="D115" s="49"/>
-      <c r="E115" s="84">
+      <c r="B137" s="197"/>
+      <c r="C137" s="198"/>
+      <c r="D137" s="49"/>
+      <c r="E137" s="84">
         <v>90710</v>
       </c>
-      <c r="F115" s="153">
+      <c r="F137" s="153">
         <v>0.376</v>
       </c>
-      <c r="G115" s="207">
-        <f>E115*0.376</f>
+      <c r="G137" s="199">
+        <f>E137*0.376</f>
         <v>34106.959999999999</v>
       </c>
-      <c r="H115" s="208"/>
-      <c r="I115" s="209">
+      <c r="H137" s="200"/>
+      <c r="I137" s="201">
         <v>34</v>
       </c>
-      <c r="J115" s="210"/>
-      <c r="K115" s="111"/>
-      <c r="L115" s="70"/>
-      <c r="M115" s="70"/>
-      <c r="N115" s="70"/>
-      <c r="O115" s="70"/>
-      <c r="P115" s="70"/>
-      <c r="Q115" s="70"/>
-      <c r="R115" s="70"/>
-      <c r="S115" s="70"/>
-      <c r="T115" s="70"/>
-      <c r="U115" s="70"/>
-    </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A116" s="204" t="s">
+      <c r="J137" s="202"/>
+      <c r="K137" s="111"/>
+      <c r="L137" s="70"/>
+      <c r="M137" s="70"/>
+      <c r="N137" s="70"/>
+      <c r="O137" s="70"/>
+      <c r="P137" s="70"/>
+      <c r="Q137" s="70"/>
+      <c r="R137" s="70"/>
+      <c r="S137" s="70"/>
+      <c r="T137" s="70"/>
+      <c r="U137" s="70"/>
+    </row>
+    <row r="138" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A138" s="196" t="s">
         <v>52</v>
       </c>
-      <c r="B116" s="205"/>
-      <c r="C116" s="206"/>
-      <c r="D116" s="49"/>
-      <c r="E116" s="84">
+      <c r="B138" s="197"/>
+      <c r="C138" s="198"/>
+      <c r="D138" s="49"/>
+      <c r="E138" s="84">
         <v>81600</v>
       </c>
-      <c r="F116" s="153">
+      <c r="F138" s="153">
         <v>0.40799999999999997</v>
       </c>
-      <c r="G116" s="207">
-        <f>E116*0.408</f>
+      <c r="G138" s="199">
+        <f>E138*0.408</f>
         <v>33292.799999999996</v>
       </c>
-      <c r="H116" s="208"/>
-      <c r="I116" s="209">
+      <c r="H138" s="200"/>
+      <c r="I138" s="201">
         <v>33</v>
       </c>
-      <c r="J116" s="210"/>
-      <c r="K116" s="111"/>
-      <c r="L116" s="70"/>
-      <c r="M116" s="70"/>
-      <c r="N116" s="70"/>
-      <c r="O116" s="70"/>
-      <c r="P116" s="70"/>
-      <c r="Q116" s="70"/>
-      <c r="R116" s="70"/>
-      <c r="S116" s="70"/>
-      <c r="T116" s="70"/>
-      <c r="U116" s="70"/>
-    </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A117" s="204" t="s">
+      <c r="J138" s="202"/>
+      <c r="K138" s="111"/>
+      <c r="L138" s="70"/>
+      <c r="M138" s="70"/>
+      <c r="N138" s="70"/>
+      <c r="O138" s="70"/>
+      <c r="P138" s="70"/>
+      <c r="Q138" s="70"/>
+      <c r="R138" s="70"/>
+      <c r="S138" s="70"/>
+      <c r="T138" s="70"/>
+      <c r="U138" s="70"/>
+    </row>
+    <row r="139" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A139" s="196" t="s">
         <v>53</v>
       </c>
-      <c r="B117" s="205"/>
-      <c r="C117" s="206"/>
-      <c r="D117" s="49"/>
-      <c r="E117" s="148">
+      <c r="B139" s="197"/>
+      <c r="C139" s="198"/>
+      <c r="D139" s="49"/>
+      <c r="E139" s="148">
         <v>89.73</v>
       </c>
-      <c r="F117" s="71">
+      <c r="F139" s="71">
         <v>0.35</v>
       </c>
-      <c r="G117" s="226">
-        <f>E117*0.35</f>
+      <c r="G139" s="220">
+        <f>E139*0.35</f>
         <v>31.4055</v>
       </c>
-      <c r="H117" s="227"/>
-      <c r="I117" s="211">
+      <c r="H139" s="221"/>
+      <c r="I139" s="222">
         <v>31</v>
       </c>
-      <c r="J117" s="212"/>
-      <c r="K117" s="111"/>
-      <c r="L117" s="70"/>
-      <c r="M117" s="70"/>
-      <c r="N117" s="70"/>
-      <c r="O117" s="70"/>
-      <c r="P117" s="70"/>
-      <c r="Q117" s="70"/>
-      <c r="R117" s="70"/>
-      <c r="S117" s="70"/>
-      <c r="T117" s="70"/>
-      <c r="U117" s="70"/>
-    </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A118" s="149"/>
-      <c r="B118" s="150" t="s">
+      <c r="J139" s="223"/>
+      <c r="K139" s="111"/>
+      <c r="L139" s="70"/>
+      <c r="M139" s="70"/>
+      <c r="N139" s="70"/>
+      <c r="O139" s="70"/>
+      <c r="P139" s="70"/>
+      <c r="Q139" s="70"/>
+      <c r="R139" s="70"/>
+      <c r="S139" s="70"/>
+      <c r="T139" s="70"/>
+      <c r="U139" s="70"/>
+    </row>
+    <row r="140" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A140" s="149"/>
+      <c r="B140" s="150" t="s">
         <v>77</v>
       </c>
-      <c r="C118" s="151"/>
-      <c r="D118" s="49"/>
-      <c r="E118" s="84">
+      <c r="C140" s="151"/>
+      <c r="D140" s="49"/>
+      <c r="E140" s="84">
         <v>34600</v>
       </c>
-      <c r="F118" s="71">
+      <c r="F140" s="71">
         <v>0.45400000000000001</v>
       </c>
-      <c r="G118" s="207">
-        <f>E118*0.454</f>
+      <c r="G140" s="199">
+        <f>E140*0.454</f>
         <v>15708.4</v>
       </c>
-      <c r="H118" s="208"/>
-      <c r="I118" s="211">
+      <c r="H140" s="200"/>
+      <c r="I140" s="222">
         <v>15</v>
       </c>
-      <c r="J118" s="212"/>
-      <c r="K118" s="111"/>
-      <c r="L118" s="70"/>
-      <c r="M118" s="70"/>
-      <c r="N118" s="70"/>
-      <c r="O118" s="70"/>
-      <c r="P118" s="70"/>
-      <c r="Q118" s="70"/>
-      <c r="R118" s="70"/>
-      <c r="S118" s="70"/>
-      <c r="T118" s="70"/>
-      <c r="U118" s="70"/>
-    </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A119" s="213" t="s">
+      <c r="J140" s="223"/>
+      <c r="K140" s="111"/>
+      <c r="L140" s="70"/>
+      <c r="M140" s="70"/>
+      <c r="N140" s="70"/>
+      <c r="O140" s="70"/>
+      <c r="P140" s="70"/>
+      <c r="Q140" s="70"/>
+      <c r="R140" s="70"/>
+      <c r="S140" s="70"/>
+      <c r="T140" s="70"/>
+      <c r="U140" s="70"/>
+    </row>
+    <row r="141" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A141" s="212" t="s">
         <v>29</v>
       </c>
-      <c r="B119" s="214"/>
-      <c r="C119" s="215"/>
-      <c r="D119" s="50">
-        <f>SUM(D114:D118)</f>
-        <v>0</v>
-      </c>
-      <c r="E119" s="86">
-        <f>SUM(E114:E118)</f>
+      <c r="B141" s="213"/>
+      <c r="C141" s="214"/>
+      <c r="D141" s="50">
+        <f>SUM(D136:D140)</f>
+        <v>0</v>
+      </c>
+      <c r="E141" s="86">
+        <f>SUM(E136:E140)</f>
         <v>287239.73</v>
       </c>
-      <c r="F119" s="60"/>
-      <c r="G119" s="216">
-        <f>SUM(G114:G118)</f>
+      <c r="F141" s="60"/>
+      <c r="G141" s="215">
+        <f>SUM(G136:G140)</f>
         <v>115797.24549999999</v>
       </c>
-      <c r="H119" s="217"/>
-      <c r="I119" s="213">
-        <f>SUM(I114:I118)</f>
+      <c r="H141" s="216"/>
+      <c r="I141" s="212">
+        <f>SUM(I136:I140)</f>
         <v>145</v>
       </c>
-      <c r="J119" s="215"/>
+      <c r="J141" s="214"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A119:C119"/>
-    <mergeCell ref="G119:H119"/>
-    <mergeCell ref="I119:J119"/>
+    <mergeCell ref="A141:C141"/>
+    <mergeCell ref="G141:H141"/>
+    <mergeCell ref="I141:J141"/>
     <mergeCell ref="G1:N1"/>
-    <mergeCell ref="G118:H118"/>
-    <mergeCell ref="A116:C116"/>
-    <mergeCell ref="G116:H116"/>
-    <mergeCell ref="I116:J116"/>
-    <mergeCell ref="A117:C117"/>
-    <mergeCell ref="G117:H117"/>
-    <mergeCell ref="I117:J117"/>
-    <mergeCell ref="I118:J118"/>
-    <mergeCell ref="L112:U112"/>
-    <mergeCell ref="A114:C114"/>
-    <mergeCell ref="G114:H114"/>
-    <mergeCell ref="I114:J114"/>
-    <mergeCell ref="A115:C115"/>
-    <mergeCell ref="G115:H115"/>
-    <mergeCell ref="I115:J115"/>
+    <mergeCell ref="G140:H140"/>
+    <mergeCell ref="A138:C138"/>
+    <mergeCell ref="G138:H138"/>
+    <mergeCell ref="I138:J138"/>
+    <mergeCell ref="A139:C139"/>
+    <mergeCell ref="G139:H139"/>
+    <mergeCell ref="I139:J139"/>
+    <mergeCell ref="I140:J140"/>
+    <mergeCell ref="L134:U134"/>
+    <mergeCell ref="A136:C136"/>
+    <mergeCell ref="G136:H136"/>
+    <mergeCell ref="I136:J136"/>
+    <mergeCell ref="A137:C137"/>
+    <mergeCell ref="G137:H137"/>
+    <mergeCell ref="I137:J137"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="D108:M108"/>
-    <mergeCell ref="A111:C111"/>
-    <mergeCell ref="G111:H111"/>
-    <mergeCell ref="I111:J111"/>
+    <mergeCell ref="D121:E121"/>
+    <mergeCell ref="D130:M130"/>
+    <mergeCell ref="A133:C133"/>
+    <mergeCell ref="G133:H133"/>
+    <mergeCell ref="I133:J133"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10092,26 +11065,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="196" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="196"/>
-      <c r="C1" s="196"/>
+      <c r="A1" s="203" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="203"/>
+      <c r="C1" s="203"/>
       <c r="D1" s="1">
         <v>46253</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="197" t="s">
+      <c r="G1" s="217" t="s">
         <v>130</v>
       </c>
-      <c r="H1" s="198"/>
-      <c r="I1" s="198"/>
-      <c r="J1" s="199"/>
-      <c r="K1" s="200" t="s">
+      <c r="H1" s="218"/>
+      <c r="I1" s="218"/>
+      <c r="J1" s="227"/>
+      <c r="K1" s="226" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="201"/>
+      <c r="L1" s="219"/>
     </row>
     <row r="2" spans="1:20" ht="39" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
@@ -17570,9 +18543,7 @@
       <c r="E159" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="F159" s="167">
-        <v>1000</v>
-      </c>
+      <c r="F159" s="167"/>
       <c r="G159" s="70"/>
       <c r="H159" s="76" t="s">
         <v>293</v>
@@ -17582,15 +18553,13 @@
       </c>
       <c r="J159" s="70">
         <f t="shared" si="3"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="K159" s="154" t="s">
         <v>186</v>
       </c>
       <c r="L159" s="63"/>
-      <c r="M159" s="139">
-        <v>1000</v>
-      </c>
+      <c r="M159" s="139"/>
       <c r="N159" s="103"/>
       <c r="O159" s="95"/>
       <c r="P159" s="18">
@@ -17621,9 +18590,7 @@
       <c r="E160" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="F160" s="167">
-        <v>1000</v>
-      </c>
+      <c r="F160" s="167"/>
       <c r="G160" s="70"/>
       <c r="H160" s="76" t="s">
         <v>293</v>
@@ -17633,15 +18600,13 @@
       </c>
       <c r="J160" s="70">
         <f t="shared" si="3"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="K160" s="154" t="s">
         <v>84</v>
       </c>
       <c r="L160" s="63"/>
-      <c r="M160" s="139">
-        <v>1000</v>
-      </c>
+      <c r="M160" s="139"/>
       <c r="N160" s="103"/>
       <c r="O160" s="95"/>
       <c r="P160" s="18">
@@ -17949,7 +18914,7 @@
       </c>
       <c r="F170" s="23">
         <f>SUM(F35:F165)</f>
-        <v>118640</v>
+        <v>116640</v>
       </c>
       <c r="G170" s="155">
         <f>SUM(G35:G169)</f>
@@ -17959,7 +18924,7 @@
       <c r="I170" s="23"/>
       <c r="J170" s="23">
         <f>F170-G170</f>
-        <v>118640</v>
+        <v>116640</v>
       </c>
       <c r="K170" s="24" t="s">
         <v>16</v>
@@ -17970,7 +18935,7 @@
       </c>
       <c r="M170" s="25">
         <f>SUM(M35:M169)</f>
-        <v>81640</v>
+        <v>79640</v>
       </c>
       <c r="N170" s="25">
         <f>SUM(N35:N165)</f>
@@ -21936,7 +22901,9 @@
         <v>1000</v>
       </c>
       <c r="G256" s="70"/>
-      <c r="H256" s="70"/>
+      <c r="H256" s="70" t="s">
+        <v>295</v>
+      </c>
       <c r="I256" s="70"/>
       <c r="J256" s="76">
         <f t="shared" si="4"/>
@@ -30361,7 +31328,7 @@
       </c>
       <c r="F441" s="88"/>
       <c r="G441" s="89">
-        <v>1348</v>
+        <v>1235</v>
       </c>
       <c r="H441" s="89"/>
       <c r="I441" s="89" t="s">
@@ -30439,13 +31406,13 @@
       </c>
       <c r="G444" s="23">
         <f>SUM(G370:G443)</f>
-        <v>1348</v>
+        <v>1235</v>
       </c>
       <c r="H444" s="23"/>
       <c r="I444" s="23"/>
       <c r="J444" s="23">
         <f>F444-G444</f>
-        <v>51705</v>
+        <v>51818</v>
       </c>
       <c r="K444" s="24" t="s">
         <v>16</v>
@@ -31240,23 +32207,23 @@
       <c r="A465" s="70"/>
       <c r="B465" s="131"/>
       <c r="C465" s="70"/>
-      <c r="D465" s="202" t="s">
+      <c r="D465" s="204" t="s">
         <v>49</v>
       </c>
-      <c r="E465" s="203"/>
+      <c r="E465" s="205"/>
       <c r="F465" s="39">
         <f>SUM(F34,F170,F369,F444,F462)</f>
-        <v>380054</v>
+        <v>378054</v>
       </c>
       <c r="G465" s="39">
         <f>SUM(G34,G170,G369,G444,G462)</f>
-        <v>1348</v>
+        <v>1235</v>
       </c>
       <c r="H465" s="39"/>
       <c r="I465" s="39"/>
       <c r="J465" s="39">
         <f>SUM(F465-G465)</f>
-        <v>378706</v>
+        <v>376819</v>
       </c>
       <c r="K465" s="40" t="s">
         <v>16</v>
@@ -31267,7 +32234,7 @@
       </c>
       <c r="M465" s="39">
         <f>SUM(M34,M170,M369,M444,M462)</f>
-        <v>269882</v>
+        <v>267882</v>
       </c>
       <c r="N465" s="39">
         <f>SUM(N34,N170,N369,N444,N462)</f>
@@ -31369,11 +32336,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="196" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="196"/>
-      <c r="C1" s="196"/>
+      <c r="A1" s="203" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="203"/>
+      <c r="C1" s="203"/>
       <c r="D1" s="1">
         <v>46231</v>
       </c>
@@ -33124,10 +34091,10 @@
       <c r="A45" s="70"/>
       <c r="B45" s="131"/>
       <c r="C45" s="70"/>
-      <c r="D45" s="202" t="s">
+      <c r="D45" s="204" t="s">
         <v>24</v>
       </c>
-      <c r="E45" s="203"/>
+      <c r="E45" s="205"/>
       <c r="F45" s="39">
         <f>SUM(F11,F23,F37,F43,)</f>
         <v>20414</v>
@@ -33361,18 +34328,18 @@
       <c r="A54" s="111"/>
       <c r="B54" s="111"/>
       <c r="C54" s="111"/>
-      <c r="D54" s="220" t="s">
+      <c r="D54" s="206" t="s">
         <v>42</v>
       </c>
-      <c r="E54" s="221"/>
-      <c r="F54" s="221"/>
-      <c r="G54" s="221"/>
-      <c r="H54" s="221"/>
-      <c r="I54" s="221"/>
-      <c r="J54" s="221"/>
-      <c r="K54" s="221"/>
-      <c r="L54" s="221"/>
-      <c r="M54" s="222"/>
+      <c r="E54" s="207"/>
+      <c r="F54" s="207"/>
+      <c r="G54" s="207"/>
+      <c r="H54" s="207"/>
+      <c r="I54" s="207"/>
+      <c r="J54" s="207"/>
+      <c r="K54" s="207"/>
+      <c r="L54" s="207"/>
+      <c r="M54" s="208"/>
       <c r="N54" s="111"/>
       <c r="O54" s="111"/>
       <c r="P54" s="111"/>
@@ -33429,11 +34396,11 @@
       <c r="U56" s="111"/>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A57" s="223" t="s">
+      <c r="A57" s="209" t="s">
         <v>25</v>
       </c>
-      <c r="B57" s="224"/>
-      <c r="C57" s="225"/>
+      <c r="B57" s="210"/>
+      <c r="C57" s="211"/>
       <c r="D57" s="44" t="s">
         <v>26</v>
       </c>
@@ -33443,14 +34410,14 @@
       <c r="F57" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="G57" s="223" t="s">
+      <c r="G57" s="209" t="s">
         <v>27</v>
       </c>
-      <c r="H57" s="225"/>
-      <c r="I57" s="223" t="s">
+      <c r="H57" s="211"/>
+      <c r="I57" s="209" t="s">
         <v>28</v>
       </c>
-      <c r="J57" s="225"/>
+      <c r="J57" s="211"/>
       <c r="K57" s="111"/>
       <c r="L57" s="111"/>
       <c r="M57" s="111"/>
@@ -33475,18 +34442,18 @@
       <c r="I58" s="111"/>
       <c r="J58" s="111"/>
       <c r="K58" s="111"/>
-      <c r="L58" s="218" t="s">
+      <c r="L58" s="224" t="s">
         <v>35</v>
       </c>
-      <c r="M58" s="219"/>
-      <c r="N58" s="219"/>
-      <c r="O58" s="219"/>
-      <c r="P58" s="219"/>
-      <c r="Q58" s="219"/>
-      <c r="R58" s="219"/>
-      <c r="S58" s="219"/>
-      <c r="T58" s="219"/>
-      <c r="U58" s="219"/>
+      <c r="M58" s="225"/>
+      <c r="N58" s="225"/>
+      <c r="O58" s="225"/>
+      <c r="P58" s="225"/>
+      <c r="Q58" s="225"/>
+      <c r="R58" s="225"/>
+      <c r="S58" s="225"/>
+      <c r="T58" s="225"/>
+      <c r="U58" s="225"/>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="111"/>
@@ -33512,11 +34479,11 @@
       <c r="U59" s="130"/>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A60" s="204" t="s">
+      <c r="A60" s="196" t="s">
         <v>57</v>
       </c>
-      <c r="B60" s="205"/>
-      <c r="C60" s="206"/>
+      <c r="B60" s="197"/>
+      <c r="C60" s="198"/>
       <c r="D60" s="49"/>
       <c r="E60" s="84">
         <v>48520</v>
@@ -33524,15 +34491,15 @@
       <c r="F60" s="71">
         <v>0.318</v>
       </c>
-      <c r="G60" s="207">
+      <c r="G60" s="199">
         <f>E60*0.318</f>
         <v>15429.36</v>
       </c>
-      <c r="H60" s="208"/>
-      <c r="I60" s="209">
+      <c r="H60" s="200"/>
+      <c r="I60" s="201">
         <v>15</v>
       </c>
-      <c r="J60" s="210"/>
+      <c r="J60" s="202"/>
       <c r="K60" s="111"/>
       <c r="L60" s="70"/>
       <c r="M60" s="70"/>
@@ -33546,9 +34513,9 @@
       <c r="U60" s="70"/>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A61" s="204"/>
-      <c r="B61" s="205"/>
-      <c r="C61" s="206"/>
+      <c r="A61" s="196"/>
+      <c r="B61" s="197"/>
+      <c r="C61" s="198"/>
       <c r="D61" s="49"/>
       <c r="E61" s="84">
         <v>20110</v>
@@ -33556,15 +34523,15 @@
       <c r="F61" s="71">
         <v>0.318</v>
       </c>
-      <c r="G61" s="207">
+      <c r="G61" s="199">
         <f>E61*0.318</f>
         <v>6394.9800000000005</v>
       </c>
-      <c r="H61" s="208"/>
-      <c r="I61" s="209">
+      <c r="H61" s="200"/>
+      <c r="I61" s="201">
         <v>6</v>
       </c>
-      <c r="J61" s="210"/>
+      <c r="J61" s="202"/>
       <c r="K61" s="111"/>
       <c r="L61" s="70"/>
       <c r="M61" s="70"/>
@@ -33578,19 +34545,19 @@
       <c r="U61" s="70"/>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A62" s="204"/>
-      <c r="B62" s="205"/>
-      <c r="C62" s="206"/>
+      <c r="A62" s="196"/>
+      <c r="B62" s="197"/>
+      <c r="C62" s="198"/>
       <c r="D62" s="117"/>
       <c r="E62" s="85"/>
       <c r="F62" s="71"/>
-      <c r="G62" s="207">
+      <c r="G62" s="199">
         <f>E62*0</f>
         <v>0</v>
       </c>
-      <c r="H62" s="208"/>
-      <c r="I62" s="209"/>
-      <c r="J62" s="210"/>
+      <c r="H62" s="200"/>
+      <c r="I62" s="201"/>
+      <c r="J62" s="202"/>
       <c r="K62" s="111"/>
       <c r="L62" s="111"/>
       <c r="M62" s="111"/>
@@ -33604,17 +34571,17 @@
       <c r="U62" s="111"/>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A63" s="204"/>
-      <c r="B63" s="205"/>
-      <c r="C63" s="206"/>
+      <c r="A63" s="196"/>
+      <c r="B63" s="197"/>
+      <c r="C63" s="198"/>
       <c r="D63" s="117"/>
       <c r="E63" s="85"/>
       <c r="F63" s="62"/>
-      <c r="G63" s="207">
+      <c r="G63" s="199">
         <f>E63*0</f>
         <v>0</v>
       </c>
-      <c r="H63" s="208"/>
+      <c r="H63" s="200"/>
       <c r="I63" s="230"/>
       <c r="J63" s="231"/>
       <c r="K63" s="111"/>
@@ -33630,11 +34597,11 @@
       <c r="U63" s="111"/>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A64" s="213" t="s">
+      <c r="A64" s="212" t="s">
         <v>29</v>
       </c>
-      <c r="B64" s="214"/>
-      <c r="C64" s="215"/>
+      <c r="B64" s="213"/>
+      <c r="C64" s="214"/>
       <c r="D64" s="50">
         <f>SUM(D60:D63)</f>
         <v>0</v>
@@ -33644,16 +34611,16 @@
         <v>68630</v>
       </c>
       <c r="F64" s="60"/>
-      <c r="G64" s="216">
+      <c r="G64" s="215">
         <f>SUM(G60:G63)</f>
         <v>21824.34</v>
       </c>
-      <c r="H64" s="217"/>
-      <c r="I64" s="213">
+      <c r="H64" s="216"/>
+      <c r="I64" s="212">
         <f>SUM(I60:I63)</f>
         <v>21</v>
       </c>
-      <c r="J64" s="215"/>
+      <c r="J64" s="214"/>
     </row>
   </sheetData>
   <mergeCells count="23">
